--- a/research/traditional_assets/database/data/australia/australia_information_services.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_information_services.xlsx
@@ -650,10 +650,10 @@
         <v>0.1647740548623768</v>
       </c>
       <c r="X2">
-        <v>0.09562061893644674</v>
+        <v>0.09558858870804832</v>
       </c>
       <c r="Y2">
-        <v>0.06915343592593001</v>
+        <v>0.06918546615432844</v>
       </c>
       <c r="Z2">
         <v>1.422937009381581</v>
@@ -662,10 +662,10 @@
         <v>0.2801417797344428</v>
       </c>
       <c r="AB2">
-        <v>0.08707822101302962</v>
+        <v>0.08705115111614727</v>
       </c>
       <c r="AC2">
-        <v>0.1930635587214132</v>
+        <v>0.1930906286182956</v>
       </c>
       <c r="AD2">
         <v>2257.5</v>
@@ -787,10 +787,10 @@
         <v>0.1647740548623768</v>
       </c>
       <c r="X3">
-        <v>0.09562061893644674</v>
+        <v>0.09558858870804832</v>
       </c>
       <c r="Y3">
-        <v>0.06915343592593001</v>
+        <v>0.06918546615432844</v>
       </c>
       <c r="Z3">
         <v>1.422937009381581</v>
@@ -799,10 +799,10 @@
         <v>0.2801417797344428</v>
       </c>
       <c r="AB3">
-        <v>0.08707822101302962</v>
+        <v>0.08705115111614727</v>
       </c>
       <c r="AC3">
-        <v>0.1930635587214132</v>
+        <v>0.1930906286182956</v>
       </c>
       <c r="AD3">
         <v>2257.5</v>
@@ -1139,49 +1139,49 @@
         <v>6.11878247958426</v>
       </c>
       <c r="F2">
-        <v>2.52579686481588</v>
+        <v>2.50820525325629</v>
       </c>
       <c r="G2">
         <v>2.31111793611794</v>
       </c>
       <c r="H2">
-        <v>5.52170454545455</v>
+        <v>5.82017506142506</v>
       </c>
       <c r="I2">
         <v>0.154864069477887</v>
       </c>
       <c r="J2">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="K2">
         <v>12319.8</v>
       </c>
       <c r="L2">
-        <v>10346.3907366793</v>
+        <v>10477.3137965882</v>
       </c>
       <c r="M2">
         <v>13383.4</v>
       </c>
       <c r="N2">
-        <v>14546.0917366793</v>
+        <v>14968.5607965882</v>
       </c>
       <c r="O2">
         <v>2257.5</v>
       </c>
       <c r="P2">
-        <v>5393.601</v>
+        <v>5685.147</v>
       </c>
       <c r="Q2">
-        <v>0.0870782210130296</v>
+        <v>0.08705115111614729</v>
       </c>
       <c r="R2">
-        <v>0.08377878860565301</v>
+        <v>0.0826826811976259</v>
       </c>
       <c r="S2">
         <v>0.04046</v>
       </c>
       <c r="T2">
-        <v>0.04235</v>
+        <v>0.04046</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0956206189364467</v>
+        <v>0.0955885887080483</v>
       </c>
       <c r="X2">
-        <v>0.108109981913735</v>
+        <v>0.109677510160043</v>
       </c>
       <c r="Y2">
         <v>1.14985193321128</v>
       </c>
       <c r="Z2">
-        <v>1.43810443730665</v>
+        <v>1.47523118152523</v>
       </c>
       <c r="AA2">
         <v>2257.5</v>
@@ -1236,7 +1236,7 @@
         <v>12319.8</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.04330000000000001</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08995668009634761</v>
+        <v>0.08992829127703955</v>
       </c>
       <c r="C2">
-        <v>13704.87097654032</v>
+        <v>13704.70972933795</v>
       </c>
       <c r="D2">
-        <v>12510.97097654032</v>
+        <v>12510.80972933795</v>
       </c>
       <c r="E2">
         <v>-2257.5</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08995668009634761</v>
+        <v>0.08992829127703955</v>
       </c>
       <c r="T2">
         <v>1.01912912879999</v>
       </c>
       <c r="U2">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.3</v>
       </c>
       <c r="W2">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08972811005605856</v>
+        <v>0.08969000640320841</v>
       </c>
       <c r="C3">
-        <v>13624.19600002719</v>
+        <v>13626.85963393936</v>
       </c>
       <c r="D3">
-        <v>12576.06900002719</v>
+        <v>12578.73263393936</v>
       </c>
       <c r="E3">
         <v>-2111.727</v>
@@ -1539,37 +1539,37 @@
         <v>824.2</v>
       </c>
       <c r="M3">
-        <v>7.536464100000002</v>
+        <v>7.332381900000001</v>
       </c>
       <c r="N3">
-        <v>816.6635359000001</v>
+        <v>816.8676181000001</v>
       </c>
       <c r="O3">
-        <v>244.99906077</v>
+        <v>245.06028543</v>
       </c>
       <c r="P3">
-        <v>571.66447513</v>
+        <v>571.8073326700001</v>
       </c>
       <c r="Q3">
-        <v>724.2644751299999</v>
+        <v>724.40733267</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.0902688990465238</v>
+        <v>0.09024030949819033</v>
       </c>
       <c r="T3">
         <v>1.026335092336959</v>
       </c>
       <c r="U3">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.3</v>
       </c>
       <c r="W3">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>109.3616302106448</v>
+        <v>112.4054926817164</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08949954001576953</v>
+        <v>0.08945172152937732</v>
       </c>
       <c r="C4">
-        <v>13544.20201273479</v>
+        <v>13549.75109008495</v>
       </c>
       <c r="D4">
-        <v>12641.84801273479</v>
+        <v>12647.39709008495</v>
       </c>
       <c r="E4">
         <v>-1965.954</v>
@@ -1621,37 +1621,37 @@
         <v>824.2</v>
       </c>
       <c r="M4">
-        <v>15.0729282</v>
+        <v>14.6647638</v>
       </c>
       <c r="N4">
-        <v>809.1270718000001</v>
+        <v>809.5352362000001</v>
       </c>
       <c r="O4">
-        <v>242.73812154</v>
+        <v>242.86057086</v>
       </c>
       <c r="P4">
-        <v>566.38895026</v>
+        <v>566.67466534</v>
       </c>
       <c r="Q4">
-        <v>718.9889502599999</v>
+        <v>719.27466534</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.09058748981200973</v>
+        <v>0.09055869543814012</v>
       </c>
       <c r="T4">
         <v>1.033688116354275</v>
       </c>
       <c r="U4">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.3</v>
       </c>
       <c r="W4">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>54.6808151053224</v>
+        <v>56.20274634085822</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08927096997548048</v>
+        <v>0.08921343665554619</v>
       </c>
       <c r="C5">
-        <v>13464.89975657209</v>
+        <v>13473.39630831574</v>
       </c>
       <c r="D5">
-        <v>12708.31875657209</v>
+        <v>12716.81530831574</v>
       </c>
       <c r="E5">
         <v>-1820.181</v>
@@ -1703,37 +1703,37 @@
         <v>824.2</v>
       </c>
       <c r="M5">
-        <v>22.6093923</v>
+        <v>21.9971457</v>
       </c>
       <c r="N5">
-        <v>801.5906077000001</v>
+        <v>802.2028543</v>
       </c>
       <c r="O5">
-        <v>240.47718231</v>
+        <v>240.66085629</v>
       </c>
       <c r="P5">
-        <v>561.1134253900001</v>
+        <v>561.54199801</v>
       </c>
       <c r="Q5">
-        <v>713.71342539</v>
+        <v>714.14199801</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.09091264945925824</v>
+        <v>0.09088364603664556</v>
       </c>
       <c r="T5">
         <v>1.041192749114216</v>
       </c>
       <c r="U5">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.3</v>
       </c>
       <c r="W5">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>36.4538767368816</v>
+        <v>37.46849756057214</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08904239993519142</v>
+        <v>0.08897515178171507</v>
       </c>
       <c r="C6">
-        <v>13386.3002005657</v>
+        <v>13397.80776873398</v>
       </c>
       <c r="D6">
-        <v>12775.4922005657</v>
+        <v>12786.99976873399</v>
       </c>
       <c r="E6">
         <v>-1674.408</v>
@@ -1785,37 +1785,37 @@
         <v>824.2</v>
       </c>
       <c r="M6">
-        <v>30.14585640000001</v>
+        <v>29.3295276</v>
       </c>
       <c r="N6">
-        <v>794.0541436000001</v>
+        <v>794.8704724</v>
       </c>
       <c r="O6">
-        <v>238.21624308</v>
+        <v>238.46114172</v>
       </c>
       <c r="P6">
-        <v>555.8379005200001</v>
+        <v>556.40933068</v>
       </c>
       <c r="Q6">
-        <v>708.43790052</v>
+        <v>709.0093306799999</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.09124458326582441</v>
+        <v>0.09121536643928653</v>
       </c>
       <c r="T6">
         <v>1.048853728389989</v>
       </c>
       <c r="U6">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.3</v>
       </c>
       <c r="W6">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>27.3404075526612</v>
+        <v>28.10137317042911</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.0888138298949024</v>
+        <v>0.08873686690788395</v>
       </c>
       <c r="C7">
-        <v>13308.41454689431</v>
+        <v>13322.99822848311</v>
       </c>
       <c r="D7">
-        <v>12843.37954689431</v>
+        <v>12857.96322848312</v>
       </c>
       <c r="E7">
         <v>-1528.635</v>
@@ -1867,37 +1867,37 @@
         <v>824.2</v>
       </c>
       <c r="M7">
-        <v>37.68232050000001</v>
+        <v>36.6619095</v>
       </c>
       <c r="N7">
-        <v>786.5176795</v>
+        <v>787.5380905000001</v>
       </c>
       <c r="O7">
-        <v>235.95530385</v>
+        <v>236.26142715</v>
       </c>
       <c r="P7">
-        <v>550.56237565</v>
+        <v>551.27666335</v>
       </c>
       <c r="Q7">
-        <v>703.1623756499999</v>
+        <v>703.8766633499999</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09158350515252883</v>
+        <v>0.09155407042935153</v>
       </c>
       <c r="T7">
         <v>1.056675991439989</v>
       </c>
       <c r="U7">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.3</v>
       </c>
       <c r="W7">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>21.87232604212895</v>
+        <v>22.48109853634329</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08858525985461337</v>
+        <v>0.08849858203405284</v>
       </c>
       <c r="C8">
-        <v>13231.25423711651</v>
+        <v>13248.98072947799</v>
       </c>
       <c r="D8">
-        <v>12911.99223711651</v>
+        <v>12929.71872947799</v>
       </c>
       <c r="E8">
         <v>-1382.862</v>
@@ -1949,37 +1949,37 @@
         <v>824.2</v>
       </c>
       <c r="M8">
-        <v>45.21878460000001</v>
+        <v>43.9942914</v>
       </c>
       <c r="N8">
-        <v>778.9812154</v>
+        <v>780.2057086000001</v>
       </c>
       <c r="O8">
-        <v>233.69436462</v>
+        <v>234.06171258</v>
       </c>
       <c r="P8">
-        <v>545.28685078</v>
+        <v>546.14399602</v>
       </c>
       <c r="Q8">
-        <v>697.8868507799999</v>
+        <v>698.7439960199999</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09192963814320571</v>
+        <v>0.09189998088729025</v>
       </c>
       <c r="T8">
         <v>1.064664685618712</v>
       </c>
       <c r="U8">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.3</v>
       </c>
       <c r="W8">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.2269383684408</v>
+        <v>18.73424878028607</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08835668981432432</v>
+        <v>0.08826029716022173</v>
       </c>
       <c r="C9">
-        <v>13154.83095859922</v>
+        <v>13175.76860639554</v>
       </c>
       <c r="D9">
-        <v>12981.34195859923</v>
+        <v>13002.27960639554</v>
       </c>
       <c r="E9">
         <v>-1237.089</v>
@@ -2031,37 +2031,37 @@
         <v>824.2</v>
       </c>
       <c r="M9">
-        <v>52.75524870000001</v>
+        <v>51.32667330000001</v>
       </c>
       <c r="N9">
-        <v>771.4447513</v>
+        <v>772.8733267</v>
       </c>
       <c r="O9">
-        <v>231.43342539</v>
+        <v>231.86199801</v>
       </c>
       <c r="P9">
-        <v>540.01132591</v>
+        <v>541.01132869</v>
       </c>
       <c r="Q9">
-        <v>692.6113259099999</v>
+        <v>693.6113286899999</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09228321485411217</v>
+        <v>0.09225333027980831</v>
       </c>
       <c r="T9">
         <v>1.072825179672247</v>
       </c>
       <c r="U9">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.3</v>
       </c>
       <c r="W9">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.62309003009211</v>
+        <v>16.05792752595949</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08812811977403529</v>
+        <v>0.08802201228639062</v>
       </c>
       <c r="C10">
-        <v>13079.1566511545</v>
+        <v>13103.37549493594</v>
       </c>
       <c r="D10">
-        <v>13051.4406511545</v>
+        <v>13075.65949493594</v>
       </c>
       <c r="E10">
         <v>-1091.316</v>
@@ -2113,37 +2113,37 @@
         <v>824.2</v>
       </c>
       <c r="M10">
-        <v>60.29171280000001</v>
+        <v>58.6590552</v>
       </c>
       <c r="N10">
-        <v>763.9082872</v>
+        <v>765.5409448</v>
       </c>
       <c r="O10">
-        <v>229.17248616</v>
+        <v>229.66228344</v>
       </c>
       <c r="P10">
-        <v>534.7358010400001</v>
+        <v>535.87866136</v>
       </c>
       <c r="Q10">
-        <v>687.33580104</v>
+        <v>688.4786613599999</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09264447801525574</v>
+        <v>0.09261436118085936</v>
       </c>
       <c r="T10">
         <v>1.081163075770424</v>
       </c>
       <c r="U10">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.3</v>
       </c>
       <c r="W10">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>13.6702037763306</v>
+        <v>14.05068658521455</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08789954973374622</v>
+        <v>0.08778372741255949</v>
       </c>
       <c r="C11">
-        <v>13004.24351389249</v>
+        <v>13031.81534036513</v>
       </c>
       <c r="D11">
-        <v>13122.30051389249</v>
+        <v>13149.87234036513</v>
       </c>
       <c r="E11">
         <v>-945.5430000000001</v>
@@ -2195,37 +2195,37 @@
         <v>824.2</v>
       </c>
       <c r="M11">
-        <v>67.8281769</v>
+        <v>65.9914371</v>
       </c>
       <c r="N11">
-        <v>756.3718231</v>
+        <v>758.2085629000001</v>
       </c>
       <c r="O11">
-        <v>226.91154693</v>
+        <v>227.46256887</v>
       </c>
       <c r="P11">
-        <v>529.46027617</v>
+        <v>530.74599403</v>
       </c>
       <c r="Q11">
-        <v>682.06027617</v>
+        <v>683.3459940299999</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09301368102609475</v>
+        <v>0.09298332682698844</v>
       </c>
       <c r="T11">
         <v>1.089684222332296</v>
       </c>
       <c r="U11">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.3</v>
       </c>
       <c r="W11">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.1512922456272</v>
+        <v>12.48949918685738</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08767097969345719</v>
+        <v>0.08754544253872835</v>
       </c>
       <c r="C12">
-        <v>12930.10401229888</v>
+        <v>12961.10240634988</v>
       </c>
       <c r="D12">
-        <v>13193.93401229888</v>
+        <v>13224.93240634988</v>
       </c>
       <c r="E12">
         <v>-799.77</v>
@@ -2277,37 +2277,37 @@
         <v>824.2</v>
       </c>
       <c r="M12">
-        <v>75.36464100000002</v>
+        <v>73.323819</v>
       </c>
       <c r="N12">
-        <v>748.835359</v>
+        <v>750.8761810000001</v>
       </c>
       <c r="O12">
-        <v>224.6506077</v>
+        <v>225.2628543</v>
       </c>
       <c r="P12">
-        <v>524.1847513</v>
+        <v>525.6133267</v>
       </c>
       <c r="Q12">
-        <v>676.7847512999999</v>
+        <v>678.2133266999999</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09339108854828576</v>
+        <v>0.09336049170969818</v>
       </c>
       <c r="T12">
         <v>1.098394727706655</v>
       </c>
       <c r="U12">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.3</v>
       </c>
       <c r="W12">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>10.93616302106448</v>
+        <v>11.24054926817164</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08744240965316814</v>
+        <v>0.08730715766489726</v>
       </c>
       <c r="C13">
-        <v>12856.7508855454</v>
+        <v>12891.25128409717</v>
       </c>
       <c r="D13">
-        <v>13266.3538855454</v>
+        <v>13300.85428409717</v>
       </c>
       <c r="E13">
         <v>-653.9970000000001</v>
@@ -2359,37 +2359,37 @@
         <v>824.2</v>
       </c>
       <c r="M13">
-        <v>82.90110510000001</v>
+        <v>80.6562009</v>
       </c>
       <c r="N13">
-        <v>741.2988949000001</v>
+        <v>743.5437991</v>
       </c>
       <c r="O13">
-        <v>222.38966847</v>
+        <v>223.06313973</v>
       </c>
       <c r="P13">
-        <v>518.90922643</v>
+        <v>520.48065937</v>
       </c>
       <c r="Q13">
-        <v>671.5092264299999</v>
+        <v>673.0806593699999</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09377697713839117</v>
+        <v>0.09374613220774972</v>
       </c>
       <c r="T13">
         <v>1.10730097477482</v>
       </c>
       <c r="U13">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.3</v>
       </c>
       <c r="W13">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.941966382785891</v>
+        <v>10.21868115288331</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.0872138396128791</v>
+        <v>0.08706887279106613</v>
       </c>
       <c r="C14">
-        <v>12784.19715404242</v>
+        <v>12822.27690181028</v>
       </c>
       <c r="D14">
-        <v>13339.57315404242</v>
+        <v>13377.65290181028</v>
       </c>
       <c r="E14">
         <v>-508.2240000000002</v>
@@ -2441,37 +2441,37 @@
         <v>824.2</v>
       </c>
       <c r="M14">
-        <v>90.43756920000001</v>
+        <v>87.9885828</v>
       </c>
       <c r="N14">
-        <v>733.7624308000001</v>
+        <v>736.2114172</v>
       </c>
       <c r="O14">
-        <v>220.12872924</v>
+        <v>220.86342516</v>
       </c>
       <c r="P14">
-        <v>513.6337015600001</v>
+        <v>515.34799204</v>
       </c>
       <c r="Q14">
-        <v>666.23370156</v>
+        <v>667.9479920399999</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09417163592372625</v>
+        <v>0.09414053726257515</v>
       </c>
       <c r="T14">
         <v>1.116409636549079</v>
       </c>
       <c r="U14">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.03619000000000001</v>
+        <v>0.03521</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.113469184220399</v>
+        <v>9.367124390143037</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08708536957259007</v>
+        <v>0.08696708791723501</v>
       </c>
       <c r="C15">
-        <v>12679.93366499702</v>
+        <v>12709.57990455074</v>
       </c>
       <c r="D15">
-        <v>13381.08266499702</v>
+        <v>13410.72890455075</v>
       </c>
       <c r="E15">
         <v>-362.451</v>
@@ -2523,37 +2523,37 @@
         <v>824.2</v>
       </c>
       <c r="M15">
-        <v>100.0585872</v>
+        <v>98.1635382</v>
       </c>
       <c r="N15">
-        <v>724.1414128</v>
+        <v>726.0364618000001</v>
       </c>
       <c r="O15">
-        <v>217.24242384</v>
+        <v>217.81093854</v>
       </c>
       <c r="P15">
-        <v>506.89898896</v>
+        <v>508.22552326</v>
       </c>
       <c r="Q15">
-        <v>659.4989889599999</v>
+        <v>660.82552326</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09457536732481617</v>
+        <v>0.09454400910027012</v>
       </c>
       <c r="T15">
         <v>1.125727692846885</v>
       </c>
       <c r="U15">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.03696</v>
+        <v>0.03626</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.237174070353053</v>
+        <v>8.396192874800025</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08686449953230102</v>
+        <v>0.08673930304340388</v>
       </c>
       <c r="C16">
-        <v>12606.13232667536</v>
+        <v>12638.42373884975</v>
       </c>
       <c r="D16">
-        <v>13453.05432667536</v>
+        <v>13485.34573884976</v>
       </c>
       <c r="E16">
         <v>-216.6779999999999</v>
@@ -2605,37 +2605,37 @@
         <v>824.2</v>
       </c>
       <c r="M16">
-        <v>107.7554016</v>
+        <v>105.7145796</v>
       </c>
       <c r="N16">
-        <v>716.4445984</v>
+        <v>718.4854204000001</v>
       </c>
       <c r="O16">
-        <v>214.93337952</v>
+        <v>215.54562612</v>
       </c>
       <c r="P16">
-        <v>501.51121888</v>
+        <v>502.9397942800001</v>
       </c>
       <c r="Q16">
-        <v>654.1112188799999</v>
+        <v>655.53979428</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.094988487828257</v>
+        <v>0.094956864003958</v>
       </c>
       <c r="T16">
         <v>1.13526244812836</v>
       </c>
       <c r="U16">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V16">
         <v>0.3</v>
       </c>
       <c r="W16">
-        <v>0.03696</v>
+        <v>0.03626</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.648804493899264</v>
+        <v>7.796464812314308</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08664362949201196</v>
+        <v>0.08651151816957277</v>
       </c>
       <c r="C17">
-        <v>12533.10939046988</v>
+        <v>12568.10254992932</v>
       </c>
       <c r="D17">
-        <v>13525.80439046988</v>
+        <v>13560.79754992932</v>
       </c>
       <c r="E17">
         <v>-70.9050000000002</v>
@@ -2687,37 +2687,37 @@
         <v>824.2</v>
       </c>
       <c r="M17">
-        <v>115.452216</v>
+        <v>113.265621</v>
       </c>
       <c r="N17">
-        <v>708.747784</v>
+        <v>710.934379</v>
       </c>
       <c r="O17">
-        <v>212.6243352</v>
+        <v>213.2803137</v>
       </c>
       <c r="P17">
-        <v>496.1234488</v>
+        <v>497.6540653000001</v>
       </c>
       <c r="Q17">
-        <v>648.7234487999999</v>
+        <v>650.2540653</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09541132881413172</v>
+        <v>0.09537943314067385</v>
       </c>
       <c r="T17">
         <v>1.145021550592929</v>
       </c>
       <c r="U17">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.03696</v>
+        <v>0.03626</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.13888419430598</v>
+        <v>7.276700491493355</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08666915945172292</v>
+        <v>0.08628373329574165</v>
       </c>
       <c r="C18">
-        <v>12378.8871528105</v>
+        <v>12498.63043197482</v>
       </c>
       <c r="D18">
-        <v>13517.3551528105</v>
+        <v>13637.09843197482</v>
       </c>
       <c r="E18">
         <v>74.86799999999994</v>
@@ -2769,45 +2769,45 @@
         <v>824.2</v>
       </c>
       <c r="M18">
-        <v>128.28024</v>
+        <v>120.8166624</v>
       </c>
       <c r="N18">
-        <v>695.91976</v>
+        <v>703.3833376</v>
       </c>
       <c r="O18">
-        <v>208.775928</v>
+        <v>211.01500128</v>
       </c>
       <c r="P18">
-        <v>487.143832</v>
+        <v>492.36833632</v>
       </c>
       <c r="Q18">
-        <v>639.7438319999999</v>
+        <v>644.9683363199999</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09584423744252729</v>
+        <v>0.0958120634473115</v>
       </c>
       <c r="T18">
         <v>1.155013012639988</v>
       </c>
       <c r="U18">
-        <v>0.05500000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.0385</v>
+        <v>0.03626</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.424995774875382</v>
+        <v>6.82190671077502</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08646368941143388</v>
+        <v>0.08625824842191053</v>
       </c>
       <c r="C19">
-        <v>12301.41615757321</v>
+        <v>12361.44751549344</v>
       </c>
       <c r="D19">
-        <v>13585.65715757321</v>
+        <v>13645.68851549344</v>
       </c>
       <c r="E19">
         <v>220.6410000000001</v>
@@ -2851,37 +2851,37 @@
         <v>824.2</v>
       </c>
       <c r="M19">
-        <v>136.297755</v>
+        <v>132.5805435</v>
       </c>
       <c r="N19">
-        <v>687.902245</v>
+        <v>691.6194565000001</v>
       </c>
       <c r="O19">
-        <v>206.3706735</v>
+        <v>207.48583695</v>
       </c>
       <c r="P19">
-        <v>481.5315715</v>
+        <v>484.13361955</v>
       </c>
       <c r="Q19">
-        <v>634.1315714999999</v>
+        <v>636.73361955</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09628757760413723</v>
+        <v>0.09625511858061511</v>
       </c>
       <c r="T19">
         <v>1.165245232808663</v>
       </c>
       <c r="U19">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.0385</v>
+        <v>0.03745</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.047054846941536</v>
+        <v>6.216598440781019</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08625821937114486</v>
+        <v>0.08604236354807941</v>
       </c>
       <c r="C20">
-        <v>12224.63891583711</v>
+        <v>12288.8784101898</v>
       </c>
       <c r="D20">
-        <v>13654.65291583711</v>
+        <v>13718.8924101898</v>
       </c>
       <c r="E20">
         <v>366.4139999999998</v>
@@ -2933,37 +2933,37 @@
         <v>824.2</v>
       </c>
       <c r="M20">
-        <v>144.31527</v>
+        <v>140.379399</v>
       </c>
       <c r="N20">
-        <v>679.88473</v>
+        <v>683.820601</v>
       </c>
       <c r="O20">
-        <v>203.965419</v>
+        <v>205.1461803</v>
       </c>
       <c r="P20">
-        <v>475.919311</v>
+        <v>478.6744207</v>
       </c>
       <c r="Q20">
-        <v>628.5193109999999</v>
+        <v>631.2744207</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09674173094042054</v>
+        <v>0.0967089799366822</v>
       </c>
       <c r="T20">
         <v>1.175727019322915</v>
       </c>
       <c r="U20">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.0385</v>
+        <v>0.03745</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.711107355444784</v>
+        <v>5.871231860737629</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08625224933085579</v>
+        <v>0.08593287867424829</v>
       </c>
       <c r="C21">
-        <v>12080.88110236911</v>
+        <v>12180.53136253237</v>
       </c>
       <c r="D21">
-        <v>13656.66810236911</v>
+        <v>13756.31836253237</v>
       </c>
       <c r="E21">
         <v>512.1869999999999</v>
@@ -3015,37 +3015,37 @@
         <v>824.2</v>
       </c>
       <c r="M21">
-        <v>156.4873155</v>
+        <v>150.3940041</v>
       </c>
       <c r="N21">
-        <v>667.7126845</v>
+        <v>673.8059959</v>
       </c>
       <c r="O21">
-        <v>200.31380535</v>
+        <v>202.14179877</v>
       </c>
       <c r="P21">
-        <v>467.39887915</v>
+        <v>471.66419713</v>
       </c>
       <c r="Q21">
-        <v>619.99887915</v>
+        <v>624.26419713</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09720709793932814</v>
+        <v>0.09717404774598554</v>
       </c>
       <c r="T21">
         <v>1.186467615380728</v>
       </c>
       <c r="U21">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V21">
         <v>0.3</v>
       </c>
       <c r="W21">
-        <v>0.03955</v>
+        <v>0.03801</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.266880560680331</v>
+        <v>5.480271669952831</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08605727929056677</v>
+        <v>0.08572259380041719</v>
       </c>
       <c r="C22">
-        <v>12001.24871537265</v>
+        <v>12107.21722343973</v>
       </c>
       <c r="D22">
-        <v>13722.80871537265</v>
+        <v>13828.77722343973</v>
       </c>
       <c r="E22">
         <v>657.96</v>
@@ -3097,37 +3097,37 @@
         <v>824.2</v>
       </c>
       <c r="M22">
-        <v>164.72349</v>
+        <v>158.309478</v>
       </c>
       <c r="N22">
-        <v>659.47651</v>
+        <v>665.890522</v>
       </c>
       <c r="O22">
-        <v>197.842953</v>
+        <v>199.7671566</v>
       </c>
       <c r="P22">
-        <v>461.633557</v>
+        <v>466.1233654</v>
       </c>
       <c r="Q22">
-        <v>614.2335569999999</v>
+        <v>618.7233653999999</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09768409911320845</v>
+        <v>0.09765074225052148</v>
       </c>
       <c r="T22">
         <v>1.197476726339988</v>
       </c>
       <c r="U22">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.03955</v>
+        <v>0.03801</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.003536532646314</v>
+        <v>5.20625808645519</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08586230925027774</v>
+        <v>0.08551230892658607</v>
       </c>
       <c r="C23">
-        <v>11922.26009745607</v>
+        <v>12034.67045360039</v>
       </c>
       <c r="D23">
-        <v>13789.59309745607</v>
+        <v>13902.0034536004</v>
       </c>
       <c r="E23">
         <v>803.7329999999997</v>
@@ -3179,37 +3179,37 @@
         <v>824.2</v>
       </c>
       <c r="M23">
-        <v>172.9596645</v>
+        <v>166.2249519</v>
       </c>
       <c r="N23">
-        <v>651.2403355</v>
+        <v>657.9750481000001</v>
       </c>
       <c r="O23">
-        <v>195.37210065</v>
+        <v>197.39251443</v>
       </c>
       <c r="P23">
-        <v>455.86823485</v>
+        <v>460.5825336700001</v>
       </c>
       <c r="Q23">
-        <v>608.4682348499999</v>
+        <v>613.18253367</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09817317626617433</v>
+        <v>0.0981395049703621</v>
       </c>
       <c r="T23">
         <v>1.208764548969101</v>
       </c>
       <c r="U23">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.03955</v>
+        <v>0.03801</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.765272888234586</v>
+        <v>4.958341034719229</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08566733920998869</v>
+        <v>0.08530202405275494</v>
       </c>
       <c r="C24">
-        <v>11843.92469362018</v>
+        <v>11962.90330804309</v>
       </c>
       <c r="D24">
-        <v>13857.03069362018</v>
+        <v>13976.00930804309</v>
       </c>
       <c r="E24">
         <v>949.5059999999999</v>
@@ -3261,37 +3261,37 @@
         <v>824.2</v>
       </c>
       <c r="M24">
-        <v>181.195839</v>
+        <v>174.1404258</v>
       </c>
       <c r="N24">
-        <v>643.0041610000001</v>
+        <v>650.0595742</v>
       </c>
       <c r="O24">
-        <v>192.9012483</v>
+        <v>195.01787226</v>
       </c>
       <c r="P24">
-        <v>450.1029127</v>
+        <v>455.0417019400001</v>
       </c>
       <c r="Q24">
-        <v>602.7029127</v>
+        <v>607.64170194</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09867479385895984</v>
+        <v>0.09864080006763454</v>
       </c>
       <c r="T24">
         <v>1.22034180294768</v>
       </c>
       <c r="U24">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.03955</v>
+        <v>0.03801</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.548669575133014</v>
+        <v>4.732961896777445</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08547236916969964</v>
+        <v>0.08509173917892382</v>
       </c>
       <c r="C25">
-        <v>11766.25213453575</v>
+        <v>11891.92830414658</v>
       </c>
       <c r="D25">
-        <v>13925.13113453575</v>
+        <v>14050.80730414658</v>
       </c>
       <c r="E25">
         <v>1095.279</v>
@@ -3343,37 +3343,37 @@
         <v>824.2</v>
       </c>
       <c r="M25">
-        <v>189.4320135</v>
+        <v>182.0558997</v>
       </c>
       <c r="N25">
-        <v>634.7679865</v>
+        <v>642.1441003</v>
       </c>
       <c r="O25">
-        <v>190.43039595</v>
+        <v>192.64323009</v>
       </c>
       <c r="P25">
-        <v>444.33759055</v>
+        <v>449.50087021</v>
       </c>
       <c r="Q25">
-        <v>596.9375905499999</v>
+        <v>602.1008702099999</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.0991894404801294</v>
+        <v>0.09915511581678418</v>
       </c>
       <c r="T25">
         <v>1.232219764821805</v>
       </c>
       <c r="U25">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.03955</v>
+        <v>0.03801</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.350901332735926</v>
+        <v>4.527180944743643</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08551259912941059</v>
+        <v>0.08488145430509272</v>
       </c>
       <c r="C26">
-        <v>11606.37259210858</v>
+        <v>11821.75822869774</v>
       </c>
       <c r="D26">
-        <v>13911.02459210858</v>
+        <v>14126.41022869774</v>
       </c>
       <c r="E26">
         <v>1241.052</v>
@@ -3425,45 +3425,45 @@
         <v>824.2</v>
       </c>
       <c r="M26">
-        <v>202.5661608</v>
+        <v>189.9713736</v>
       </c>
       <c r="N26">
-        <v>621.6338392</v>
+        <v>634.2286264000001</v>
       </c>
       <c r="O26">
-        <v>186.49015176</v>
+        <v>190.26858792</v>
       </c>
       <c r="P26">
-        <v>435.14368744</v>
+        <v>443.96003848</v>
       </c>
       <c r="Q26">
-        <v>587.7436874399999</v>
+        <v>596.56003848</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09971763043343498</v>
+        <v>0.09968296619091147</v>
       </c>
       <c r="T26">
         <v>1.244410304639987</v>
       </c>
       <c r="U26">
-        <v>0.05790000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.04053</v>
+        <v>0.03801</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.068794100381647</v>
+        <v>4.338548405379325</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08532742908912155</v>
+        <v>0.08484616943126159</v>
       </c>
       <c r="C27">
-        <v>11525.76712370733</v>
+        <v>11688.75084975268</v>
       </c>
       <c r="D27">
-        <v>13976.19212370733</v>
+        <v>14139.17584975268</v>
       </c>
       <c r="E27">
         <v>1386.825</v>
@@ -3507,37 +3507,37 @@
         <v>824.2</v>
       </c>
       <c r="M27">
-        <v>211.0064175</v>
+        <v>201.5311725</v>
       </c>
       <c r="N27">
-        <v>613.1935825</v>
+        <v>622.6688275</v>
       </c>
       <c r="O27">
-        <v>183.95807475</v>
+        <v>186.80064825</v>
       </c>
       <c r="P27">
-        <v>429.23550775</v>
+        <v>435.86817925</v>
       </c>
       <c r="Q27">
-        <v>581.8355077499999</v>
+        <v>588.4681792499999</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1002599054521621</v>
+        <v>0.1002248925750154</v>
       </c>
       <c r="T27">
         <v>1.256925925519987</v>
       </c>
       <c r="U27">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.906042336366381</v>
+        <v>4.089689896484872</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08514225904883251</v>
+        <v>0.08464288455743046</v>
       </c>
       <c r="C28">
-        <v>11445.7750961579</v>
+        <v>11616.9754586183</v>
       </c>
       <c r="D28">
-        <v>14041.9730961579</v>
+        <v>14213.1734586183</v>
       </c>
       <c r="E28">
         <v>1532.598</v>
@@ -3589,37 +3589,37 @@
         <v>824.2</v>
       </c>
       <c r="M28">
-        <v>219.4466742</v>
+        <v>209.5924194</v>
       </c>
       <c r="N28">
-        <v>604.7533258000001</v>
+        <v>614.6075806</v>
       </c>
       <c r="O28">
-        <v>181.42599774</v>
+        <v>184.38227418</v>
       </c>
       <c r="P28">
-        <v>423.3273280600001</v>
+        <v>430.22530642</v>
       </c>
       <c r="Q28">
-        <v>575.92732806</v>
+        <v>582.8253064199999</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1008168365524764</v>
+        <v>0.1007814656181493</v>
       </c>
       <c r="T28">
         <v>1.269779806423771</v>
       </c>
       <c r="U28">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V28">
         <v>0.3</v>
       </c>
       <c r="W28">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.755809938813828</v>
+        <v>3.932394131235454</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08495708900854346</v>
+        <v>0.08443959968359935</v>
       </c>
       <c r="C29">
-        <v>11366.40521216547</v>
+        <v>11545.97867775448</v>
       </c>
       <c r="D29">
-        <v>14108.37621216547</v>
+        <v>14287.94967775448</v>
       </c>
       <c r="E29">
         <v>1678.371</v>
@@ -3671,37 +3671,37 @@
         <v>824.2</v>
       </c>
       <c r="M29">
-        <v>227.8869309</v>
+        <v>217.6536663</v>
       </c>
       <c r="N29">
-        <v>596.3130691</v>
+        <v>606.5463337</v>
       </c>
       <c r="O29">
-        <v>178.89392073</v>
+        <v>181.96390011</v>
       </c>
       <c r="P29">
-        <v>417.41914837</v>
+        <v>424.58243359</v>
       </c>
       <c r="Q29">
-        <v>570.0191483699999</v>
+        <v>577.1824335899998</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1013890260391006</v>
+        <v>0.1013532872378073</v>
       </c>
       <c r="T29">
         <v>1.282985848448206</v>
       </c>
       <c r="U29">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V29">
         <v>0.3</v>
       </c>
       <c r="W29">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.616705867005908</v>
+        <v>3.786749904152659</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08477191896825442</v>
+        <v>0.08423631480976822</v>
       </c>
       <c r="C30">
-        <v>11287.66633983436</v>
+        <v>11475.77286107897</v>
       </c>
       <c r="D30">
-        <v>14175.41033983436</v>
+        <v>14363.51686107898</v>
       </c>
       <c r="E30">
         <v>1824.144</v>
@@ -3753,37 +3753,37 @@
         <v>824.2</v>
       </c>
       <c r="M30">
-        <v>236.3271876</v>
+        <v>225.7149132</v>
       </c>
       <c r="N30">
-        <v>587.8728124</v>
+        <v>598.4850868</v>
       </c>
       <c r="O30">
-        <v>176.36184372</v>
+        <v>179.54552604</v>
       </c>
       <c r="P30">
-        <v>411.51096868</v>
+        <v>418.9395607599999</v>
       </c>
       <c r="Q30">
-        <v>564.1109686799999</v>
+        <v>571.5395607599999</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1019771096781311</v>
+        <v>0.1019409927913448</v>
       </c>
       <c r="T30">
         <v>1.29655872497332</v>
       </c>
       <c r="U30">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V30">
         <v>0.3</v>
       </c>
       <c r="W30">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.487537800327126</v>
+        <v>3.651508836147207</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08458674892796537</v>
+        <v>0.08403302993593711</v>
       </c>
       <c r="C31">
-        <v>11209.56751661612</v>
+        <v>11406.37062525246</v>
       </c>
       <c r="D31">
-        <v>14243.08451661612</v>
+        <v>14439.88762525246</v>
       </c>
       <c r="E31">
         <v>1969.916999999999</v>
@@ -3835,37 +3835,37 @@
         <v>824.2</v>
       </c>
       <c r="M31">
-        <v>244.7674443</v>
+        <v>233.7761601</v>
       </c>
       <c r="N31">
-        <v>579.4325557000001</v>
+        <v>590.4238399000001</v>
       </c>
       <c r="O31">
-        <v>173.82976671</v>
+        <v>177.12715197</v>
       </c>
       <c r="P31">
-        <v>405.60278899</v>
+        <v>413.2966879300001</v>
       </c>
       <c r="Q31">
-        <v>558.2027889899999</v>
+        <v>565.89668793</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1025817590534724</v>
+        <v>0.1025452534308973</v>
       </c>
       <c r="T31">
         <v>1.310513936048437</v>
       </c>
       <c r="U31">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.367277876177915</v>
+        <v>3.525594738349028</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08440157888767634</v>
+        <v>0.08382974506210598</v>
       </c>
       <c r="C32">
-        <v>11132.11795337129</v>
+        <v>11337.78485670094</v>
       </c>
       <c r="D32">
-        <v>14311.40795337129</v>
+        <v>14517.07485670093</v>
       </c>
       <c r="E32">
         <v>2115.69</v>
@@ -3917,37 +3917,37 @@
         <v>824.2</v>
       </c>
       <c r="M32">
-        <v>253.207701</v>
+        <v>241.837407</v>
       </c>
       <c r="N32">
-        <v>570.992299</v>
+        <v>582.3625930000001</v>
       </c>
       <c r="O32">
-        <v>171.2976897</v>
+        <v>174.7087779</v>
       </c>
       <c r="P32">
-        <v>399.6946093</v>
+        <v>407.6538151000001</v>
       </c>
       <c r="Q32">
-        <v>552.2946092999999</v>
+        <v>560.2538151</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1032036841252519</v>
+        <v>0.1031667786601514</v>
       </c>
       <c r="T32">
         <v>1.324867867439987</v>
       </c>
       <c r="U32">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V32">
         <v>0.3</v>
       </c>
       <c r="W32">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.255035280305317</v>
+        <v>3.408074913737394</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08421640884738728</v>
+        <v>0.08362646018827487</v>
       </c>
       <c r="C33">
-        <v>11055.32703854866</v>
+        <v>11270.02871886442</v>
       </c>
       <c r="D33">
-        <v>14380.39003854866</v>
+        <v>14595.09171886442</v>
       </c>
       <c r="E33">
         <v>2261.463</v>
@@ -3999,37 +3999,37 @@
         <v>824.2</v>
       </c>
       <c r="M33">
-        <v>261.6479577</v>
+        <v>249.8986539</v>
       </c>
       <c r="N33">
-        <v>562.5520423</v>
+        <v>574.3013461</v>
       </c>
       <c r="O33">
-        <v>168.76561269</v>
+        <v>172.29040383</v>
       </c>
       <c r="P33">
-        <v>393.78642961</v>
+        <v>402.01094227</v>
       </c>
       <c r="Q33">
-        <v>546.3864296099999</v>
+        <v>554.6109422699999</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1038436360107062</v>
+        <v>0.1038063191134418</v>
       </c>
       <c r="T33">
         <v>1.339637854813899</v>
       </c>
       <c r="U33">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.150034142230953</v>
+        <v>3.298137013294252</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08403123880709823</v>
+        <v>0.08342317531444375</v>
       </c>
       <c r="C34">
-        <v>10979.20434248586</v>
+        <v>11203.11565968084</v>
       </c>
       <c r="D34">
-        <v>14450.04034248587</v>
+        <v>14673.95165968084</v>
       </c>
       <c r="E34">
         <v>2407.236</v>
@@ -4081,37 +4081,37 @@
         <v>824.2</v>
       </c>
       <c r="M34">
-        <v>270.0882144</v>
+        <v>257.9599008</v>
       </c>
       <c r="N34">
-        <v>554.1117856000001</v>
+        <v>566.2400992</v>
       </c>
       <c r="O34">
-        <v>166.23353568</v>
+        <v>169.87202976</v>
       </c>
       <c r="P34">
-        <v>387.87824992</v>
+        <v>396.36806944</v>
       </c>
       <c r="Q34">
-        <v>540.4782499199999</v>
+        <v>548.9680694399999</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1045024100104386</v>
+        <v>0.1044646695800643</v>
       </c>
       <c r="T34">
         <v>1.354842253581162</v>
       </c>
       <c r="U34">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V34">
         <v>0.3</v>
       </c>
       <c r="W34">
-        <v>0.04053</v>
+        <v>0.03871</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.051595575286235</v>
+        <v>3.195070231628807</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.0844466687668092</v>
+        <v>0.08321989044061263</v>
       </c>
       <c r="C35">
-        <v>10678.10153350485</v>
+        <v>11137.0594193137</v>
       </c>
       <c r="D35">
-        <v>14294.71053350485</v>
+        <v>14753.6684193137</v>
       </c>
       <c r="E35">
         <v>2553.009</v>
@@ -4163,45 +4163,45 @@
         <v>824.2</v>
       </c>
       <c r="M35">
-        <v>291.0357945</v>
+        <v>266.0211477</v>
       </c>
       <c r="N35">
-        <v>533.1642055</v>
+        <v>558.1788523</v>
       </c>
       <c r="O35">
-        <v>159.94926165</v>
+        <v>167.45365569</v>
       </c>
       <c r="P35">
-        <v>373.21494385</v>
+        <v>390.72519661</v>
       </c>
       <c r="Q35">
-        <v>525.81494385</v>
+        <v>543.3251966099999</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1051808489056854</v>
+        <v>0.1051426722994219</v>
       </c>
       <c r="T35">
         <v>1.370500514998195</v>
       </c>
       <c r="U35">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.04235</v>
+        <v>0.03871</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.831954060551133</v>
+        <v>3.098249921579449</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08427969872652015</v>
+        <v>0.0830166055667815</v>
       </c>
       <c r="C36">
-        <v>10594.35574454574</v>
+        <v>11071.87403813307</v>
       </c>
       <c r="D36">
-        <v>14356.73774454574</v>
+        <v>14834.25603813307</v>
       </c>
       <c r="E36">
         <v>2698.782</v>
@@ -4245,45 +4245,45 @@
         <v>824.2</v>
       </c>
       <c r="M36">
-        <v>299.855061</v>
+        <v>274.0823946</v>
       </c>
       <c r="N36">
-        <v>524.3449390000001</v>
+        <v>550.1176054</v>
       </c>
       <c r="O36">
-        <v>157.3034817</v>
+        <v>165.03528162</v>
       </c>
       <c r="P36">
-        <v>367.0414573</v>
+        <v>385.08232378</v>
       </c>
       <c r="Q36">
-        <v>519.6414573</v>
+        <v>537.6823237799999</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1058798465553336</v>
+        <v>0.1058412205557296</v>
       </c>
       <c r="T36">
         <v>1.38663326918544</v>
       </c>
       <c r="U36">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V36">
         <v>0.3</v>
       </c>
       <c r="W36">
-        <v>0.04235</v>
+        <v>0.03871</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.748661294064335</v>
+        <v>3.007124923885935</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08411272868623113</v>
+        <v>0.0834258206929504</v>
       </c>
       <c r="C37">
-        <v>10511.15059501804</v>
+        <v>10764.76497038841</v>
       </c>
       <c r="D37">
-        <v>14419.30559501804</v>
+        <v>14672.91997038841</v>
       </c>
       <c r="E37">
         <v>2844.555</v>
@@ -4327,37 +4327,37 @@
         <v>824.2</v>
       </c>
       <c r="M37">
-        <v>308.6743275000001</v>
+        <v>294.898779</v>
       </c>
       <c r="N37">
-        <v>515.5256724999999</v>
+        <v>529.3012209999999</v>
       </c>
       <c r="O37">
-        <v>154.65770175</v>
+        <v>158.7903663</v>
       </c>
       <c r="P37">
-        <v>360.8679707499999</v>
+        <v>370.5108547</v>
       </c>
       <c r="Q37">
-        <v>513.4679707499998</v>
+        <v>523.1108546999999</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.106600351824971</v>
+        <v>0.1065612626045391</v>
       </c>
       <c r="T37">
         <v>1.403262415809216</v>
       </c>
       <c r="U37">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.04235</v>
+        <v>0.04046</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.670128114233925</v>
+        <v>2.794857282199869</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08394575864594207</v>
+        <v>0.08324003581911928</v>
       </c>
       <c r="C38">
-        <v>10428.49318431558</v>
+        <v>10691.80190568341</v>
       </c>
       <c r="D38">
-        <v>14482.42118431558</v>
+        <v>14745.72990568341</v>
       </c>
       <c r="E38">
         <v>2990.328</v>
@@ -4409,37 +4409,37 @@
         <v>824.2</v>
       </c>
       <c r="M38">
-        <v>317.493594</v>
+        <v>303.3244584</v>
       </c>
       <c r="N38">
-        <v>506.7064060000001</v>
+        <v>520.8755416000001</v>
       </c>
       <c r="O38">
-        <v>152.0119218</v>
+        <v>156.26266248</v>
       </c>
       <c r="P38">
-        <v>354.6944842</v>
+        <v>364.6128791200001</v>
       </c>
       <c r="Q38">
-        <v>507.2944841999999</v>
+        <v>517.21287912</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1073433728842845</v>
+        <v>0.1073038059673739</v>
       </c>
       <c r="T38">
         <v>1.420411223264985</v>
       </c>
       <c r="U38">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V38">
         <v>0.3</v>
       </c>
       <c r="W38">
-        <v>0.04235</v>
+        <v>0.04046</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.595957888838539</v>
+        <v>2.717222357694318</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08377878860565303</v>
+        <v>0.08305425094528816</v>
       </c>
       <c r="C39">
-        <v>10346.39073667932</v>
+        <v>10619.56503915979</v>
       </c>
       <c r="D39">
-        <v>14546.09173667933</v>
+        <v>14819.26603915979</v>
       </c>
       <c r="E39">
         <v>3136.101</v>
@@ -4491,37 +4491,37 @@
         <v>824.2</v>
       </c>
       <c r="M39">
-        <v>326.3128605</v>
+        <v>311.7501378</v>
       </c>
       <c r="N39">
-        <v>497.8871395</v>
+        <v>512.4498622000001</v>
       </c>
       <c r="O39">
-        <v>149.36614185</v>
+        <v>153.73495866</v>
       </c>
       <c r="P39">
-        <v>348.52099765</v>
+        <v>358.7149035400001</v>
       </c>
       <c r="Q39">
-        <v>501.1209976499999</v>
+        <v>511.31490354</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.108109981913735</v>
+        <v>0.108069922135378</v>
       </c>
       <c r="T39">
         <v>1.438104437306652</v>
       </c>
       <c r="U39">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V39">
         <v>0.3</v>
       </c>
       <c r="W39">
-        <v>0.04235</v>
+        <v>0.04046</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.525796864815876</v>
+        <v>2.643783915594471</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08433001856536398</v>
+        <v>0.08286846607145704</v>
       </c>
       <c r="C40">
-        <v>9992.513981204642</v>
+        <v>10548.0652897995</v>
       </c>
       <c r="D40">
-        <v>14337.98798120464</v>
+        <v>14893.5392897995</v>
       </c>
       <c r="E40">
         <v>3281.874</v>
@@ -4573,45 +4573,45 @@
         <v>824.2</v>
       </c>
       <c r="M40">
-        <v>350.0884368</v>
+        <v>320.1758172</v>
       </c>
       <c r="N40">
-        <v>474.1115632</v>
+        <v>504.0241828000001</v>
       </c>
       <c r="O40">
-        <v>142.23346896</v>
+        <v>151.20725484</v>
       </c>
       <c r="P40">
-        <v>331.87809424</v>
+        <v>352.81692796</v>
       </c>
       <c r="Q40">
-        <v>484.4780942399999</v>
+        <v>505.41692796</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1089013202667161</v>
+        <v>0.1088607517281565</v>
       </c>
       <c r="T40">
         <v>1.456368400188372</v>
       </c>
       <c r="U40">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.3</v>
       </c>
       <c r="W40">
-        <v>0.04424</v>
+        <v>0.04046</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.354262275937016</v>
+        <v>2.574210654657775</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08418194852507496</v>
+        <v>0.08268268119762592</v>
       </c>
       <c r="C41">
-        <v>9902.05413073517</v>
+        <v>10477.31379658823</v>
       </c>
       <c r="D41">
-        <v>14393.30113073517</v>
+        <v>14968.56079658823</v>
       </c>
       <c r="E41">
         <v>3427.647</v>
@@ -4655,45 +4655,45 @@
         <v>824.2</v>
       </c>
       <c r="M41">
-        <v>359.3012904</v>
+        <v>328.6014966</v>
       </c>
       <c r="N41">
-        <v>464.8987096</v>
+        <v>495.5985034</v>
       </c>
       <c r="O41">
-        <v>139.46961288</v>
+        <v>148.67955102</v>
       </c>
       <c r="P41">
-        <v>325.42909672</v>
+        <v>346.9189523800001</v>
       </c>
       <c r="Q41">
-        <v>478.0290967199999</v>
+        <v>499.51895238</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1097186041394671</v>
+        <v>0.1096775101600425</v>
       </c>
       <c r="T41">
         <v>1.475231181525231</v>
       </c>
       <c r="U41">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V41">
         <v>0.3</v>
       </c>
       <c r="W41">
-        <v>0.04424</v>
+        <v>0.04046</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.293896576554015</v>
+        <v>2.508205253256294</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.0853498784847859</v>
+        <v>0.08347689632379481</v>
       </c>
       <c r="C42">
-        <v>9331.238924443853</v>
+        <v>10016.00903676753</v>
       </c>
       <c r="D42">
-        <v>13968.25892444385</v>
+        <v>14653.02903676754</v>
       </c>
       <c r="E42">
         <v>3573.42</v>
@@ -4737,45 +4737,45 @@
         <v>824.2</v>
       </c>
       <c r="M42">
-        <v>395.9194680000001</v>
+        <v>357.435396</v>
       </c>
       <c r="N42">
-        <v>428.2805319999999</v>
+        <v>466.764604</v>
       </c>
       <c r="O42">
-        <v>128.4841596</v>
+        <v>140.0293812</v>
       </c>
       <c r="P42">
-        <v>299.7963724</v>
+        <v>326.7352228</v>
       </c>
       <c r="Q42">
-        <v>452.3963723999999</v>
+        <v>479.3352227999999</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1105631308079765</v>
+        <v>0.1105214938729913</v>
       </c>
       <c r="T42">
         <v>1.494722722239985</v>
       </c>
       <c r="U42">
-        <v>0.06790000000000002</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V42">
         <v>0.3</v>
       </c>
       <c r="W42">
-        <v>0.04753000000000001</v>
+        <v>0.04291</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.08173648081382</v>
+        <v>2.305871240575178</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08523470844449685</v>
+        <v>0.08411921144996368</v>
       </c>
       <c r="C43">
-        <v>9226.260569733557</v>
+        <v>9624.618712235759</v>
       </c>
       <c r="D43">
-        <v>14009.05356973356</v>
+        <v>14407.41171223576</v>
       </c>
       <c r="E43">
         <v>3719.193</v>
@@ -4819,37 +4819,37 @@
         <v>824.2</v>
       </c>
       <c r="M43">
-        <v>405.8174547000001</v>
+        <v>383.1060213000001</v>
       </c>
       <c r="N43">
-        <v>418.3825452999999</v>
+        <v>441.0939787</v>
       </c>
       <c r="O43">
-        <v>125.51476359</v>
+        <v>132.32819361</v>
       </c>
       <c r="P43">
-        <v>292.86778171</v>
+        <v>308.76578509</v>
       </c>
       <c r="Q43">
-        <v>445.4677817099999</v>
+        <v>461.3657850899999</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1114362854991472</v>
+        <v>0.1113940872033283</v>
       </c>
       <c r="T43">
         <v>1.514874993148459</v>
       </c>
       <c r="U43">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V43">
         <v>0.3</v>
       </c>
       <c r="W43">
-        <v>0.04753000000000001</v>
+        <v>0.04487</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.030962420306166</v>
+        <v>2.151362688592647</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08923553840420781</v>
+        <v>0.08397752657613257</v>
       </c>
       <c r="C44">
-        <v>7790.11928403605</v>
+        <v>9532.314663573143</v>
       </c>
       <c r="D44">
-        <v>12718.68528403605</v>
+        <v>14460.88066357314</v>
       </c>
       <c r="E44">
         <v>3864.965999999999</v>
@@ -4901,45 +4901,45 @@
         <v>824.2</v>
       </c>
       <c r="M44">
-        <v>501.4299654</v>
+        <v>392.4500706</v>
       </c>
       <c r="N44">
-        <v>322.7700346000001</v>
+        <v>431.7499294</v>
       </c>
       <c r="O44">
-        <v>96.83101038000002</v>
+        <v>129.52497882</v>
       </c>
       <c r="P44">
-        <v>225.9390242200001</v>
+        <v>302.22495058</v>
       </c>
       <c r="Q44">
-        <v>378.53902422</v>
+        <v>454.8249505799999</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1123395489727721</v>
+        <v>0.1122967699588492</v>
       </c>
       <c r="T44">
         <v>1.535722169950329</v>
       </c>
       <c r="U44">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V44">
         <v>0.3</v>
       </c>
       <c r="W44">
-        <v>0.05733</v>
+        <v>0.04487</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>1.643699134220111</v>
+        <v>2.10013976743568</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08921836836391879</v>
+        <v>0.08383584170230145</v>
       </c>
       <c r="C45">
-        <v>7649.375960345391</v>
+        <v>9440.408962431455</v>
       </c>
       <c r="D45">
-        <v>12723.71496034539</v>
+        <v>14514.74796243145</v>
       </c>
       <c r="E45">
         <v>4010.739</v>
@@ -4983,45 +4983,45 @@
         <v>824.2</v>
       </c>
       <c r="M45">
-        <v>513.3687741</v>
+        <v>401.7941199</v>
       </c>
       <c r="N45">
-        <v>310.8312259</v>
+        <v>422.4058801</v>
       </c>
       <c r="O45">
-        <v>93.24936777000001</v>
+        <v>126.72176403</v>
       </c>
       <c r="P45">
-        <v>217.5818581300001</v>
+        <v>295.6841160700001</v>
       </c>
       <c r="Q45">
-        <v>370.18185813</v>
+        <v>448.28411607</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1132745059016119</v>
+        <v>0.1132311257935113</v>
       </c>
       <c r="T45">
         <v>1.557300826639984</v>
       </c>
       <c r="U45">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.3</v>
       </c>
       <c r="W45">
-        <v>0.05733</v>
+        <v>0.04487</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>1.605473572959178</v>
+        <v>2.051299307727873</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08920119832362973</v>
+        <v>0.08369415682847034</v>
       </c>
       <c r="C46">
-        <v>7508.636616256609</v>
+        <v>9348.906077031352</v>
       </c>
       <c r="D46">
-        <v>12728.74861625661</v>
+        <v>14569.01807703135</v>
       </c>
       <c r="E46">
         <v>4156.512</v>
@@ -5065,45 +5065,45 @@
         <v>824.2</v>
       </c>
       <c r="M46">
-        <v>525.3075828</v>
+        <v>411.1381692</v>
       </c>
       <c r="N46">
-        <v>298.8924172000001</v>
+        <v>413.0618308000001</v>
       </c>
       <c r="O46">
-        <v>89.66772516000002</v>
+        <v>123.91854924</v>
       </c>
       <c r="P46">
-        <v>209.22469204</v>
+        <v>289.14328156</v>
       </c>
       <c r="Q46">
-        <v>361.8246920399999</v>
+        <v>441.74328156</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1142428541493388</v>
+        <v>0.1141988514794113</v>
       </c>
       <c r="T46">
         <v>1.579650149639984</v>
       </c>
       <c r="U46">
-        <v>0.0819</v>
+        <v>0.0641</v>
       </c>
       <c r="V46">
         <v>0.3</v>
       </c>
       <c r="W46">
-        <v>0.05733</v>
+        <v>0.04487</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.568985537210106</v>
+        <v>2.004678868915876</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.0891840282833407</v>
+        <v>0.08723797195463923</v>
       </c>
       <c r="C47">
-        <v>7367.901256494686</v>
+        <v>7957.176670397133</v>
       </c>
       <c r="D47">
-        <v>12733.78625649469</v>
+        <v>13323.06167039713</v>
       </c>
       <c r="E47">
         <v>4302.285</v>
@@ -5147,37 +5147,37 @@
         <v>824.2</v>
       </c>
       <c r="M47">
-        <v>537.2463915</v>
+        <v>497.231703</v>
       </c>
       <c r="N47">
-        <v>286.9536085000001</v>
+        <v>326.968297</v>
       </c>
       <c r="O47">
-        <v>86.08608255000003</v>
+        <v>98.0904891</v>
       </c>
       <c r="P47">
-        <v>200.8675259500001</v>
+        <v>228.8778079</v>
       </c>
       <c r="Q47">
-        <v>353.46752595</v>
+        <v>381.4778078999999</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1152464150606194</v>
+        <v>0.1152017671902531</v>
       </c>
       <c r="T47">
         <v>1.602812175294529</v>
       </c>
       <c r="U47">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V47">
         <v>0.3</v>
       </c>
       <c r="W47">
-        <v>0.05733</v>
+        <v>0.05306</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.53411919193877</v>
+        <v>1.657577332714845</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08916685824305164</v>
+        <v>0.08717818708080809</v>
       </c>
       <c r="C48">
-        <v>7227.169885792132</v>
+        <v>7830.653367331744</v>
       </c>
       <c r="D48">
-        <v>12738.82788579213</v>
+        <v>13342.31136733174</v>
       </c>
       <c r="E48">
         <v>4448.058</v>
@@ -5229,37 +5229,37 @@
         <v>824.2</v>
       </c>
       <c r="M48">
-        <v>549.1852002000001</v>
+        <v>508.2812964</v>
       </c>
       <c r="N48">
-        <v>275.0147998</v>
+        <v>315.9187036</v>
       </c>
       <c r="O48">
-        <v>82.50443994</v>
+        <v>94.77561108</v>
       </c>
       <c r="P48">
-        <v>192.51035986</v>
+        <v>221.14309252</v>
       </c>
       <c r="Q48">
-        <v>345.1103598599999</v>
+        <v>373.7430925199999</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1162871448945401</v>
+        <v>0.1162418279274224</v>
       </c>
       <c r="T48">
         <v>1.626832053751094</v>
       </c>
       <c r="U48">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V48">
         <v>0.3</v>
       </c>
       <c r="W48">
-        <v>0.05733</v>
+        <v>0.05306</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.50076877472271</v>
+        <v>1.621543042873218</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1072698798277881</v>
+        <v>0.08711840220697699</v>
       </c>
       <c r="C49">
-        <v>3329.782650872361</v>
+        <v>7704.185770229837</v>
       </c>
       <c r="D49">
-        <v>8987.213650872362</v>
+        <v>13361.61677022984</v>
       </c>
       <c r="E49">
         <v>4593.831</v>
@@ -5311,45 +5311,45 @@
         <v>824.2</v>
       </c>
       <c r="M49">
-        <v>896.8392279000001</v>
+        <v>519.3308898</v>
       </c>
       <c r="N49">
-        <v>-72.63922790000004</v>
+        <v>304.8691102</v>
       </c>
       <c r="O49">
-        <v>-21.79176837000001</v>
+        <v>91.46073306000001</v>
       </c>
       <c r="P49">
-        <v>-50.84745953000002</v>
+        <v>213.40837714</v>
       </c>
       <c r="Q49">
-        <v>101.7525404699999</v>
+        <v>366.0083771399999</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.118318620138602</v>
+        <v>0.1173211362395792</v>
       </c>
       <c r="T49">
-        <v>1.673718178141384</v>
+        <v>1.651758342715455</v>
       </c>
       <c r="U49">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V49">
-        <v>0.2757015887663314</v>
+        <v>0.3</v>
       </c>
       <c r="W49">
-        <v>0.09481066203048723</v>
+        <v>0.05306</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.9190052958877715</v>
+        <v>1.587042127067405</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1081208798277881</v>
+        <v>0.08705861733314586</v>
       </c>
       <c r="C50">
-        <v>3061.28803914245</v>
+        <v>7577.774121249868</v>
       </c>
       <c r="D50">
-        <v>8864.492039142449</v>
+        <v>13380.97812124987</v>
       </c>
       <c r="E50">
         <v>4739.603999999999</v>
@@ -5393,45 +5393,45 @@
         <v>824.2</v>
       </c>
       <c r="M50">
-        <v>915.9209136000001</v>
+        <v>530.3804832</v>
       </c>
       <c r="N50">
-        <v>-91.72091360000002</v>
+        <v>293.8195168000001</v>
       </c>
       <c r="O50">
-        <v>-27.51627408000001</v>
+        <v>88.14585504000003</v>
       </c>
       <c r="P50">
-        <v>-64.20463952000001</v>
+        <v>205.6736617600001</v>
       </c>
       <c r="Q50">
-        <v>88.39536047999989</v>
+        <v>358.27366176</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1197132089874213</v>
+        <v>0.1184419564098959</v>
       </c>
       <c r="T50">
-        <v>1.705905066182564</v>
+        <v>1.677643335101521</v>
       </c>
       <c r="U50">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
-        <v>0.2699578056670328</v>
+        <v>0.3</v>
       </c>
       <c r="W50">
-        <v>0.09556252323818541</v>
+        <v>0.05306</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.8998593522234428</v>
+        <v>1.553978749420168</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1089718798277881</v>
+        <v>0.08699883245931474</v>
       </c>
       <c r="C51">
-        <v>2796.099838172097</v>
+        <v>7451.418663955864</v>
       </c>
       <c r="D51">
-        <v>8745.076838172097</v>
+        <v>13400.39566395586</v>
       </c>
       <c r="E51">
         <v>4885.376999999999</v>
@@ -5475,45 +5475,45 @@
         <v>824.2</v>
       </c>
       <c r="M51">
-        <v>935.0025993</v>
+        <v>541.4300766</v>
       </c>
       <c r="N51">
-        <v>-110.8025993</v>
+        <v>282.7699234</v>
       </c>
       <c r="O51">
-        <v>-33.24077979</v>
+        <v>84.83097702000001</v>
       </c>
       <c r="P51">
-        <v>-77.56181950999999</v>
+        <v>197.93894638</v>
       </c>
       <c r="Q51">
-        <v>75.03818048999992</v>
+        <v>350.53894638</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1211624875950178</v>
+        <v>0.1196067303123818</v>
       </c>
       <c r="T51">
-        <v>1.73935418512732</v>
+        <v>1.704543425228218</v>
       </c>
       <c r="U51">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V51">
-        <v>0.2644484626942363</v>
+        <v>0.3</v>
       </c>
       <c r="W51">
-        <v>0.09628369623332449</v>
+        <v>0.05306</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.8814948756474543</v>
+        <v>1.522264897391184</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1098228798277881</v>
+        <v>0.09190904758548361</v>
       </c>
       <c r="C52">
-        <v>2534.086200304784</v>
+        <v>5878.619322459295</v>
       </c>
       <c r="D52">
-        <v>8628.836200304784</v>
+        <v>11973.3693224593</v>
       </c>
       <c r="E52">
         <v>5031.15</v>
@@ -5557,45 +5557,45 @@
         <v>824.2</v>
       </c>
       <c r="M52">
-        <v>954.084285</v>
+        <v>655.9785000000001</v>
       </c>
       <c r="N52">
-        <v>-129.884285</v>
+        <v>168.2215</v>
       </c>
       <c r="O52">
-        <v>-38.96528549999999</v>
+        <v>50.46644999999999</v>
       </c>
       <c r="P52">
-        <v>-90.91899949999998</v>
+        <v>117.75505</v>
       </c>
       <c r="Q52">
-        <v>61.68100049999993</v>
+        <v>270.3550499999999</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1226697373469181</v>
+        <v>0.1208180951709672</v>
       </c>
       <c r="T52">
-        <v>1.774141268829867</v>
+        <v>1.732519518959982</v>
       </c>
       <c r="U52">
-        <v>0.1309</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V52">
-        <v>0.2591594934403516</v>
+        <v>0.3</v>
       </c>
       <c r="W52">
-        <v>0.09697602230865798</v>
+        <v>0.063</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.8638649781345051</v>
+        <v>1.256443618197852</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1106738798277881</v>
+        <v>0.1037831423603764</v>
       </c>
       <c r="C53">
-        <v>2275.122196067759</v>
+        <v>3280.876382195563</v>
       </c>
       <c r="D53">
-        <v>8515.645196067759</v>
+        <v>9521.399382195563</v>
       </c>
       <c r="E53">
         <v>5176.923</v>
@@ -5639,37 +5639,37 @@
         <v>824.2</v>
       </c>
       <c r="M53">
-        <v>973.1659707000001</v>
+        <v>881.7225678000001</v>
       </c>
       <c r="N53">
-        <v>-148.9659707000001</v>
+        <v>-57.52256780000005</v>
       </c>
       <c r="O53">
-        <v>-44.68979121000002</v>
+        <v>-17.25677034000001</v>
       </c>
       <c r="P53">
-        <v>-104.2761794900001</v>
+        <v>-40.26579746000003</v>
       </c>
       <c r="Q53">
-        <v>48.32382050999985</v>
+        <v>112.3342025399999</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1242385074968552</v>
+        <v>0.1229778187878519</v>
       </c>
       <c r="T53">
-        <v>1.810348233499864</v>
+        <v>1.782397662536995</v>
       </c>
       <c r="U53">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V53">
-        <v>0.2540779347454427</v>
+        <v>0.2804283445040341</v>
       </c>
       <c r="W53">
-        <v>0.09764119834182156</v>
+        <v>0.08534119834182156</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8469264491514756</v>
+        <v>0.9347611483467804</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1115248798277881</v>
+        <v>0.1045111423603764</v>
       </c>
       <c r="C54">
-        <v>2019.089366291855</v>
+        <v>3017.040975783988</v>
       </c>
       <c r="D54">
-        <v>8405.385366291855</v>
+        <v>9403.336975783988</v>
       </c>
       <c r="E54">
         <v>5322.696</v>
@@ -5721,37 +5721,37 @@
         <v>824.2</v>
       </c>
       <c r="M54">
-        <v>992.2476564000001</v>
+        <v>899.0112456000001</v>
       </c>
       <c r="N54">
-        <v>-168.0476564000001</v>
+        <v>-74.81124560000001</v>
       </c>
       <c r="O54">
-        <v>-50.41429692000001</v>
+        <v>-22.44337368</v>
       </c>
       <c r="P54">
-        <v>-117.63335948</v>
+        <v>-52.36787192000001</v>
       </c>
       <c r="Q54">
-        <v>34.96664051999987</v>
+        <v>100.2321280799999</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1258726430697064</v>
+        <v>0.1245856900125988</v>
       </c>
       <c r="T54">
-        <v>1.848063821697778</v>
+        <v>1.819530947173182</v>
       </c>
       <c r="U54">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V54">
-        <v>0.2491918206157226</v>
+        <v>0.2750354917251104</v>
       </c>
       <c r="W54">
-        <v>0.09828079068140191</v>
+        <v>0.08598079068140192</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8306394020524088</v>
+        <v>0.9167849724170347</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1123758798277881</v>
+        <v>0.1052391423603764</v>
       </c>
       <c r="C55">
-        <v>1765.875308581209</v>
+        <v>2756.097583908781</v>
       </c>
       <c r="D55">
-        <v>8297.944308581209</v>
+        <v>9288.166583908782</v>
       </c>
       <c r="E55">
         <v>5468.469</v>
@@ -5803,37 +5803,37 @@
         <v>824.2</v>
       </c>
       <c r="M55">
-        <v>1011.3293421</v>
+        <v>916.2999234000001</v>
       </c>
       <c r="N55">
-        <v>-187.1293421</v>
+        <v>-92.09992340000008</v>
       </c>
       <c r="O55">
-        <v>-56.13880263000001</v>
+        <v>-27.62997702000002</v>
       </c>
       <c r="P55">
-        <v>-130.99053947</v>
+        <v>-64.46994638000005</v>
       </c>
       <c r="Q55">
-        <v>21.60946052999989</v>
+        <v>88.13005361999986</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1275763163265087</v>
+        <v>0.1262619812894626</v>
       </c>
       <c r="T55">
-        <v>1.887384328542412</v>
+        <v>1.858244371581123</v>
       </c>
       <c r="U55">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V55">
-        <v>0.244490088151275</v>
+        <v>0.2698461428246366</v>
       </c>
       <c r="W55">
-        <v>0.09889624746099811</v>
+        <v>0.0865962474609981</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8149669605042501</v>
+        <v>0.8994871427487887</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1613239539232618</v>
+        <v>0.1059671423603764</v>
       </c>
       <c r="C56">
-        <v>-1895.777983451992</v>
+        <v>2497.941229675582</v>
       </c>
       <c r="D56">
-        <v>4782.064016548008</v>
+        <v>9175.783229675582</v>
       </c>
       <c r="E56">
         <v>5614.242</v>
@@ -5885,45 +5885,45 @@
         <v>824.2</v>
       </c>
       <c r="M56">
-        <v>1698.7219236</v>
+        <v>933.5886012000001</v>
       </c>
       <c r="N56">
-        <v>-874.5219236</v>
+        <v>-109.3886012</v>
       </c>
       <c r="O56">
-        <v>-262.35657708</v>
+        <v>-32.81658036000001</v>
       </c>
       <c r="P56">
-        <v>-612.16534652</v>
+        <v>-76.57202084000002</v>
       </c>
       <c r="Q56">
-        <v>-459.56534652</v>
+        <v>76.02797915999989</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1342477016715931</v>
+        <v>0.1280111547957553</v>
       </c>
       <c r="T56">
-        <v>2.041358837490772</v>
+        <v>1.898640988354625</v>
       </c>
       <c r="U56">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V56">
-        <v>0.1455564895966001</v>
+        <v>0.2648489920315878</v>
       </c>
       <c r="W56">
-        <v>0.1843889095450537</v>
+        <v>0.08718890954505371</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.4851882986553339</v>
+        <v>0.882829973438626</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1630239539232619</v>
+        <v>0.1066951423603764</v>
       </c>
       <c r="C57">
-        <v>-2110.901219099679</v>
+        <v>2242.471956175278</v>
       </c>
       <c r="D57">
-        <v>4712.713780900322</v>
+        <v>9066.086956175279</v>
       </c>
       <c r="E57">
         <v>5760.015</v>
@@ -5967,45 +5967,45 @@
         <v>824.2</v>
       </c>
       <c r="M57">
-        <v>1730.179737</v>
+        <v>950.8772790000002</v>
       </c>
       <c r="N57">
-        <v>-905.9797370000001</v>
+        <v>-126.6772790000001</v>
       </c>
       <c r="O57">
-        <v>-271.7939211</v>
+        <v>-38.00318370000003</v>
       </c>
       <c r="P57">
-        <v>-634.1858159000001</v>
+        <v>-88.67409530000009</v>
       </c>
       <c r="Q57">
-        <v>-481.5858159000002</v>
+        <v>63.92590469999982</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1362132061531841</v>
+        <v>0.1298380693467721</v>
       </c>
       <c r="T57">
-        <v>2.086722367212789</v>
+        <v>1.940833010318061</v>
       </c>
       <c r="U57">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V57">
-        <v>0.1429100079675711</v>
+        <v>0.2600335558128316</v>
       </c>
       <c r="W57">
-        <v>0.1849600202805982</v>
+        <v>0.08776002028059818</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.4763666932252368</v>
+        <v>0.8667785193761054</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1647239539232618</v>
+        <v>0.1074231423603764</v>
       </c>
       <c r="C58">
-        <v>-2324.041752411766</v>
+        <v>1989.594529959915</v>
       </c>
       <c r="D58">
-        <v>4645.346247588235</v>
+        <v>8958.982529959916</v>
       </c>
       <c r="E58">
         <v>5905.788</v>
@@ -6049,45 +6049,45 @@
         <v>824.2</v>
       </c>
       <c r="M58">
-        <v>1761.6375504</v>
+        <v>968.1659568000001</v>
       </c>
       <c r="N58">
-        <v>-937.4375504000002</v>
+        <v>-143.9659568000001</v>
       </c>
       <c r="O58">
-        <v>-281.23126512</v>
+        <v>-43.18978704000002</v>
       </c>
       <c r="P58">
-        <v>-656.2062852800002</v>
+        <v>-100.77616976</v>
       </c>
       <c r="Q58">
-        <v>-503.6062852800003</v>
+        <v>51.82383023999986</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1382680517475746</v>
+        <v>0.1317480254682896</v>
       </c>
       <c r="T58">
-        <v>2.134147875558534</v>
+        <v>1.984942851461654</v>
       </c>
       <c r="U58">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V58">
-        <v>0.1403580435395787</v>
+        <v>0.2553900994590311</v>
       </c>
       <c r="W58">
-        <v>0.1855107342041589</v>
+        <v>0.08831073420415893</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.467860145131929</v>
+        <v>0.8513003315301035</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1664239539232618</v>
+        <v>0.1081511423603764</v>
       </c>
       <c r="C59">
-        <v>-2535.283412359058</v>
+        <v>1739.218165291564</v>
       </c>
       <c r="D59">
-        <v>4579.877587640942</v>
+        <v>8854.379165291564</v>
       </c>
       <c r="E59">
         <v>6051.561</v>
@@ -6131,45 +6131,45 @@
         <v>824.2</v>
       </c>
       <c r="M59">
-        <v>1793.0953638</v>
+        <v>985.4546346000001</v>
       </c>
       <c r="N59">
-        <v>-968.8953638</v>
+        <v>-161.2546346</v>
       </c>
       <c r="O59">
-        <v>-290.66860914</v>
+        <v>-48.37639038000001</v>
       </c>
       <c r="P59">
-        <v>-678.2267546600001</v>
+        <v>-112.87824422</v>
       </c>
       <c r="Q59">
-        <v>-525.6267546600002</v>
+        <v>39.72175577999988</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1404184715556577</v>
+        <v>0.1337468167582498</v>
       </c>
       <c r="T59">
-        <v>2.183779221501756</v>
+        <v>2.031104313123552</v>
       </c>
       <c r="U59">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V59">
-        <v>0.1378956217230949</v>
+        <v>0.2509095713983464</v>
       </c>
       <c r="W59">
-        <v>0.1860421248321562</v>
+        <v>0.08884212483215613</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.4596520724103162</v>
+        <v>0.8363652379944878</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1681239539232618</v>
+        <v>0.1088791423603764</v>
       </c>
       <c r="C60">
-        <v>-2744.705367852057</v>
+        <v>1491.256267485918</v>
       </c>
       <c r="D60">
-        <v>4516.228632147941</v>
+        <v>8752.190267485918</v>
       </c>
       <c r="E60">
         <v>6197.333999999999</v>
@@ -6213,45 +6213,45 @@
         <v>824.2</v>
       </c>
       <c r="M60">
-        <v>1824.5531772</v>
+        <v>1002.7433124</v>
       </c>
       <c r="N60">
-        <v>-1000.3531772</v>
+        <v>-178.5433123999999</v>
       </c>
       <c r="O60">
-        <v>-300.10595316</v>
+        <v>-53.56299371999996</v>
       </c>
       <c r="P60">
-        <v>-700.24722404</v>
+        <v>-124.9803186799999</v>
       </c>
       <c r="Q60">
-        <v>-547.6472240400001</v>
+        <v>27.61968131999998</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1426712923069829</v>
+        <v>0.1358407885858272</v>
       </c>
       <c r="T60">
-        <v>2.235773964870845</v>
+        <v>2.079463939626494</v>
       </c>
       <c r="U60">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V60">
-        <v>0.1355181110037312</v>
+        <v>0.2465835443052714</v>
       </c>
       <c r="W60">
-        <v>0.1865551916453948</v>
+        <v>0.08935519164539482</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.451727036679104</v>
+        <v>0.8219451476842381</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1698239539232618</v>
+        <v>0.1096071423603764</v>
       </c>
       <c r="C61">
-        <v>-2952.382447118891</v>
+        <v>1245.626193825676</v>
       </c>
       <c r="D61">
-        <v>4454.324552881109</v>
+        <v>8652.333193825676</v>
       </c>
       <c r="E61">
         <v>6343.107</v>
@@ -6295,45 +6295,45 @@
         <v>824.2</v>
       </c>
       <c r="M61">
-        <v>1856.0109906</v>
+        <v>1020.0319902</v>
       </c>
       <c r="N61">
-        <v>-1031.8109906</v>
+        <v>-195.8319902000001</v>
       </c>
       <c r="O61">
-        <v>-309.54329718</v>
+        <v>-58.74959706000001</v>
       </c>
       <c r="P61">
-        <v>-722.2676934200001</v>
+        <v>-137.0823931400001</v>
       </c>
       <c r="Q61">
-        <v>-569.6676934200002</v>
+        <v>15.51760685999986</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1450340067534947</v>
+        <v>0.1380369053806035</v>
       </c>
       <c r="T61">
-        <v>2.290305037184768</v>
+        <v>2.130182572300311</v>
       </c>
       <c r="U61">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V61">
-        <v>0.1332211938680747</v>
+        <v>0.2424041621984024</v>
       </c>
       <c r="W61">
-        <v>0.1870508663632695</v>
+        <v>0.08985086636326949</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.4440706462269157</v>
+        <v>0.8080138739946746</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1715239539232618</v>
+        <v>0.1622386949392388</v>
       </c>
       <c r="C62">
-        <v>-3158.385431172048</v>
+        <v>-2811.095221203417</v>
       </c>
       <c r="D62">
-        <v>4394.094568827952</v>
+        <v>4741.384778796582</v>
       </c>
       <c r="E62">
         <v>6488.879999999999</v>
@@ -6377,37 +6377,37 @@
         <v>824.2</v>
       </c>
       <c r="M62">
-        <v>1887.468804</v>
+        <v>1756.273104</v>
       </c>
       <c r="N62">
-        <v>-1063.268804</v>
+        <v>-932.0731039999998</v>
       </c>
       <c r="O62">
-        <v>-318.9806412</v>
+        <v>-279.6219311999999</v>
       </c>
       <c r="P62">
-        <v>-744.2881628</v>
+        <v>-652.4511727999999</v>
       </c>
       <c r="Q62">
-        <v>-591.6881628000001</v>
+        <v>-499.8511728</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1475148569223321</v>
+        <v>0.1468017094622744</v>
       </c>
       <c r="T62">
-        <v>2.347562663114387</v>
+        <v>2.332602989890862</v>
       </c>
       <c r="U62">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1310008406369401</v>
+        <v>0.1407867600072295</v>
       </c>
       <c r="W62">
-        <v>0.1875300185905484</v>
+        <v>0.1725300185905483</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4366694687898005</v>
+        <v>0.4692892000240984</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1732239539232618</v>
+        <v>0.1637886949392387</v>
       </c>
       <c r="C63">
-        <v>-3362.781323783796</v>
+        <v>-3019.15509038965</v>
       </c>
       <c r="D63">
-        <v>4335.471676216204</v>
+        <v>4679.09790961035</v>
       </c>
       <c r="E63">
         <v>6634.653</v>
@@ -6459,37 +6459,37 @@
         <v>824.2</v>
       </c>
       <c r="M63">
-        <v>1918.9266174</v>
+        <v>1785.5443224</v>
       </c>
       <c r="N63">
-        <v>-1094.7266174</v>
+        <v>-961.3443224</v>
       </c>
       <c r="O63">
-        <v>-328.41798522</v>
+        <v>-288.40329672</v>
       </c>
       <c r="P63">
-        <v>-766.3086321800001</v>
+        <v>-672.9410256799999</v>
       </c>
       <c r="Q63">
-        <v>-613.7086321800002</v>
+        <v>-520.34102568</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1501229301767509</v>
+        <v>0.149391496884384</v>
       </c>
       <c r="T63">
-        <v>2.407756577553218</v>
+        <v>2.392413322964987</v>
       </c>
       <c r="U63">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1288532858724001</v>
+        <v>0.1384787803349798</v>
       </c>
       <c r="W63">
-        <v>0.1879934609087361</v>
+        <v>0.172993460908736</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4295109529080005</v>
+        <v>0.4615959344499327</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1749239539232618</v>
+        <v>0.1653386949392387</v>
       </c>
       <c r="C64">
-        <v>-3565.633600135165</v>
+        <v>-3225.599672621516</v>
       </c>
       <c r="D64">
-        <v>4278.392399864835</v>
+        <v>4618.426327378484</v>
       </c>
       <c r="E64">
         <v>6780.425999999999</v>
@@ -6541,37 +6541,37 @@
         <v>824.2</v>
       </c>
       <c r="M64">
-        <v>1950.3844308</v>
+        <v>1814.8155408</v>
       </c>
       <c r="N64">
-        <v>-1126.1844308</v>
+        <v>-990.6155408</v>
       </c>
       <c r="O64">
-        <v>-337.85532924</v>
+        <v>-297.18466224</v>
       </c>
       <c r="P64">
-        <v>-788.32910156</v>
+        <v>-693.43087856</v>
       </c>
       <c r="Q64">
-        <v>-635.7291015600001</v>
+        <v>-540.8308785600001</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1528682704445601</v>
+        <v>0.1521175889076572</v>
       </c>
       <c r="T64">
-        <v>2.471118592751986</v>
+        <v>2.455371568306171</v>
       </c>
       <c r="U64">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1267750070680066</v>
+        <v>0.1362452516198995</v>
       </c>
       <c r="W64">
-        <v>0.1884419534747242</v>
+        <v>0.1734419534747242</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4225833568933554</v>
+        <v>0.4541508387329983</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1766239539232618</v>
+        <v>0.1668886949392387</v>
       </c>
       <c r="C65">
-        <v>-3767.002436078454</v>
+        <v>-3430.49099750749</v>
       </c>
       <c r="D65">
-        <v>4222.796563921544</v>
+        <v>4559.308002492509</v>
       </c>
       <c r="E65">
         <v>6926.198999999999</v>
@@ -6623,37 +6623,37 @@
         <v>824.2</v>
       </c>
       <c r="M65">
-        <v>1981.8422442</v>
+        <v>1844.0867592</v>
       </c>
       <c r="N65">
-        <v>-1157.6422442</v>
+        <v>-1019.8867592</v>
       </c>
       <c r="O65">
-        <v>-347.29267326</v>
+        <v>-305.9660277599999</v>
       </c>
       <c r="P65">
-        <v>-810.3495709399999</v>
+        <v>-713.9207314399998</v>
       </c>
       <c r="Q65">
-        <v>-657.74957094</v>
+        <v>-561.3207314399999</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1557620074836022</v>
+        <v>0.1549910372565128</v>
       </c>
       <c r="T65">
-        <v>2.537905581745283</v>
+        <v>2.521732962044176</v>
       </c>
       <c r="U65">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1247627053685144</v>
+        <v>0.1340826285783138</v>
       </c>
       <c r="W65">
-        <v>0.1888762081814746</v>
+        <v>0.1738762081814746</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4158756845617148</v>
+        <v>0.4469420952610461</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1783239539232619</v>
+        <v>0.1684386949392387</v>
       </c>
       <c r="C66">
-        <v>-3966.944919754016</v>
+        <v>-3633.887958748801</v>
       </c>
       <c r="D66">
-        <v>4168.627080245984</v>
+        <v>4501.684041251199</v>
       </c>
       <c r="E66">
         <v>7071.972</v>
@@ -6705,37 +6705,37 @@
         <v>824.2</v>
       </c>
       <c r="M66">
-        <v>2013.3000576</v>
+        <v>1873.3579776</v>
       </c>
       <c r="N66">
-        <v>-1189.1000576</v>
+        <v>-1049.1579776</v>
       </c>
       <c r="O66">
-        <v>-356.73001728</v>
+        <v>-314.7473932799999</v>
       </c>
       <c r="P66">
-        <v>-832.37004032</v>
+        <v>-734.41058432</v>
       </c>
       <c r="Q66">
-        <v>-679.7700403200001</v>
+        <v>-581.8105843200001</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1588165076914801</v>
+        <v>0.1580241216247493</v>
       </c>
       <c r="T66">
-        <v>2.608402959015986</v>
+        <v>2.591781099878736</v>
       </c>
       <c r="U66">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1228132880971314</v>
+        <v>0.1319875875067777</v>
       </c>
       <c r="W66">
-        <v>0.1892968924286391</v>
+        <v>0.174296892428639</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4093776269904379</v>
+        <v>0.4399586250225922</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1800239539232618</v>
+        <v>0.1699886949392387</v>
       </c>
       <c r="C67">
-        <v>-4165.51524712577</v>
+        <v>-3835.846509835823</v>
       </c>
       <c r="D67">
-        <v>4115.829752874229</v>
+        <v>4445.498490164176</v>
       </c>
       <c r="E67">
         <v>7217.744999999999</v>
@@ -6787,37 +6787,37 @@
         <v>824.2</v>
       </c>
       <c r="M67">
-        <v>2044.757871</v>
+        <v>1902.629196</v>
       </c>
       <c r="N67">
-        <v>-1220.557871</v>
+        <v>-1078.429196</v>
       </c>
       <c r="O67">
-        <v>-366.1673613</v>
+        <v>-323.5287587999999</v>
       </c>
       <c r="P67">
-        <v>-854.3905096999999</v>
+        <v>-754.9004371999999</v>
       </c>
       <c r="Q67">
-        <v>-701.7905097</v>
+        <v>-602.3004372</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1620455507683795</v>
+        <v>0.1612305250997421</v>
       </c>
       <c r="T67">
-        <v>2.682928757845014</v>
+        <v>2.6658319884467</v>
       </c>
       <c r="U67">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.120923852895637</v>
+        <v>0.1299570092374426</v>
       </c>
       <c r="W67">
-        <v>0.1897046325451215</v>
+        <v>0.1747046325451215</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4030795096521235</v>
+        <v>0.4331900307914754</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1817239539232618</v>
+        <v>0.1715386949392387</v>
       </c>
       <c r="C68">
-        <v>-4362.764902843399</v>
+        <v>-4036.419845270228</v>
       </c>
       <c r="D68">
-        <v>4064.353097156602</v>
+        <v>4390.698154729773</v>
       </c>
       <c r="E68">
         <v>7363.518</v>
@@ -6869,37 +6869,37 @@
         <v>824.2</v>
       </c>
       <c r="M68">
-        <v>2076.2156844</v>
+        <v>1931.9004144</v>
       </c>
       <c r="N68">
-        <v>-1252.0156844</v>
+        <v>-1107.7004144</v>
       </c>
       <c r="O68">
-        <v>-375.60470532</v>
+        <v>-332.31012432</v>
       </c>
       <c r="P68">
-        <v>-876.4109790800001</v>
+        <v>-775.39029008</v>
       </c>
       <c r="Q68">
-        <v>-723.8109790800002</v>
+        <v>-622.7902900800001</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1654645375556848</v>
+        <v>0.1646255405438522</v>
       </c>
       <c r="T68">
-        <v>2.761838427193397</v>
+        <v>2.744238811636309</v>
       </c>
       <c r="U68">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1190916733063092</v>
+        <v>0.1279879636429359</v>
       </c>
       <c r="W68">
-        <v>0.1901000169004985</v>
+        <v>0.1751000169004985</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3969722443543641</v>
+        <v>0.4266265454764531</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1834239539232618</v>
+        <v>0.1730886949392387</v>
       </c>
       <c r="C69">
-        <v>-4558.742827699856</v>
+        <v>-4235.658568546594</v>
       </c>
       <c r="D69">
-        <v>4014.148172300143</v>
+        <v>4337.232431453405</v>
       </c>
       <c r="E69">
         <v>7509.290999999999</v>
@@ -6951,37 +6951,37 @@
         <v>824.2</v>
       </c>
       <c r="M69">
-        <v>2107.6734978</v>
+        <v>1961.1716328</v>
       </c>
       <c r="N69">
-        <v>-1283.4734978</v>
+        <v>-1136.9716328</v>
       </c>
       <c r="O69">
-        <v>-385.0420493399999</v>
+        <v>-341.09148984</v>
       </c>
       <c r="P69">
-        <v>-898.43144846</v>
+        <v>-795.8801429600001</v>
       </c>
       <c r="Q69">
-        <v>-745.83144846</v>
+        <v>-643.2801429600001</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1690907356634328</v>
+        <v>0.1682263144997265</v>
       </c>
       <c r="T69">
-        <v>2.845530500744712</v>
+        <v>2.827397563504076</v>
       </c>
       <c r="U69">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.117314185645021</v>
+        <v>0.1260776955288622</v>
       </c>
       <c r="W69">
-        <v>0.1904835987378045</v>
+        <v>0.1754835987378044</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3910472854834034</v>
+        <v>0.4202589850962074</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1851239539232619</v>
+        <v>0.1746386949392388</v>
       </c>
       <c r="C70">
-        <v>-4753.495573829292</v>
+        <v>-4433.610848008586</v>
       </c>
       <c r="D70">
-        <v>3965.168426170708</v>
+        <v>4285.053151991414</v>
       </c>
       <c r="E70">
         <v>7655.064</v>
@@ -7033,37 +7033,37 @@
         <v>824.2</v>
       </c>
       <c r="M70">
-        <v>2139.1313112</v>
+        <v>1990.4428512</v>
       </c>
       <c r="N70">
-        <v>-1314.9313112</v>
+        <v>-1166.2428512</v>
       </c>
       <c r="O70">
-        <v>-394.4793933600001</v>
+        <v>-349.87285536</v>
       </c>
       <c r="P70">
-        <v>-920.4519178400001</v>
+        <v>-816.3699958400001</v>
       </c>
       <c r="Q70">
-        <v>-767.8519178400002</v>
+        <v>-663.7699958400002</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1729435711529151</v>
+        <v>0.172052136827843</v>
       </c>
       <c r="T70">
-        <v>2.934453328892984</v>
+        <v>2.915753737363578</v>
       </c>
       <c r="U70">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1155889770325942</v>
+        <v>0.1242236117710848</v>
       </c>
       <c r="W70">
-        <v>0.1908558987563662</v>
+        <v>0.1758558987563662</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3852965901086475</v>
+        <v>0.4140787059036162</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1868239539232618</v>
+        <v>0.1761886949392387</v>
       </c>
       <c r="C71">
-        <v>-4947.067448679716</v>
+        <v>-4630.322561588637</v>
       </c>
       <c r="D71">
-        <v>3917.369551320283</v>
+        <v>4234.114438411362</v>
       </c>
       <c r="E71">
         <v>7800.837</v>
@@ -7115,37 +7115,37 @@
         <v>824.2</v>
       </c>
       <c r="M71">
-        <v>2170.5891246</v>
+        <v>2019.7140696</v>
       </c>
       <c r="N71">
-        <v>-1346.3891246</v>
+        <v>-1195.5140696</v>
       </c>
       <c r="O71">
-        <v>-403.91673738</v>
+        <v>-358.65422088</v>
       </c>
       <c r="P71">
-        <v>-942.47238722</v>
+        <v>-836.8598487199999</v>
       </c>
       <c r="Q71">
-        <v>-789.8723872200001</v>
+        <v>-684.25984872</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1770449766739769</v>
+        <v>0.1761247864029347</v>
       </c>
       <c r="T71">
-        <v>3.029113113695984</v>
+        <v>3.009810309536597</v>
       </c>
       <c r="U71">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1139137744669045</v>
+        <v>0.1224232695715039</v>
       </c>
       <c r="W71">
-        <v>0.191217407470042</v>
+        <v>0.176217407470042</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3797125815563482</v>
+        <v>0.4080775652383464</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1885239539232618</v>
+        <v>0.1777386949392387</v>
       </c>
       <c r="C72">
-        <v>-5139.500648696492</v>
+        <v>-4825.837431345348</v>
       </c>
       <c r="D72">
-        <v>3870.709351303508</v>
+        <v>4184.372568654653</v>
       </c>
       <c r="E72">
         <v>7946.610000000001</v>
@@ -7197,37 +7197,37 @@
         <v>824.2</v>
       </c>
       <c r="M72">
-        <v>2202.046938</v>
+        <v>2048.985288</v>
       </c>
       <c r="N72">
-        <v>-1377.846938</v>
+        <v>-1224.785288</v>
       </c>
       <c r="O72">
-        <v>-413.3540814000001</v>
+        <v>-367.4355864000001</v>
       </c>
       <c r="P72">
-        <v>-964.4928566000003</v>
+        <v>-857.3497016000001</v>
       </c>
       <c r="Q72">
-        <v>-811.8928566000004</v>
+        <v>-704.7497016000002</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1814198092297761</v>
+        <v>0.1804689459496992</v>
       </c>
       <c r="T72">
-        <v>3.130083550819183</v>
+        <v>3.110137319854484</v>
       </c>
       <c r="U72">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.112286434831663</v>
+        <v>0.1206743657204824</v>
       </c>
       <c r="W72">
-        <v>0.1915685873633271</v>
+        <v>0.1765685873633271</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3742881161055432</v>
+        <v>0.4022478857349414</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1902239539232619</v>
+        <v>0.1792886949392387</v>
       </c>
       <c r="C73">
-        <v>-5330.835383564327</v>
+        <v>-5020.197148627785</v>
       </c>
       <c r="D73">
-        <v>3825.147616435673</v>
+        <v>4135.785851372214</v>
       </c>
       <c r="E73">
         <v>8092.383</v>
@@ -7279,37 +7279,37 @@
         <v>824.2</v>
       </c>
       <c r="M73">
-        <v>2233.5047514</v>
+        <v>2078.2565064</v>
       </c>
       <c r="N73">
-        <v>-1409.3047514</v>
+        <v>-1254.0565064</v>
       </c>
       <c r="O73">
-        <v>-422.7914254200001</v>
+        <v>-376.21695192</v>
       </c>
       <c r="P73">
-        <v>-986.5133259800002</v>
+        <v>-877.8395544800001</v>
       </c>
       <c r="Q73">
-        <v>-833.9133259800003</v>
+        <v>-725.2395544800002</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1860963543756305</v>
+        <v>0.1851127027065853</v>
       </c>
       <c r="T73">
-        <v>3.238017466364672</v>
+        <v>3.217383434332224</v>
       </c>
       <c r="U73">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1107049357495269</v>
+        <v>0.1189747267666728</v>
       </c>
       <c r="W73">
-        <v>0.1919098748652521</v>
+        <v>0.1769098748652521</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3690164524984229</v>
+        <v>0.3965824225555761</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1919239539232618</v>
+        <v>0.1808386949392387</v>
       </c>
       <c r="C74">
-        <v>-5521.109991776731</v>
+        <v>-5213.441490619881</v>
       </c>
       <c r="D74">
-        <v>3780.646008223267</v>
+        <v>4088.314509380118</v>
       </c>
       <c r="E74">
         <v>8238.155999999999</v>
@@ -7361,37 +7361,37 @@
         <v>824.2</v>
       </c>
       <c r="M74">
-        <v>2264.9625648</v>
+        <v>2107.5277248</v>
       </c>
       <c r="N74">
-        <v>-1440.7625648</v>
+        <v>-1283.3277248</v>
       </c>
       <c r="O74">
-        <v>-432.22876944</v>
+        <v>-384.9983174399999</v>
       </c>
       <c r="P74">
-        <v>-1008.53379536</v>
+        <v>-898.3294073599998</v>
       </c>
       <c r="Q74">
-        <v>-855.9337953600002</v>
+        <v>-745.7294073599999</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1911069384604744</v>
+        <v>0.1900881563746776</v>
       </c>
       <c r="T74">
-        <v>3.353660947306267</v>
+        <v>3.332289985558374</v>
       </c>
       <c r="U74">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1091673671974501</v>
+        <v>0.1173223000060246</v>
       </c>
       <c r="W74">
-        <v>0.1922416821587903</v>
+        <v>0.1772416821587903</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3638912239915004</v>
+        <v>0.3910743333534153</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1936239539232618</v>
+        <v>0.1823886949392387</v>
       </c>
       <c r="C75">
-        <v>-5710.361048231074</v>
+        <v>-5405.608428949537</v>
       </c>
       <c r="D75">
-        <v>3737.167951768926</v>
+        <v>4041.920571050463</v>
       </c>
       <c r="E75">
         <v>8383.929</v>
@@ -7443,37 +7443,37 @@
         <v>824.2</v>
       </c>
       <c r="M75">
-        <v>2296.4203782</v>
+        <v>2136.7989432</v>
       </c>
       <c r="N75">
-        <v>-1472.2203782</v>
+        <v>-1312.5989432</v>
       </c>
       <c r="O75">
-        <v>-441.6661134600001</v>
+        <v>-393.7796829599999</v>
       </c>
       <c r="P75">
-        <v>-1030.55426474</v>
+        <v>-918.8192602399999</v>
       </c>
       <c r="Q75">
-        <v>-877.9542647400003</v>
+        <v>-766.21926024</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1964886769219734</v>
+        <v>0.1954321621663323</v>
       </c>
       <c r="T75">
-        <v>3.477870612021314</v>
+        <v>3.455708133171647</v>
       </c>
       <c r="U75">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1076719238111837</v>
+        <v>0.1157151452114215</v>
       </c>
       <c r="W75">
-        <v>0.1925643988415466</v>
+        <v>0.1775643988415466</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3589064127039455</v>
+        <v>0.3857171507047383</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1953239539232618</v>
+        <v>0.1839386949392388</v>
       </c>
       <c r="C76">
-        <v>-5898.623464483855</v>
+        <v>-5596.734230985809</v>
       </c>
       <c r="D76">
-        <v>3694.678535516145</v>
+        <v>3996.567769014191</v>
       </c>
       <c r="E76">
         <v>8529.701999999999</v>
@@ -7525,37 +7525,37 @@
         <v>824.2</v>
       </c>
       <c r="M76">
-        <v>2327.8781916</v>
+        <v>2166.0701616</v>
       </c>
       <c r="N76">
-        <v>-1503.6781916</v>
+        <v>-1341.8701616</v>
       </c>
       <c r="O76">
-        <v>-451.10345748</v>
+        <v>-402.56104848</v>
       </c>
       <c r="P76">
-        <v>-1052.57473412</v>
+        <v>-939.3091131200001</v>
       </c>
       <c r="Q76">
-        <v>-899.9747341200002</v>
+        <v>-786.7091131200002</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2022843952651263</v>
+        <v>0.2011872453265759</v>
       </c>
       <c r="T76">
-        <v>3.611634866329827</v>
+        <v>3.58861998444748</v>
       </c>
       <c r="U76">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1062168978137352</v>
+        <v>0.1141514270328888</v>
       </c>
       <c r="W76">
-        <v>0.1928783934517959</v>
+        <v>0.177878393451796</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3540563260457842</v>
+        <v>0.3805047567762959</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1970239539232619</v>
+        <v>0.1854886949392388</v>
       </c>
       <c r="C77">
-        <v>-6085.930582243827</v>
+        <v>-5786.853554392055</v>
       </c>
       <c r="D77">
-        <v>3653.144417756171</v>
+        <v>3952.221445607943</v>
       </c>
       <c r="E77">
         <v>8675.474999999999</v>
@@ -7607,37 +7607,37 @@
         <v>824.2</v>
       </c>
       <c r="M77">
-        <v>2359.336005</v>
+        <v>2195.34138</v>
       </c>
       <c r="N77">
-        <v>-1535.136005</v>
+        <v>-1371.14138</v>
       </c>
       <c r="O77">
-        <v>-460.5408015</v>
+        <v>-411.3424139999999</v>
       </c>
       <c r="P77">
-        <v>-1074.5952035</v>
+        <v>-959.7989659999998</v>
       </c>
       <c r="Q77">
-        <v>-921.9952035000001</v>
+        <v>-807.1989659999999</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2085437710757313</v>
+        <v>0.207402735139639</v>
       </c>
       <c r="T77">
-        <v>3.75610026098302</v>
+        <v>3.73216478382538</v>
       </c>
       <c r="U77">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1048006725095521</v>
+        <v>0.1126294080057836</v>
       </c>
       <c r="W77">
-        <v>0.1931840148724387</v>
+        <v>0.1781840148724387</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3493355750318403</v>
+        <v>0.3754313600192787</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1987239539232618</v>
+        <v>0.1870386949392387</v>
       </c>
       <c r="C78">
-        <v>-6272.314260629124</v>
+        <v>-5975.999535453144</v>
       </c>
       <c r="D78">
-        <v>3612.533739370875</v>
+        <v>3908.848464546856</v>
       </c>
       <c r="E78">
         <v>8821.248</v>
@@ -7689,37 +7689,37 @@
         <v>824.2</v>
       </c>
       <c r="M78">
-        <v>2390.7938184</v>
+        <v>2224.6125984</v>
       </c>
       <c r="N78">
-        <v>-1566.5938184</v>
+        <v>-1400.4125984</v>
       </c>
       <c r="O78">
-        <v>-469.9781455199999</v>
+        <v>-420.12377952</v>
       </c>
       <c r="P78">
-        <v>-1096.61567288</v>
+        <v>-980.28881888</v>
       </c>
       <c r="Q78">
-        <v>-944.01567288</v>
+        <v>-827.6888188800001</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2153247615372201</v>
+        <v>0.214136182437124</v>
       </c>
       <c r="T78">
-        <v>3.912604438523979</v>
+        <v>3.887671649818104</v>
       </c>
       <c r="U78">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1034217162923212</v>
+        <v>0.1111474421109707</v>
       </c>
       <c r="W78">
-        <v>0.1934815936241171</v>
+        <v>0.1784815936241171</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3447390543077372</v>
+        <v>0.3704914737032355</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2004239539232618</v>
+        <v>0.1885886949392387</v>
       </c>
       <c r="C79">
-        <v>-6457.804957668343</v>
+        <v>-6164.20387164979</v>
       </c>
       <c r="D79">
-        <v>3572.816042331655</v>
+        <v>3866.417128350208</v>
       </c>
       <c r="E79">
         <v>8967.020999999999</v>
@@ -7771,37 +7771,37 @@
         <v>824.2</v>
       </c>
       <c r="M79">
-        <v>2422.2516318</v>
+        <v>2253.8838168</v>
       </c>
       <c r="N79">
-        <v>-1598.0516318</v>
+        <v>-1429.6838168</v>
       </c>
       <c r="O79">
-        <v>-479.4154895399999</v>
+        <v>-428.9051450399999</v>
       </c>
       <c r="P79">
-        <v>-1118.63614226</v>
+        <v>-1000.77867176</v>
       </c>
       <c r="Q79">
-        <v>-966.0361422599999</v>
+        <v>-848.1786717599998</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2226954033431862</v>
+        <v>0.2214551468909119</v>
       </c>
       <c r="T79">
-        <v>4.082717674981543</v>
+        <v>4.056700851984108</v>
       </c>
       <c r="U79">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1020785771196936</v>
+        <v>0.1097039688368022</v>
       </c>
       <c r="W79">
-        <v>0.1937714430575701</v>
+        <v>0.1787714430575701</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3402619237323121</v>
+        <v>0.365679896122674</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2021239539232619</v>
+        <v>0.1901386949392387</v>
       </c>
       <c r="C80">
-        <v>-6642.43180648377</v>
+        <v>-6351.496898912515</v>
       </c>
       <c r="D80">
-        <v>3533.962193516229</v>
+        <v>3824.897101087485</v>
       </c>
       <c r="E80">
         <v>9112.794</v>
@@ -7853,37 +7853,37 @@
         <v>824.2</v>
       </c>
       <c r="M80">
-        <v>2453.7094452</v>
+        <v>2283.1550352</v>
       </c>
       <c r="N80">
-        <v>-1629.5094452</v>
+        <v>-1458.9550352</v>
       </c>
       <c r="O80">
-        <v>-488.85283356</v>
+        <v>-437.6865105599999</v>
       </c>
       <c r="P80">
-        <v>-1140.65661164</v>
+        <v>-1021.26852464</v>
       </c>
       <c r="Q80">
-        <v>-988.05661164</v>
+        <v>-868.66852464</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2307361034951493</v>
+        <v>0.2294394717495898</v>
       </c>
       <c r="T80">
-        <v>4.268295751117068</v>
+        <v>4.241096345256114</v>
       </c>
       <c r="U80">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1007698774130309</v>
+        <v>0.1082975076978688</v>
       </c>
       <c r="W80">
-        <v>0.194053860454268</v>
+        <v>0.1790538604542679</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3358995913767696</v>
+        <v>0.3609916923262295</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2038239539232618</v>
+        <v>0.1916886949392387</v>
       </c>
       <c r="C81">
-        <v>-6826.22268655716</v>
+        <v>-6537.907663950818</v>
       </c>
       <c r="D81">
-        <v>3495.944313442839</v>
+        <v>3784.259336049181</v>
       </c>
       <c r="E81">
         <v>9258.566999999999</v>
@@ -7935,37 +7935,37 @@
         <v>824.2</v>
       </c>
       <c r="M81">
-        <v>2485.1672586</v>
+        <v>2312.4262536</v>
       </c>
       <c r="N81">
-        <v>-1660.9672586</v>
+        <v>-1488.2262536</v>
       </c>
       <c r="O81">
-        <v>-498.29017758</v>
+        <v>-446.46787608</v>
       </c>
       <c r="P81">
-        <v>-1162.67708102</v>
+        <v>-1041.75837752</v>
       </c>
       <c r="Q81">
-        <v>-1010.07708102</v>
+        <v>-889.1583775200002</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2395425846139659</v>
+        <v>0.2381842084995702</v>
       </c>
       <c r="T81">
-        <v>4.471547929741691</v>
+        <v>4.443053314077834</v>
       </c>
       <c r="U81">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.09949430934451149</v>
+        <v>0.1069266531700477</v>
       </c>
       <c r="W81">
-        <v>0.1943291280434544</v>
+        <v>0.1793291280434544</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3316476978150383</v>
+        <v>0.3564221772334923</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2055239539232618</v>
+        <v>0.1932386949392388</v>
       </c>
       <c r="C82">
-        <v>-7009.204290444516</v>
+        <v>-6723.463992020112</v>
       </c>
       <c r="D82">
-        <v>3458.735709555484</v>
+        <v>3744.476007979888</v>
       </c>
       <c r="E82">
         <v>9404.34</v>
@@ -8017,37 +8017,37 @@
         <v>824.2</v>
       </c>
       <c r="M82">
-        <v>2516.625072</v>
+        <v>2341.697472</v>
       </c>
       <c r="N82">
-        <v>-1692.425072</v>
+        <v>-1517.497472</v>
       </c>
       <c r="O82">
-        <v>-507.7275216</v>
+        <v>-455.2492416000001</v>
       </c>
       <c r="P82">
-        <v>-1184.6975504</v>
+        <v>-1062.2482304</v>
       </c>
       <c r="Q82">
-        <v>-1032.0975504</v>
+        <v>-909.6482304000003</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2492297138446642</v>
+        <v>0.2478034189245488</v>
       </c>
       <c r="T82">
-        <v>4.695125326228776</v>
+        <v>4.665205979781726</v>
       </c>
       <c r="U82">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.09825063047770509</v>
+        <v>0.1055900700054221</v>
       </c>
       <c r="W82">
-        <v>0.1945975139429112</v>
+        <v>0.1795975139429113</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3275021015923504</v>
+        <v>0.3519669000180737</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2072239539232618</v>
+        <v>0.1947886949392387</v>
       </c>
       <c r="C83">
-        <v>-7191.402186275276</v>
+        <v>-6908.192550458526</v>
       </c>
       <c r="D83">
-        <v>3422.310813724724</v>
+        <v>3705.520449541473</v>
       </c>
       <c r="E83">
         <v>9550.112999999999</v>
@@ -8099,37 +8099,37 @@
         <v>824.2</v>
       </c>
       <c r="M83">
-        <v>2548.0828854</v>
+        <v>2370.9686904</v>
       </c>
       <c r="N83">
-        <v>-1723.8828854</v>
+        <v>-1546.7686904</v>
       </c>
       <c r="O83">
-        <v>-517.16486562</v>
+        <v>-464.03060712</v>
       </c>
       <c r="P83">
-        <v>-1206.71801978</v>
+        <v>-1082.73808328</v>
       </c>
       <c r="Q83">
-        <v>-1054.11801978</v>
+        <v>-930.13808328</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2599365408891202</v>
+        <v>0.2584351778153144</v>
       </c>
       <c r="T83">
-        <v>4.942237185503974</v>
+        <v>4.910743136612343</v>
       </c>
       <c r="U83">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.09703765973106677</v>
+        <v>0.1042864888942441</v>
       </c>
       <c r="W83">
-        <v>0.1948592730300358</v>
+        <v>0.1798592730300358</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3234588657702225</v>
+        <v>0.3476216296474802</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2089239539232619</v>
+        <v>0.1963386949392387</v>
       </c>
       <c r="C84">
-        <v>-7372.840876343511</v>
+        <v>-7092.118908298566</v>
       </c>
       <c r="D84">
-        <v>3386.645123656489</v>
+        <v>3667.367091701434</v>
       </c>
       <c r="E84">
         <v>9695.886</v>
@@ -8181,37 +8181,37 @@
         <v>824.2</v>
       </c>
       <c r="M84">
-        <v>2579.5406988</v>
+        <v>2400.2399088</v>
       </c>
       <c r="N84">
-        <v>-1755.3406988</v>
+        <v>-1576.0399088</v>
       </c>
       <c r="O84">
-        <v>-526.6022096400001</v>
+        <v>-472.81197264</v>
       </c>
       <c r="P84">
-        <v>-1228.73848916</v>
+        <v>-1103.22793616</v>
       </c>
       <c r="Q84">
-        <v>-1076.138489160001</v>
+        <v>-950.6279361600002</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2718330153829602</v>
+        <v>0.2702482432494986</v>
       </c>
       <c r="T84">
-        <v>5.216805918031973</v>
+        <v>5.183562199757473</v>
       </c>
       <c r="U84">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.09585427363678546</v>
+        <v>0.1030147024443143</v>
       </c>
       <c r="W84">
-        <v>0.1951146477491817</v>
+        <v>0.1801146477491817</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3195142454559515</v>
+        <v>0.3433823414810475</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2106239539232619</v>
+        <v>0.1978886949392387</v>
       </c>
       <c r="C85">
-        <v>-7553.54385207323</v>
+        <v>-7275.267592233577</v>
       </c>
       <c r="D85">
-        <v>3351.715147926769</v>
+        <v>3629.991407766423</v>
       </c>
       <c r="E85">
         <v>9841.659</v>
@@ -8263,37 +8263,37 @@
         <v>824.2</v>
       </c>
       <c r="M85">
-        <v>2610.9985122</v>
+        <v>2429.5111272</v>
       </c>
       <c r="N85">
-        <v>-1786.7985122</v>
+        <v>-1605.3111272</v>
       </c>
       <c r="O85">
-        <v>-536.03955366</v>
+        <v>-481.5933381599999</v>
       </c>
       <c r="P85">
-        <v>-1250.75895854</v>
+        <v>-1123.71778904</v>
       </c>
       <c r="Q85">
-        <v>-1098.15895854</v>
+        <v>-971.1177890399999</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2851290751113697</v>
+        <v>0.2834510810877044</v>
       </c>
       <c r="T85">
-        <v>5.523676854386796</v>
+        <v>5.488477623272619</v>
       </c>
       <c r="U85">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.09469940287007721</v>
+        <v>0.1017735614510093</v>
       </c>
       <c r="W85">
-        <v>0.1953638688606374</v>
+        <v>0.1803638688606373</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3156646762335906</v>
+        <v>0.3392452048366976</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2123239539232618</v>
+        <v>0.1994386949392387</v>
       </c>
       <c r="C86">
-        <v>-7733.533645616945</v>
+        <v>-7457.662139196489</v>
       </c>
       <c r="D86">
-        <v>3317.498354383054</v>
+        <v>3593.369860803509</v>
       </c>
       <c r="E86">
         <v>9987.431999999999</v>
@@ -8345,37 +8345,37 @@
         <v>824.2</v>
       </c>
       <c r="M86">
-        <v>2642.4563256</v>
+        <v>2458.7823456</v>
       </c>
       <c r="N86">
-        <v>-1818.2563256</v>
+        <v>-1634.5823456</v>
       </c>
       <c r="O86">
-        <v>-545.47689768</v>
+        <v>-490.3747036799999</v>
       </c>
       <c r="P86">
-        <v>-1272.77942792</v>
+        <v>-1144.20764192</v>
       </c>
       <c r="Q86">
-        <v>-1120.17942792</v>
+        <v>-991.6076419199999</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3000871423058302</v>
+        <v>0.2983042736556858</v>
       </c>
       <c r="T86">
-        <v>5.868906657785967</v>
+        <v>5.831507474727156</v>
       </c>
       <c r="U86">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.09357202902638581</v>
+        <v>0.1005619714337354</v>
       </c>
       <c r="W86">
-        <v>0.195607156136106</v>
+        <v>0.180607156136106</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3119067634212861</v>
+        <v>0.3352065714457846</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2140239539232618</v>
+        <v>0.2009886949392388</v>
       </c>
       <c r="C87">
-        <v>-7912.831878325624</v>
+        <v>-7639.325145787668</v>
       </c>
       <c r="D87">
-        <v>3283.973121674376</v>
+        <v>3557.479854212332</v>
       </c>
       <c r="E87">
         <v>10133.205</v>
@@ -8427,37 +8427,37 @@
         <v>824.2</v>
       </c>
       <c r="M87">
-        <v>2673.914139</v>
+        <v>2488.053564</v>
       </c>
       <c r="N87">
-        <v>-1849.714139</v>
+        <v>-1663.853564</v>
       </c>
       <c r="O87">
-        <v>-554.9142417</v>
+        <v>-499.1560692</v>
       </c>
       <c r="P87">
-        <v>-1294.7998973</v>
+        <v>-1164.6974948</v>
       </c>
       <c r="Q87">
-        <v>-1142.1998973</v>
+        <v>-1012.0974948</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3170396184595522</v>
+        <v>0.3151378918993982</v>
       </c>
       <c r="T87">
-        <v>6.260167101638365</v>
+        <v>6.220274639708966</v>
       </c>
       <c r="U87">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.09247118162607537</v>
+        <v>0.09937888941686787</v>
       </c>
       <c r="W87">
-        <v>0.195844719005093</v>
+        <v>0.1808447190050929</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.308237272086918</v>
+        <v>0.3312629647228928</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2157239539232619</v>
+        <v>0.2025386949392387</v>
       </c>
       <c r="C88">
-        <v>-8091.459306309142</v>
+        <v>-7820.278314769976</v>
       </c>
       <c r="D88">
-        <v>3251.118693690857</v>
+        <v>3522.299685230024</v>
       </c>
       <c r="E88">
         <v>10278.978</v>
@@ -8509,37 +8509,37 @@
         <v>824.2</v>
       </c>
       <c r="M88">
-        <v>2705.3719524</v>
+        <v>2517.3247824</v>
       </c>
       <c r="N88">
-        <v>-1881.1719524</v>
+        <v>-1693.1247824</v>
       </c>
       <c r="O88">
-        <v>-564.35158572</v>
+        <v>-507.9374347199999</v>
       </c>
       <c r="P88">
-        <v>-1316.82036668</v>
+        <v>-1185.18734768</v>
       </c>
       <c r="Q88">
-        <v>-1164.22036668</v>
+        <v>-1032.58734768</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3364138769209488</v>
+        <v>0.3343763127493553</v>
       </c>
       <c r="T88">
-        <v>6.707321894612535</v>
+        <v>6.664579971116749</v>
       </c>
       <c r="U88">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.09139593532809777</v>
+        <v>0.0982233209352764</v>
       </c>
       <c r="W88">
-        <v>0.1960767571561965</v>
+        <v>0.1810767571561965</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3046531177603259</v>
+        <v>0.3274110697842546</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2174239539232619</v>
+        <v>0.2040886949392388</v>
       </c>
       <c r="C89">
-        <v>-8269.435863288991</v>
+        <v>-8000.542498832126</v>
       </c>
       <c r="D89">
-        <v>3218.915136711009</v>
+        <v>3487.808501167875</v>
       </c>
       <c r="E89">
         <v>10424.751</v>
@@ -8591,37 +8591,37 @@
         <v>824.2</v>
       </c>
       <c r="M89">
-        <v>2736.8297658</v>
+        <v>2546.5960008</v>
       </c>
       <c r="N89">
-        <v>-1912.6297658</v>
+        <v>-1722.3960008</v>
       </c>
       <c r="O89">
-        <v>-573.78892974</v>
+        <v>-516.7188002400001</v>
       </c>
       <c r="P89">
-        <v>-1338.84083606</v>
+        <v>-1205.67720056</v>
       </c>
       <c r="Q89">
-        <v>-1186.24083606</v>
+        <v>-1053.07720056</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3587687905302526</v>
+        <v>0.3565744906531518</v>
       </c>
       <c r="T89">
-        <v>7.223269732659653</v>
+        <v>7.177239968894961</v>
       </c>
       <c r="U89">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.09034540733582078</v>
+        <v>0.09709431724636516</v>
       </c>
       <c r="W89">
-        <v>0.1963034610969299</v>
+        <v>0.1813034610969299</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3011513577860693</v>
+        <v>0.3236477241545506</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2191239539232618</v>
+        <v>0.2056386949392387</v>
       </c>
       <c r="C90">
-        <v>-8446.780700929108</v>
+        <v>-8180.137741805675</v>
       </c>
       <c r="D90">
-        <v>3187.343299070892</v>
+        <v>3453.986258194324</v>
       </c>
       <c r="E90">
         <v>10570.524</v>
@@ -8673,37 +8673,37 @@
         <v>824.2</v>
       </c>
       <c r="M90">
-        <v>2768.2875792</v>
+        <v>2575.8672192</v>
       </c>
       <c r="N90">
-        <v>-1944.0875792</v>
+        <v>-1751.6672192</v>
       </c>
       <c r="O90">
-        <v>-583.2262737599999</v>
+        <v>-525.50016576</v>
       </c>
       <c r="P90">
-        <v>-1360.86130544</v>
+        <v>-1226.16705344</v>
       </c>
       <c r="Q90">
-        <v>-1208.26130544</v>
+        <v>-1073.56705344</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3848495230744403</v>
+        <v>0.3824723648742478</v>
       </c>
       <c r="T90">
-        <v>7.825208877047958</v>
+        <v>7.775343299636208</v>
       </c>
       <c r="U90">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.08931875497973192</v>
+        <v>0.09599097273220193</v>
       </c>
       <c r="W90">
-        <v>0.1965250126753739</v>
+        <v>0.1815250126753739</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.297729183265773</v>
+        <v>0.3199699091073398</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2208239539232618</v>
+        <v>0.2071886949392387</v>
       </c>
       <c r="C91">
-        <v>-8623.512226816347</v>
+        <v>-8359.083317506946</v>
       </c>
       <c r="D91">
-        <v>3156.384773183651</v>
+        <v>3420.813682493053</v>
       </c>
       <c r="E91">
         <v>10716.297</v>
@@ -8755,37 +8755,37 @@
         <v>824.2</v>
       </c>
       <c r="M91">
-        <v>2799.7453926</v>
+        <v>2605.1384376</v>
       </c>
       <c r="N91">
-        <v>-1975.5453926</v>
+        <v>-1780.9384376</v>
       </c>
       <c r="O91">
-        <v>-592.6636177799999</v>
+        <v>-534.2815312799999</v>
       </c>
       <c r="P91">
-        <v>-1382.88177482</v>
+        <v>-1246.65690632</v>
       </c>
       <c r="Q91">
-        <v>-1230.28177482</v>
+        <v>-1094.05690632</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4156722069902985</v>
+        <v>0.4130789434991795</v>
       </c>
       <c r="T91">
-        <v>8.536591502234137</v>
+        <v>8.482192690512228</v>
       </c>
       <c r="U91">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.08831517346310573</v>
+        <v>0.09491242247678394</v>
       </c>
       <c r="W91">
-        <v>0.1967415855666618</v>
+        <v>0.1817415855666618</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2943839115436857</v>
+        <v>0.3163747415892798</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2225239539232619</v>
+        <v>0.2087386949392387</v>
       </c>
       <c r="C92">
-        <v>-8799.648140248799</v>
+        <v>-8537.397766361937</v>
       </c>
       <c r="D92">
-        <v>3126.0218597512</v>
+        <v>3388.272233638062</v>
       </c>
       <c r="E92">
         <v>10862.07</v>
@@ -8837,37 +8837,37 @@
         <v>824.2</v>
       </c>
       <c r="M92">
-        <v>2831.203206</v>
+        <v>2634.409656</v>
       </c>
       <c r="N92">
-        <v>-2007.003206</v>
+        <v>-1810.209656</v>
       </c>
       <c r="O92">
-        <v>-602.1009618000001</v>
+        <v>-543.0628967999999</v>
       </c>
       <c r="P92">
-        <v>-1404.9022442</v>
+        <v>-1267.1467592</v>
       </c>
       <c r="Q92">
-        <v>-1252.3022442</v>
+        <v>-1114.5467592</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4526594276893284</v>
+        <v>0.4498068378490975</v>
       </c>
       <c r="T92">
-        <v>9.390250652457551</v>
+        <v>9.330411959563451</v>
       </c>
       <c r="U92">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.08733389375796008</v>
+        <v>0.09385784000481967</v>
       </c>
       <c r="W92">
-        <v>0.1969533457270322</v>
+        <v>0.1819533457270322</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2911129791932003</v>
+        <v>0.3128594666827322</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2242239539232618</v>
+        <v>0.2102886949392387</v>
       </c>
       <c r="C93">
-        <v>-8975.205465978193</v>
+        <v>-8715.098929960528</v>
       </c>
       <c r="D93">
-        <v>3096.237534021806</v>
+        <v>3356.34407003947</v>
       </c>
       <c r="E93">
         <v>11007.843</v>
@@ -8919,37 +8919,37 @@
         <v>824.2</v>
       </c>
       <c r="M93">
-        <v>2862.6610194</v>
+        <v>2663.6808744</v>
       </c>
       <c r="N93">
-        <v>-2038.4610194</v>
+        <v>-1839.4808744</v>
       </c>
       <c r="O93">
-        <v>-611.53830582</v>
+        <v>-551.84426232</v>
       </c>
       <c r="P93">
-        <v>-1426.92271358</v>
+        <v>-1287.63661208</v>
       </c>
       <c r="Q93">
-        <v>-1274.32271358</v>
+        <v>-1135.03661208</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4978660307659205</v>
+        <v>0.4946964864989972</v>
       </c>
       <c r="T93">
-        <v>10.43361183606395</v>
+        <v>10.36712439951495</v>
       </c>
       <c r="U93">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.08637418063974076</v>
+        <v>0.09282643516960186</v>
       </c>
       <c r="W93">
-        <v>0.1971604518179439</v>
+        <v>0.1821604518179439</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2879139354658026</v>
+        <v>0.3094214505653395</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2259239539232619</v>
+        <v>0.2118386949392387</v>
       </c>
       <c r="C94">
-        <v>-9150.200586041579</v>
+        <v>-8892.203983675268</v>
       </c>
       <c r="D94">
-        <v>3067.015413958421</v>
+        <v>3325.012016324732</v>
       </c>
       <c r="E94">
         <v>11153.616</v>
@@ -9001,37 +9001,37 @@
         <v>824.2</v>
       </c>
       <c r="M94">
-        <v>2894.1188328</v>
+        <v>2692.9520928</v>
       </c>
       <c r="N94">
-        <v>-2069.9188328</v>
+        <v>-1868.7520928</v>
       </c>
       <c r="O94">
-        <v>-620.97564984</v>
+        <v>-560.62562784</v>
       </c>
       <c r="P94">
-        <v>-1448.94318296</v>
+        <v>-1308.12646496</v>
       </c>
       <c r="Q94">
-        <v>-1296.34318296</v>
+        <v>-1155.52646496</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5543742846116606</v>
+        <v>0.550808547311372</v>
       </c>
       <c r="T94">
-        <v>11.73781331557194</v>
+        <v>11.66301494945432</v>
       </c>
       <c r="U94">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.08543533085017835</v>
+        <v>0.09181745217862793</v>
       </c>
       <c r="W94">
-        <v>0.1973630556025315</v>
+        <v>0.1823630556025315</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2847844361672612</v>
+        <v>0.3060581739287598</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2276239539232618</v>
+        <v>0.2133886949392387</v>
       </c>
       <c r="C95">
-        <v>-9324.64926980726</v>
+        <v>-9068.729467470024</v>
       </c>
       <c r="D95">
-        <v>3038.339730192739</v>
+        <v>3294.259532529974</v>
       </c>
       <c r="E95">
         <v>11299.389</v>
@@ -9083,37 +9083,37 @@
         <v>824.2</v>
       </c>
       <c r="M95">
-        <v>2925.5766462</v>
+        <v>2722.2233112</v>
       </c>
       <c r="N95">
-        <v>-2101.3766462</v>
+        <v>-1898.0233112</v>
       </c>
       <c r="O95">
-        <v>-630.41299386</v>
+        <v>-569.4069933599999</v>
       </c>
       <c r="P95">
-        <v>-1470.96365234</v>
+        <v>-1328.61631784</v>
       </c>
       <c r="Q95">
-        <v>-1318.36365234</v>
+        <v>-1176.01631784</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.6270277538418979</v>
+        <v>0.6229526254987109</v>
       </c>
       <c r="T95">
-        <v>13.41464378922508</v>
+        <v>13.32915994223351</v>
       </c>
       <c r="U95">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.08451667137867107</v>
+        <v>0.09083016774659967</v>
       </c>
       <c r="W95">
-        <v>0.1975613023164828</v>
+        <v>0.1825613023164828</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2817222379289035</v>
+        <v>0.3027672258219989</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2293239539232619</v>
+        <v>0.2149386949392387</v>
       </c>
       <c r="C96">
-        <v>-9498.566702350859</v>
+        <v>-9244.691315014676</v>
       </c>
       <c r="D96">
-        <v>3010.195297649141</v>
+        <v>3264.070684985325</v>
       </c>
       <c r="E96">
         <v>11445.162</v>
@@ -9165,37 +9165,37 @@
         <v>824.2</v>
       </c>
       <c r="M96">
-        <v>2957.0344596</v>
+        <v>2751.4945296</v>
       </c>
       <c r="N96">
-        <v>-2132.834459600001</v>
+        <v>-1927.2945296</v>
       </c>
       <c r="O96">
-        <v>-639.8503378800002</v>
+        <v>-578.18835888</v>
       </c>
       <c r="P96">
-        <v>-1492.984121720001</v>
+        <v>-1349.10617072</v>
       </c>
       <c r="Q96">
-        <v>-1340.384121720001</v>
+        <v>-1196.50617072</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.7238990461488811</v>
+        <v>0.7191447297484962</v>
       </c>
       <c r="T96">
-        <v>15.65041775409593</v>
+        <v>15.55068659927243</v>
       </c>
       <c r="U96">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.08361755785336603</v>
+        <v>0.08986388936631669</v>
       </c>
       <c r="W96">
-        <v>0.1977553310152436</v>
+        <v>0.1827553310152436</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2787251928445533</v>
+        <v>0.2995462978877224</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2310239539232618</v>
+        <v>0.2164886949392388</v>
       </c>
       <c r="C97">
-        <v>-9671.967511268724</v>
+        <v>-9420.10488121344</v>
       </c>
       <c r="D97">
-        <v>2982.567488731276</v>
+        <v>3234.43011878656</v>
       </c>
       <c r="E97">
         <v>11590.935</v>
@@ -9247,37 +9247,37 @@
         <v>824.2</v>
       </c>
       <c r="M97">
-        <v>2988.492273</v>
+        <v>2780.765748</v>
       </c>
       <c r="N97">
-        <v>-2164.292273</v>
+        <v>-1956.565748</v>
       </c>
       <c r="O97">
-        <v>-649.2876818999999</v>
+        <v>-586.9697243999999</v>
       </c>
       <c r="P97">
-        <v>-1515.0045911</v>
+        <v>-1369.5960236</v>
       </c>
       <c r="Q97">
-        <v>-1362.4045911</v>
+        <v>-1216.9960236</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.8595188553786577</v>
+        <v>0.853813675698196</v>
       </c>
       <c r="T97">
-        <v>18.78050130491512</v>
+        <v>18.66082391912693</v>
       </c>
       <c r="U97">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.08273737303385693</v>
+        <v>0.08891795368877653</v>
       </c>
       <c r="W97">
-        <v>0.1979452748992937</v>
+        <v>0.1829452748992937</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2757912434461899</v>
+        <v>0.2963931789625884</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2327239539232618</v>
+        <v>0.2180386949392387</v>
       </c>
       <c r="C98">
-        <v>-9844.865792028217</v>
+        <v>-9594.984968246856</v>
       </c>
       <c r="D98">
-        <v>2955.442207971782</v>
+        <v>3205.323031753142</v>
       </c>
       <c r="E98">
         <v>11736.708</v>
@@ -9329,37 +9329,37 @@
         <v>824.2</v>
       </c>
       <c r="M98">
-        <v>3019.9500864</v>
+        <v>2810.0369664</v>
       </c>
       <c r="N98">
-        <v>-2195.7500864</v>
+        <v>-1985.8369664</v>
       </c>
       <c r="O98">
-        <v>-658.7250259200001</v>
+        <v>-595.7510899199999</v>
       </c>
       <c r="P98">
-        <v>-1537.02506048</v>
+        <v>-1390.08587648</v>
       </c>
       <c r="Q98">
-        <v>-1384.42506048</v>
+        <v>-1237.48587648</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.06294856922332</v>
+        <v>1.055817094622743</v>
       </c>
       <c r="T98">
-        <v>23.47562663114385</v>
+        <v>23.3260298989086</v>
       </c>
       <c r="U98">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.08187552539808758</v>
+        <v>0.08799172500451845</v>
       </c>
       <c r="W98">
-        <v>0.1981312616190927</v>
+        <v>0.1831312616190927</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2729184179936253</v>
+        <v>0.2933057500150614</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2344239539232618</v>
+        <v>0.2195886949392387</v>
       </c>
       <c r="C99">
-        <v>-10017.27513194714</v>
+        <v>-9769.345850220161</v>
       </c>
       <c r="D99">
-        <v>2928.805868052855</v>
+        <v>3176.735149779839</v>
       </c>
       <c r="E99">
         <v>11882.481</v>
@@ -9411,37 +9411,37 @@
         <v>824.2</v>
       </c>
       <c r="M99">
-        <v>3051.4078998</v>
+        <v>2839.3081848</v>
       </c>
       <c r="N99">
-        <v>-2227.207899800001</v>
+        <v>-2015.1081848</v>
       </c>
       <c r="O99">
-        <v>-668.1623699400002</v>
+        <v>-604.53245544</v>
       </c>
       <c r="P99">
-        <v>-1559.04552986</v>
+        <v>-1410.57572936</v>
       </c>
       <c r="Q99">
-        <v>-1406.445529860001</v>
+        <v>-1257.97572936</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.40199809229776</v>
+        <v>1.39248945949699</v>
       </c>
       <c r="T99">
-        <v>31.30083550819181</v>
+        <v>31.10137319854481</v>
       </c>
       <c r="U99">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.08103144781666399</v>
+        <v>0.08708459381890483</v>
       </c>
       <c r="W99">
-        <v>0.1983134135611639</v>
+        <v>0.1833134135611639</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2701048260555465</v>
+        <v>0.2902819793963495</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2361239539232619</v>
+        <v>0.2211386949392387</v>
       </c>
       <c r="C100">
-        <v>-10189.20863288807</v>
+        <v>-9943.201296504278</v>
       </c>
       <c r="D100">
-        <v>2902.64536711193</v>
+        <v>3148.65270349572</v>
       </c>
       <c r="E100">
         <v>12028.254</v>
@@ -9493,37 +9493,37 @@
         <v>824.2</v>
       </c>
       <c r="M100">
-        <v>3082.8657132</v>
+        <v>2868.5794032</v>
       </c>
       <c r="N100">
-        <v>-2258.6657132</v>
+        <v>-2044.3794032</v>
       </c>
       <c r="O100">
-        <v>-677.59971396</v>
+        <v>-613.3138209599999</v>
       </c>
       <c r="P100">
-        <v>-1581.06599924</v>
+        <v>-1431.06558224</v>
       </c>
       <c r="Q100">
-        <v>-1428.46599924</v>
+        <v>-1278.46558224</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.08009713844664</v>
+        <v>2.065834189245485</v>
       </c>
       <c r="T100">
-        <v>46.95125326228771</v>
+        <v>46.65205979781721</v>
       </c>
       <c r="U100">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.0802045963083307</v>
+        <v>0.0861959755146303</v>
       </c>
       <c r="W100">
-        <v>0.1984918481166623</v>
+        <v>0.1834918481166622</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2673486543611022</v>
+        <v>0.287319918382101</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2378239539232619</v>
+        <v>0.2226886949392388</v>
       </c>
       <c r="C101">
-        <v>-10360.67893274714</v>
+        <v>-10116.56459384971</v>
       </c>
       <c r="D101">
-        <v>2876.948067252859</v>
+        <v>3121.062406150289</v>
       </c>
       <c r="E101">
         <v>12174.027</v>
@@ -9575,37 +9575,37 @@
         <v>824.2</v>
       </c>
       <c r="M101">
-        <v>3114.3235266</v>
+        <v>2897.8506216</v>
       </c>
       <c r="N101">
-        <v>-2290.1235266</v>
+        <v>-2073.6506216</v>
       </c>
       <c r="O101">
-        <v>-687.0370579800001</v>
+        <v>-622.0951864799999</v>
       </c>
       <c r="P101">
-        <v>-1603.08646862</v>
+        <v>-1451.55543512</v>
       </c>
       <c r="Q101">
-        <v>-1450.48646862</v>
+        <v>-1298.95543512</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.11439427689328</v>
+        <v>4.085868378490971</v>
       </c>
       <c r="T101">
-        <v>93.90250652457541</v>
+        <v>93.30411959563442</v>
       </c>
       <c r="U101">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V101">
-        <v>0.07939444887087281</v>
+        <v>0.08532530909529061</v>
       </c>
       <c r="W101">
-        <v>0.1986666779336657</v>
+        <v>0.1836666779336657</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2646481629029093</v>
+        <v>0.2844176969843021</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/australia/australia_information_services.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_information_services.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08992829127703955</v>
+        <v>0.08969000640320841</v>
       </c>
       <c r="C2">
-        <v>13704.70972933795</v>
+        <v>13626.85963393936</v>
       </c>
       <c r="D2">
-        <v>12510.80972933795</v>
+        <v>12578.73263393936</v>
       </c>
       <c r="E2">
-        <v>-2257.5</v>
+        <v>-2111.727</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>145.773</v>
       </c>
       <c r="G2">
         <v>1193.9</v>
@@ -1457,28 +1457,28 @@
         <v>824.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>7.332381900000001</v>
       </c>
       <c r="N2">
-        <v>824.2</v>
+        <v>816.8676181000001</v>
       </c>
       <c r="O2">
-        <v>247.26</v>
+        <v>245.06028543</v>
       </c>
       <c r="P2">
-        <v>576.9400000000001</v>
+        <v>571.8073326700001</v>
       </c>
       <c r="Q2">
-        <v>729.54</v>
+        <v>724.40733267</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08992829127703955</v>
+        <v>0.09024030949819033</v>
       </c>
       <c r="T2">
-        <v>1.01912912879999</v>
+        <v>1.026335092336959</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>112.4054926817164</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08969000640320841</v>
+        <v>0.08945172152937732</v>
       </c>
       <c r="C3">
-        <v>13626.85963393936</v>
+        <v>13549.75109008495</v>
       </c>
       <c r="D3">
-        <v>12578.73263393936</v>
+        <v>12647.39709008495</v>
       </c>
       <c r="E3">
-        <v>-2111.727</v>
+        <v>-1965.954</v>
       </c>
       <c r="F3">
-        <v>145.773</v>
+        <v>291.546</v>
       </c>
       <c r="G3">
         <v>1193.9</v>
@@ -1539,28 +1539,28 @@
         <v>824.2</v>
       </c>
       <c r="M3">
-        <v>7.332381900000001</v>
+        <v>14.6647638</v>
       </c>
       <c r="N3">
-        <v>816.8676181000001</v>
+        <v>809.5352362000001</v>
       </c>
       <c r="O3">
-        <v>245.06028543</v>
+        <v>242.86057086</v>
       </c>
       <c r="P3">
-        <v>571.8073326700001</v>
+        <v>566.67466534</v>
       </c>
       <c r="Q3">
-        <v>724.40733267</v>
+        <v>719.27466534</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09024030949819033</v>
+        <v>0.09055869543814012</v>
       </c>
       <c r="T3">
-        <v>1.026335092336959</v>
+        <v>1.033688116354275</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>112.4054926817164</v>
+        <v>56.20274634085822</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08945172152937732</v>
+        <v>0.08921343665554619</v>
       </c>
       <c r="C4">
-        <v>13549.75109008495</v>
+        <v>13473.39630831574</v>
       </c>
       <c r="D4">
-        <v>12647.39709008495</v>
+        <v>12716.81530831574</v>
       </c>
       <c r="E4">
-        <v>-1965.954</v>
+        <v>-1820.181</v>
       </c>
       <c r="F4">
-        <v>291.546</v>
+        <v>437.319</v>
       </c>
       <c r="G4">
         <v>1193.9</v>
@@ -1621,28 +1621,28 @@
         <v>824.2</v>
       </c>
       <c r="M4">
-        <v>14.6647638</v>
+        <v>21.9971457</v>
       </c>
       <c r="N4">
-        <v>809.5352362000001</v>
+        <v>802.2028543</v>
       </c>
       <c r="O4">
-        <v>242.86057086</v>
+        <v>240.66085629</v>
       </c>
       <c r="P4">
-        <v>566.67466534</v>
+        <v>561.54199801</v>
       </c>
       <c r="Q4">
-        <v>719.27466534</v>
+        <v>714.14199801</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09055869543814012</v>
+        <v>0.09088364603664556</v>
       </c>
       <c r="T4">
-        <v>1.033688116354275</v>
+        <v>1.041192749114216</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>56.20274634085822</v>
+        <v>37.46849756057214</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08921343665554619</v>
+        <v>0.08897515178171507</v>
       </c>
       <c r="C5">
-        <v>13473.39630831574</v>
+        <v>13397.80776873398</v>
       </c>
       <c r="D5">
-        <v>12716.81530831574</v>
+        <v>12786.99976873399</v>
       </c>
       <c r="E5">
-        <v>-1820.181</v>
+        <v>-1674.408</v>
       </c>
       <c r="F5">
-        <v>437.319</v>
+        <v>583.092</v>
       </c>
       <c r="G5">
         <v>1193.9</v>
@@ -1703,28 +1703,28 @@
         <v>824.2</v>
       </c>
       <c r="M5">
-        <v>21.9971457</v>
+        <v>29.3295276</v>
       </c>
       <c r="N5">
-        <v>802.2028543</v>
+        <v>794.8704724</v>
       </c>
       <c r="O5">
-        <v>240.66085629</v>
+        <v>238.46114172</v>
       </c>
       <c r="P5">
-        <v>561.54199801</v>
+        <v>556.40933068</v>
       </c>
       <c r="Q5">
-        <v>714.14199801</v>
+        <v>709.0093306799999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09088364603664556</v>
+        <v>0.09121536643928653</v>
       </c>
       <c r="T5">
-        <v>1.041192749114216</v>
+        <v>1.048853728389989</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>37.46849756057214</v>
+        <v>28.10137317042911</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08897515178171507</v>
+        <v>0.08873686690788395</v>
       </c>
       <c r="C6">
-        <v>13397.80776873398</v>
+        <v>13322.99822848311</v>
       </c>
       <c r="D6">
-        <v>12786.99976873399</v>
+        <v>12857.96322848312</v>
       </c>
       <c r="E6">
-        <v>-1674.408</v>
+        <v>-1528.635</v>
       </c>
       <c r="F6">
-        <v>583.092</v>
+        <v>728.865</v>
       </c>
       <c r="G6">
         <v>1193.9</v>
@@ -1785,28 +1785,28 @@
         <v>824.2</v>
       </c>
       <c r="M6">
-        <v>29.3295276</v>
+        <v>36.6619095</v>
       </c>
       <c r="N6">
-        <v>794.8704724</v>
+        <v>787.5380905000001</v>
       </c>
       <c r="O6">
-        <v>238.46114172</v>
+        <v>236.26142715</v>
       </c>
       <c r="P6">
-        <v>556.40933068</v>
+        <v>551.27666335</v>
       </c>
       <c r="Q6">
-        <v>709.0093306799999</v>
+        <v>703.8766633499999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09121536643928653</v>
+        <v>0.09155407042935153</v>
       </c>
       <c r="T6">
-        <v>1.048853728389989</v>
+        <v>1.056675991439989</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>28.10137317042911</v>
+        <v>22.48109853634329</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08873686690788395</v>
+        <v>0.08849858203405284</v>
       </c>
       <c r="C7">
-        <v>13322.99822848311</v>
+        <v>13248.98072947799</v>
       </c>
       <c r="D7">
-        <v>12857.96322848312</v>
+        <v>12929.71872947799</v>
       </c>
       <c r="E7">
-        <v>-1528.635</v>
+        <v>-1382.862</v>
       </c>
       <c r="F7">
-        <v>728.865</v>
+        <v>874.638</v>
       </c>
       <c r="G7">
         <v>1193.9</v>
@@ -1867,28 +1867,28 @@
         <v>824.2</v>
       </c>
       <c r="M7">
-        <v>36.6619095</v>
+        <v>43.99429140000001</v>
       </c>
       <c r="N7">
-        <v>787.5380905000001</v>
+        <v>780.2057086</v>
       </c>
       <c r="O7">
-        <v>236.26142715</v>
+        <v>234.06171258</v>
       </c>
       <c r="P7">
-        <v>551.27666335</v>
+        <v>546.14399602</v>
       </c>
       <c r="Q7">
-        <v>703.8766633499999</v>
+        <v>698.7439960199999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09155407042935153</v>
+        <v>0.09189998088729025</v>
       </c>
       <c r="T7">
-        <v>1.056675991439989</v>
+        <v>1.064664685618712</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.48109853634329</v>
+        <v>18.73424878028607</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08849858203405284</v>
+        <v>0.08826029716022173</v>
       </c>
       <c r="C8">
-        <v>13248.98072947799</v>
+        <v>13175.76860639554</v>
       </c>
       <c r="D8">
-        <v>12929.71872947799</v>
+        <v>13002.27960639554</v>
       </c>
       <c r="E8">
-        <v>-1382.862</v>
+        <v>-1237.089</v>
       </c>
       <c r="F8">
-        <v>874.6379999999999</v>
+        <v>1020.411</v>
       </c>
       <c r="G8">
         <v>1193.9</v>
@@ -1949,28 +1949,28 @@
         <v>824.2</v>
       </c>
       <c r="M8">
-        <v>43.9942914</v>
+        <v>51.3266733</v>
       </c>
       <c r="N8">
-        <v>780.2057086000001</v>
+        <v>772.8733267</v>
       </c>
       <c r="O8">
-        <v>234.06171258</v>
+        <v>231.86199801</v>
       </c>
       <c r="P8">
-        <v>546.14399602</v>
+        <v>541.01132869</v>
       </c>
       <c r="Q8">
-        <v>698.7439960199999</v>
+        <v>693.6113286899999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09189998088729025</v>
+        <v>0.09225333027980831</v>
       </c>
       <c r="T8">
-        <v>1.064664685618712</v>
+        <v>1.072825179672247</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.73424878028607</v>
+        <v>16.05792752595949</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08826029716022173</v>
+        <v>0.08802201228639062</v>
       </c>
       <c r="C9">
-        <v>13175.76860639554</v>
+        <v>13103.37549493594</v>
       </c>
       <c r="D9">
-        <v>13002.27960639554</v>
+        <v>13075.65949493594</v>
       </c>
       <c r="E9">
-        <v>-1237.089</v>
+        <v>-1091.316</v>
       </c>
       <c r="F9">
-        <v>1020.411</v>
+        <v>1166.184</v>
       </c>
       <c r="G9">
         <v>1193.9</v>
@@ -2031,28 +2031,28 @@
         <v>824.2</v>
       </c>
       <c r="M9">
-        <v>51.32667330000001</v>
+        <v>58.6590552</v>
       </c>
       <c r="N9">
-        <v>772.8733267</v>
+        <v>765.5409448</v>
       </c>
       <c r="O9">
-        <v>231.86199801</v>
+        <v>229.66228344</v>
       </c>
       <c r="P9">
-        <v>541.01132869</v>
+        <v>535.87866136</v>
       </c>
       <c r="Q9">
-        <v>693.6113286899999</v>
+        <v>688.4786613599999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09225333027980831</v>
+        <v>0.09261436118085936</v>
       </c>
       <c r="T9">
-        <v>1.072825179672247</v>
+        <v>1.081163075770424</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.05792752595949</v>
+        <v>14.05068658521455</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08802201228639062</v>
+        <v>0.08778372741255949</v>
       </c>
       <c r="C10">
-        <v>13103.37549493594</v>
+        <v>13031.81534036513</v>
       </c>
       <c r="D10">
-        <v>13075.65949493594</v>
+        <v>13149.87234036513</v>
       </c>
       <c r="E10">
-        <v>-1091.316</v>
+        <v>-945.5430000000001</v>
       </c>
       <c r="F10">
-        <v>1166.184</v>
+        <v>1311.957</v>
       </c>
       <c r="G10">
         <v>1193.9</v>
@@ -2113,28 +2113,28 @@
         <v>824.2</v>
       </c>
       <c r="M10">
-        <v>58.6590552</v>
+        <v>65.9914371</v>
       </c>
       <c r="N10">
-        <v>765.5409448</v>
+        <v>758.2085629000001</v>
       </c>
       <c r="O10">
-        <v>229.66228344</v>
+        <v>227.46256887</v>
       </c>
       <c r="P10">
-        <v>535.87866136</v>
+        <v>530.74599403</v>
       </c>
       <c r="Q10">
-        <v>688.4786613599999</v>
+        <v>683.3459940299999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09261436118085936</v>
+        <v>0.09298332682698844</v>
       </c>
       <c r="T10">
-        <v>1.081163075770424</v>
+        <v>1.089684222332296</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.05068658521455</v>
+        <v>12.48949918685738</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08778372741255949</v>
+        <v>0.08754544253872835</v>
       </c>
       <c r="C11">
-        <v>13031.81534036513</v>
+        <v>12961.10240634988</v>
       </c>
       <c r="D11">
-        <v>13149.87234036513</v>
+        <v>13224.93240634988</v>
       </c>
       <c r="E11">
-        <v>-945.5430000000001</v>
+        <v>-799.7700000000002</v>
       </c>
       <c r="F11">
-        <v>1311.957</v>
+        <v>1457.73</v>
       </c>
       <c r="G11">
         <v>1193.9</v>
@@ -2195,28 +2195,28 @@
         <v>824.2</v>
       </c>
       <c r="M11">
-        <v>65.9914371</v>
+        <v>73.323819</v>
       </c>
       <c r="N11">
-        <v>758.2085629000001</v>
+        <v>750.8761810000001</v>
       </c>
       <c r="O11">
-        <v>227.46256887</v>
+        <v>225.2628543</v>
       </c>
       <c r="P11">
-        <v>530.74599403</v>
+        <v>525.6133267</v>
       </c>
       <c r="Q11">
-        <v>683.3459940299999</v>
+        <v>678.2133266999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09298332682698844</v>
+        <v>0.09336049170969818</v>
       </c>
       <c r="T11">
-        <v>1.089684222332296</v>
+        <v>1.098394727706655</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.48949918685738</v>
+        <v>11.24054926817164</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08754544253872835</v>
+        <v>0.08730715766489726</v>
       </c>
       <c r="C12">
-        <v>12961.10240634988</v>
+        <v>12891.25128409717</v>
       </c>
       <c r="D12">
-        <v>13224.93240634988</v>
+        <v>13300.85428409717</v>
       </c>
       <c r="E12">
-        <v>-799.77</v>
+        <v>-653.9970000000001</v>
       </c>
       <c r="F12">
-        <v>1457.73</v>
+        <v>1603.503</v>
       </c>
       <c r="G12">
         <v>1193.9</v>
@@ -2277,28 +2277,28 @@
         <v>824.2</v>
       </c>
       <c r="M12">
-        <v>73.323819</v>
+        <v>80.6562009</v>
       </c>
       <c r="N12">
-        <v>750.8761810000001</v>
+        <v>743.5437991</v>
       </c>
       <c r="O12">
-        <v>225.2628543</v>
+        <v>223.06313973</v>
       </c>
       <c r="P12">
-        <v>525.6133267</v>
+        <v>520.48065937</v>
       </c>
       <c r="Q12">
-        <v>678.2133266999999</v>
+        <v>673.0806593699999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09336049170969818</v>
+        <v>0.09374613220774972</v>
       </c>
       <c r="T12">
-        <v>1.098394727706655</v>
+        <v>1.10730097477482</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.24054926817164</v>
+        <v>10.21868115288331</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08730715766489726</v>
+        <v>0.08706887279106613</v>
       </c>
       <c r="C13">
-        <v>12891.25128409717</v>
+        <v>12822.27690181028</v>
       </c>
       <c r="D13">
-        <v>13300.85428409717</v>
+        <v>13377.65290181028</v>
       </c>
       <c r="E13">
-        <v>-653.9970000000001</v>
+        <v>-508.2240000000002</v>
       </c>
       <c r="F13">
-        <v>1603.503</v>
+        <v>1749.276</v>
       </c>
       <c r="G13">
         <v>1193.9</v>
@@ -2359,28 +2359,28 @@
         <v>824.2</v>
       </c>
       <c r="M13">
-        <v>80.6562009</v>
+        <v>87.9885828</v>
       </c>
       <c r="N13">
-        <v>743.5437991</v>
+        <v>736.2114172</v>
       </c>
       <c r="O13">
-        <v>223.06313973</v>
+        <v>220.86342516</v>
       </c>
       <c r="P13">
-        <v>520.48065937</v>
+        <v>515.34799204</v>
       </c>
       <c r="Q13">
-        <v>673.0806593699999</v>
+        <v>667.9479920399999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09374613220774972</v>
+        <v>0.09414053726257515</v>
       </c>
       <c r="T13">
-        <v>1.10730097477482</v>
+        <v>1.116409636549079</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.21868115288331</v>
+        <v>9.367124390143037</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08706887279106613</v>
+        <v>0.08696708791723501</v>
       </c>
       <c r="C14">
-        <v>12822.27690181028</v>
+        <v>12709.57990455074</v>
       </c>
       <c r="D14">
-        <v>13377.65290181028</v>
+        <v>13410.72890455075</v>
       </c>
       <c r="E14">
-        <v>-508.2240000000002</v>
+        <v>-362.451</v>
       </c>
       <c r="F14">
-        <v>1749.276</v>
+        <v>1895.049</v>
       </c>
       <c r="G14">
         <v>1193.9</v>
@@ -2441,45 +2441,45 @@
         <v>824.2</v>
       </c>
       <c r="M14">
-        <v>87.9885828</v>
+        <v>98.1635382</v>
       </c>
       <c r="N14">
-        <v>736.2114172</v>
+        <v>726.0364618000001</v>
       </c>
       <c r="O14">
-        <v>220.86342516</v>
+        <v>217.81093854</v>
       </c>
       <c r="P14">
-        <v>515.34799204</v>
+        <v>508.22552326</v>
       </c>
       <c r="Q14">
-        <v>667.9479920399999</v>
+        <v>660.82552326</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09414053726257515</v>
+        <v>0.09454400910027012</v>
       </c>
       <c r="T14">
-        <v>1.116409636549079</v>
+        <v>1.125727692846885</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.03521</v>
+        <v>0.03626</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>9.367124390143037</v>
+        <v>8.396192874800025</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08696708791723501</v>
+        <v>0.08673930304340388</v>
       </c>
       <c r="C15">
-        <v>12709.57990455074</v>
+        <v>12638.42373884975</v>
       </c>
       <c r="D15">
-        <v>13410.72890455075</v>
+        <v>13485.34573884976</v>
       </c>
       <c r="E15">
-        <v>-362.451</v>
+        <v>-216.6779999999999</v>
       </c>
       <c r="F15">
-        <v>1895.049</v>
+        <v>2040.822</v>
       </c>
       <c r="G15">
         <v>1193.9</v>
@@ -2523,28 +2523,28 @@
         <v>824.2</v>
       </c>
       <c r="M15">
-        <v>98.1635382</v>
+        <v>105.7145796</v>
       </c>
       <c r="N15">
-        <v>726.0364618000001</v>
+        <v>718.4854204000001</v>
       </c>
       <c r="O15">
-        <v>217.81093854</v>
+        <v>215.54562612</v>
       </c>
       <c r="P15">
-        <v>508.22552326</v>
+        <v>502.9397942800001</v>
       </c>
       <c r="Q15">
-        <v>660.82552326</v>
+        <v>655.53979428</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09454400910027012</v>
+        <v>0.094956864003958</v>
       </c>
       <c r="T15">
-        <v>1.125727692846885</v>
+        <v>1.13526244812836</v>
       </c>
       <c r="U15">
         <v>0.05180000000000001</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.396192874800025</v>
+        <v>7.796464812314308</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08673930304340388</v>
+        <v>0.08651151816957277</v>
       </c>
       <c r="C16">
-        <v>12638.42373884975</v>
+        <v>12568.10254992932</v>
       </c>
       <c r="D16">
-        <v>13485.34573884976</v>
+        <v>13560.79754992932</v>
       </c>
       <c r="E16">
-        <v>-216.6779999999999</v>
+        <v>-70.90499999999975</v>
       </c>
       <c r="F16">
-        <v>2040.822</v>
+        <v>2186.595</v>
       </c>
       <c r="G16">
         <v>1193.9</v>
@@ -2605,28 +2605,28 @@
         <v>824.2</v>
       </c>
       <c r="M16">
-        <v>105.7145796</v>
+        <v>113.265621</v>
       </c>
       <c r="N16">
-        <v>718.4854204000001</v>
+        <v>710.934379</v>
       </c>
       <c r="O16">
-        <v>215.54562612</v>
+        <v>213.2803137</v>
       </c>
       <c r="P16">
-        <v>502.9397942800001</v>
+        <v>497.6540653000001</v>
       </c>
       <c r="Q16">
-        <v>655.53979428</v>
+        <v>650.2540653</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.094956864003958</v>
+        <v>0.09537943314067385</v>
       </c>
       <c r="T16">
-        <v>1.13526244812836</v>
+        <v>1.145021550592929</v>
       </c>
       <c r="U16">
         <v>0.05180000000000001</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.796464812314308</v>
+        <v>7.276700491493354</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08651151816957277</v>
+        <v>0.08628373329574165</v>
       </c>
       <c r="C17">
-        <v>12568.10254992932</v>
+        <v>12498.63043197482</v>
       </c>
       <c r="D17">
-        <v>13560.79754992932</v>
+        <v>13637.09843197482</v>
       </c>
       <c r="E17">
-        <v>-70.9050000000002</v>
+        <v>74.86799999999994</v>
       </c>
       <c r="F17">
-        <v>2186.595</v>
+        <v>2332.368</v>
       </c>
       <c r="G17">
         <v>1193.9</v>
@@ -2687,28 +2687,28 @@
         <v>824.2</v>
       </c>
       <c r="M17">
-        <v>113.265621</v>
+        <v>120.8166624</v>
       </c>
       <c r="N17">
-        <v>710.934379</v>
+        <v>703.3833376</v>
       </c>
       <c r="O17">
-        <v>213.2803137</v>
+        <v>211.01500128</v>
       </c>
       <c r="P17">
-        <v>497.6540653000001</v>
+        <v>492.36833632</v>
       </c>
       <c r="Q17">
-        <v>650.2540653</v>
+        <v>644.9683363199999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09537943314067385</v>
+        <v>0.0958120634473115</v>
       </c>
       <c r="T17">
-        <v>1.145021550592929</v>
+        <v>1.155013012639988</v>
       </c>
       <c r="U17">
         <v>0.05180000000000001</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.276700491493355</v>
+        <v>6.82190671077502</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08628373329574165</v>
+        <v>0.08625824842191053</v>
       </c>
       <c r="C18">
-        <v>12498.63043197482</v>
+        <v>12361.44751549344</v>
       </c>
       <c r="D18">
-        <v>13637.09843197482</v>
+        <v>13645.68851549344</v>
       </c>
       <c r="E18">
-        <v>74.86799999999994</v>
+        <v>220.6410000000001</v>
       </c>
       <c r="F18">
-        <v>2332.368</v>
+        <v>2478.141</v>
       </c>
       <c r="G18">
         <v>1193.9</v>
@@ -2769,45 +2769,45 @@
         <v>824.2</v>
       </c>
       <c r="M18">
-        <v>120.8166624</v>
+        <v>132.5805435</v>
       </c>
       <c r="N18">
-        <v>703.3833376</v>
+        <v>691.6194565000001</v>
       </c>
       <c r="O18">
-        <v>211.01500128</v>
+        <v>207.48583695</v>
       </c>
       <c r="P18">
-        <v>492.36833632</v>
+        <v>484.13361955</v>
       </c>
       <c r="Q18">
-        <v>644.9683363199999</v>
+        <v>636.73361955</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0958120634473115</v>
+        <v>0.09625511858061511</v>
       </c>
       <c r="T18">
-        <v>1.155013012639988</v>
+        <v>1.165245232808663</v>
       </c>
       <c r="U18">
-        <v>0.05180000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.03626</v>
+        <v>0.03745</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.82190671077502</v>
+        <v>6.216598440781019</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08625824842191053</v>
+        <v>0.0860423635480794</v>
       </c>
       <c r="C19">
-        <v>12361.44751549344</v>
+        <v>12288.87841018981</v>
       </c>
       <c r="D19">
-        <v>13645.68851549344</v>
+        <v>13718.89241018981</v>
       </c>
       <c r="E19">
-        <v>220.6410000000001</v>
+        <v>366.4140000000002</v>
       </c>
       <c r="F19">
-        <v>2478.141</v>
+        <v>2623.914</v>
       </c>
       <c r="G19">
         <v>1193.9</v>
@@ -2851,28 +2851,28 @@
         <v>824.2</v>
       </c>
       <c r="M19">
-        <v>132.5805435</v>
+        <v>140.379399</v>
       </c>
       <c r="N19">
-        <v>691.6194565000001</v>
+        <v>683.820601</v>
       </c>
       <c r="O19">
-        <v>207.48583695</v>
+        <v>205.1461803</v>
       </c>
       <c r="P19">
-        <v>484.13361955</v>
+        <v>478.6744207</v>
       </c>
       <c r="Q19">
-        <v>636.73361955</v>
+        <v>631.2744207</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09625511858061511</v>
+        <v>0.0967089799366822</v>
       </c>
       <c r="T19">
-        <v>1.165245232808663</v>
+        <v>1.175727019322915</v>
       </c>
       <c r="U19">
         <v>0.05350000000000001</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.216598440781019</v>
+        <v>5.871231860737628</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08604236354807941</v>
+        <v>0.08593287867424829</v>
       </c>
       <c r="C20">
-        <v>12288.8784101898</v>
+        <v>12180.53136253237</v>
       </c>
       <c r="D20">
-        <v>13718.8924101898</v>
+        <v>13756.31836253237</v>
       </c>
       <c r="E20">
-        <v>366.4139999999998</v>
+        <v>512.1869999999999</v>
       </c>
       <c r="F20">
-        <v>2623.914</v>
+        <v>2769.687</v>
       </c>
       <c r="G20">
         <v>1193.9</v>
@@ -2933,45 +2933,45 @@
         <v>824.2</v>
       </c>
       <c r="M20">
-        <v>140.379399</v>
+        <v>150.3940041</v>
       </c>
       <c r="N20">
-        <v>683.820601</v>
+        <v>673.8059959</v>
       </c>
       <c r="O20">
-        <v>205.1461803</v>
+        <v>202.14179877</v>
       </c>
       <c r="P20">
-        <v>478.6744207</v>
+        <v>471.66419713</v>
       </c>
       <c r="Q20">
-        <v>631.2744207</v>
+        <v>624.26419713</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0967089799366822</v>
+        <v>0.09717404774598554</v>
       </c>
       <c r="T20">
-        <v>1.175727019322915</v>
+        <v>1.186467615380728</v>
       </c>
       <c r="U20">
-        <v>0.05350000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>5.871231860737629</v>
+        <v>5.480271669952831</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08593287867424829</v>
+        <v>0.08572259380041719</v>
       </c>
       <c r="C21">
-        <v>12180.53136253237</v>
+        <v>12107.21722343973</v>
       </c>
       <c r="D21">
-        <v>13756.31836253237</v>
+        <v>13828.77722343973</v>
       </c>
       <c r="E21">
-        <v>512.1869999999999</v>
+        <v>657.96</v>
       </c>
       <c r="F21">
-        <v>2769.687</v>
+        <v>2915.46</v>
       </c>
       <c r="G21">
         <v>1193.9</v>
@@ -3015,28 +3015,28 @@
         <v>824.2</v>
       </c>
       <c r="M21">
-        <v>150.3940041</v>
+        <v>158.309478</v>
       </c>
       <c r="N21">
-        <v>673.8059959</v>
+        <v>665.890522</v>
       </c>
       <c r="O21">
-        <v>202.14179877</v>
+        <v>199.7671566</v>
       </c>
       <c r="P21">
-        <v>471.66419713</v>
+        <v>466.1233654</v>
       </c>
       <c r="Q21">
-        <v>624.26419713</v>
+        <v>618.7233653999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09717404774598554</v>
+        <v>0.09765074225052148</v>
       </c>
       <c r="T21">
-        <v>1.186467615380728</v>
+        <v>1.197476726339988</v>
       </c>
       <c r="U21">
         <v>0.05430000000000001</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.480271669952831</v>
+        <v>5.20625808645519</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08572259380041719</v>
+        <v>0.08551230892658608</v>
       </c>
       <c r="C22">
-        <v>12107.21722343973</v>
+        <v>12034.67045360039</v>
       </c>
       <c r="D22">
-        <v>13828.77722343973</v>
+        <v>13902.00345360039</v>
       </c>
       <c r="E22">
-        <v>657.96</v>
+        <v>803.7330000000002</v>
       </c>
       <c r="F22">
-        <v>2915.46</v>
+        <v>3061.233</v>
       </c>
       <c r="G22">
         <v>1193.9</v>
@@ -3097,28 +3097,28 @@
         <v>824.2</v>
       </c>
       <c r="M22">
-        <v>158.309478</v>
+        <v>166.2249519</v>
       </c>
       <c r="N22">
-        <v>665.890522</v>
+        <v>657.9750481</v>
       </c>
       <c r="O22">
-        <v>199.7671566</v>
+        <v>197.39251443</v>
       </c>
       <c r="P22">
-        <v>466.1233654</v>
+        <v>460.58253367</v>
       </c>
       <c r="Q22">
-        <v>618.7233653999999</v>
+        <v>613.1825336699999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09765074225052148</v>
+        <v>0.09813950497036211</v>
       </c>
       <c r="T22">
-        <v>1.197476726339988</v>
+        <v>1.208764548969102</v>
       </c>
       <c r="U22">
         <v>0.05430000000000001</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.20625808645519</v>
+        <v>4.958341034719227</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08551230892658607</v>
+        <v>0.08530202405275494</v>
       </c>
       <c r="C23">
-        <v>12034.67045360039</v>
+        <v>11962.90330804309</v>
       </c>
       <c r="D23">
-        <v>13902.0034536004</v>
+        <v>13976.00930804309</v>
       </c>
       <c r="E23">
-        <v>803.7329999999997</v>
+        <v>949.5059999999999</v>
       </c>
       <c r="F23">
-        <v>3061.233</v>
+        <v>3207.006</v>
       </c>
       <c r="G23">
         <v>1193.9</v>
@@ -3179,28 +3179,28 @@
         <v>824.2</v>
       </c>
       <c r="M23">
-        <v>166.2249519</v>
+        <v>174.1404258</v>
       </c>
       <c r="N23">
-        <v>657.9750481000001</v>
+        <v>650.0595742</v>
       </c>
       <c r="O23">
-        <v>197.39251443</v>
+        <v>195.01787226</v>
       </c>
       <c r="P23">
-        <v>460.5825336700001</v>
+        <v>455.0417019400001</v>
       </c>
       <c r="Q23">
-        <v>613.18253367</v>
+        <v>607.64170194</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0981395049703621</v>
+        <v>0.09864080006763454</v>
       </c>
       <c r="T23">
-        <v>1.208764548969101</v>
+        <v>1.22034180294768</v>
       </c>
       <c r="U23">
         <v>0.05430000000000001</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.958341034719229</v>
+        <v>4.732961896777445</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08530202405275494</v>
+        <v>0.08509173917892382</v>
       </c>
       <c r="C24">
-        <v>11962.90330804309</v>
+        <v>11891.92830414658</v>
       </c>
       <c r="D24">
-        <v>13976.00930804309</v>
+        <v>14050.80730414658</v>
       </c>
       <c r="E24">
-        <v>949.5059999999999</v>
+        <v>1095.279</v>
       </c>
       <c r="F24">
-        <v>3207.006</v>
+        <v>3352.779</v>
       </c>
       <c r="G24">
         <v>1193.9</v>
@@ -3261,28 +3261,28 @@
         <v>824.2</v>
       </c>
       <c r="M24">
-        <v>174.1404258</v>
+        <v>182.0558997</v>
       </c>
       <c r="N24">
-        <v>650.0595742</v>
+        <v>642.1441003</v>
       </c>
       <c r="O24">
-        <v>195.01787226</v>
+        <v>192.64323009</v>
       </c>
       <c r="P24">
-        <v>455.0417019400001</v>
+        <v>449.50087021</v>
       </c>
       <c r="Q24">
-        <v>607.64170194</v>
+        <v>602.1008702099999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09864080006763454</v>
+        <v>0.09915511581678418</v>
       </c>
       <c r="T24">
-        <v>1.22034180294768</v>
+        <v>1.232219764821805</v>
       </c>
       <c r="U24">
         <v>0.05430000000000001</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.732961896777445</v>
+        <v>4.527180944743643</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08509173917892382</v>
+        <v>0.08488145430509272</v>
       </c>
       <c r="C25">
-        <v>11891.92830414658</v>
+        <v>11821.75822869774</v>
       </c>
       <c r="D25">
-        <v>14050.80730414658</v>
+        <v>14126.41022869774</v>
       </c>
       <c r="E25">
-        <v>1095.279</v>
+        <v>1241.052</v>
       </c>
       <c r="F25">
-        <v>3352.779</v>
+        <v>3498.552</v>
       </c>
       <c r="G25">
         <v>1193.9</v>
@@ -3343,28 +3343,28 @@
         <v>824.2</v>
       </c>
       <c r="M25">
-        <v>182.0558997</v>
+        <v>189.9713736</v>
       </c>
       <c r="N25">
-        <v>642.1441003</v>
+        <v>634.2286264000001</v>
       </c>
       <c r="O25">
-        <v>192.64323009</v>
+        <v>190.26858792</v>
       </c>
       <c r="P25">
-        <v>449.50087021</v>
+        <v>443.96003848</v>
       </c>
       <c r="Q25">
-        <v>602.1008702099999</v>
+        <v>596.56003848</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09915511581678418</v>
+        <v>0.09968296619091147</v>
       </c>
       <c r="T25">
-        <v>1.232219764821805</v>
+        <v>1.244410304639987</v>
       </c>
       <c r="U25">
         <v>0.05430000000000001</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.527180944743643</v>
+        <v>4.338548405379325</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08488145430509272</v>
+        <v>0.08484616943126159</v>
       </c>
       <c r="C26">
-        <v>11821.75822869774</v>
+        <v>11688.75084975268</v>
       </c>
       <c r="D26">
-        <v>14126.41022869774</v>
+        <v>14139.17584975268</v>
       </c>
       <c r="E26">
-        <v>1241.052</v>
+        <v>1386.825</v>
       </c>
       <c r="F26">
-        <v>3498.552</v>
+        <v>3644.325</v>
       </c>
       <c r="G26">
         <v>1193.9</v>
@@ -3425,45 +3425,45 @@
         <v>824.2</v>
       </c>
       <c r="M26">
-        <v>189.9713736</v>
+        <v>201.5311725</v>
       </c>
       <c r="N26">
-        <v>634.2286264000001</v>
+        <v>622.6688275</v>
       </c>
       <c r="O26">
-        <v>190.26858792</v>
+        <v>186.80064825</v>
       </c>
       <c r="P26">
-        <v>443.96003848</v>
+        <v>435.86817925</v>
       </c>
       <c r="Q26">
-        <v>596.56003848</v>
+        <v>588.4681792499999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09968296619091147</v>
+        <v>0.1002248925750154</v>
       </c>
       <c r="T26">
-        <v>1.244410304639987</v>
+        <v>1.256925925519987</v>
       </c>
       <c r="U26">
-        <v>0.05430000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.338548405379325</v>
+        <v>4.089689896484872</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08484616943126159</v>
+        <v>0.08464288455743046</v>
       </c>
       <c r="C27">
-        <v>11688.75084975268</v>
+        <v>11616.9754586183</v>
       </c>
       <c r="D27">
-        <v>14139.17584975268</v>
+        <v>14213.1734586183</v>
       </c>
       <c r="E27">
-        <v>1386.825</v>
+        <v>1532.598</v>
       </c>
       <c r="F27">
-        <v>3644.325</v>
+        <v>3790.098</v>
       </c>
       <c r="G27">
         <v>1193.9</v>
@@ -3507,28 +3507,28 @@
         <v>824.2</v>
       </c>
       <c r="M27">
-        <v>201.5311725</v>
+        <v>209.5924194</v>
       </c>
       <c r="N27">
-        <v>622.6688275</v>
+        <v>614.6075806</v>
       </c>
       <c r="O27">
-        <v>186.80064825</v>
+        <v>184.38227418</v>
       </c>
       <c r="P27">
-        <v>435.86817925</v>
+        <v>430.22530642</v>
       </c>
       <c r="Q27">
-        <v>588.4681792499999</v>
+        <v>582.8253064199999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1002248925750154</v>
+        <v>0.1007814656181493</v>
       </c>
       <c r="T27">
-        <v>1.256925925519987</v>
+        <v>1.269779806423771</v>
       </c>
       <c r="U27">
         <v>0.05530000000000001</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.089689896484872</v>
+        <v>3.932394131235454</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08464288455743046</v>
+        <v>0.08443959968359935</v>
       </c>
       <c r="C28">
-        <v>11616.9754586183</v>
+        <v>11545.97867775448</v>
       </c>
       <c r="D28">
-        <v>14213.1734586183</v>
+        <v>14287.94967775448</v>
       </c>
       <c r="E28">
-        <v>1532.598</v>
+        <v>1678.371</v>
       </c>
       <c r="F28">
-        <v>3790.098</v>
+        <v>3935.871</v>
       </c>
       <c r="G28">
         <v>1193.9</v>
@@ -3589,28 +3589,28 @@
         <v>824.2</v>
       </c>
       <c r="M28">
-        <v>209.5924194</v>
+        <v>217.6536663</v>
       </c>
       <c r="N28">
-        <v>614.6075806</v>
+        <v>606.5463337</v>
       </c>
       <c r="O28">
-        <v>184.38227418</v>
+        <v>181.96390011</v>
       </c>
       <c r="P28">
-        <v>430.22530642</v>
+        <v>424.58243359</v>
       </c>
       <c r="Q28">
-        <v>582.8253064199999</v>
+        <v>577.1824335899998</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1007814656181493</v>
+        <v>0.1013532872378073</v>
       </c>
       <c r="T28">
-        <v>1.269779806423771</v>
+        <v>1.282985848448206</v>
       </c>
       <c r="U28">
         <v>0.05530000000000001</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.932394131235454</v>
+        <v>3.786749904152659</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08443959968359935</v>
+        <v>0.08423631480976822</v>
       </c>
       <c r="C29">
-        <v>11545.97867775448</v>
+        <v>11475.77286107897</v>
       </c>
       <c r="D29">
-        <v>14287.94967775448</v>
+        <v>14363.51686107898</v>
       </c>
       <c r="E29">
-        <v>1678.371</v>
+        <v>1824.144</v>
       </c>
       <c r="F29">
-        <v>3935.871</v>
+        <v>4081.644</v>
       </c>
       <c r="G29">
         <v>1193.9</v>
@@ -3671,28 +3671,28 @@
         <v>824.2</v>
       </c>
       <c r="M29">
-        <v>217.6536663</v>
+        <v>225.7149132</v>
       </c>
       <c r="N29">
-        <v>606.5463337</v>
+        <v>598.4850868</v>
       </c>
       <c r="O29">
-        <v>181.96390011</v>
+        <v>179.54552604</v>
       </c>
       <c r="P29">
-        <v>424.58243359</v>
+        <v>418.9395607599999</v>
       </c>
       <c r="Q29">
-        <v>577.1824335899998</v>
+        <v>571.5395607599999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1013532872378073</v>
+        <v>0.1019409927913448</v>
       </c>
       <c r="T29">
-        <v>1.282985848448206</v>
+        <v>1.29655872497332</v>
       </c>
       <c r="U29">
         <v>0.05530000000000001</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.786749904152659</v>
+        <v>3.651508836147207</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08423631480976822</v>
+        <v>0.08403302993593711</v>
       </c>
       <c r="C30">
-        <v>11475.77286107897</v>
+        <v>11406.37062525246</v>
       </c>
       <c r="D30">
-        <v>14363.51686107898</v>
+        <v>14439.88762525246</v>
       </c>
       <c r="E30">
-        <v>1824.144</v>
+        <v>1969.917</v>
       </c>
       <c r="F30">
-        <v>4081.644</v>
+        <v>4227.417</v>
       </c>
       <c r="G30">
         <v>1193.9</v>
@@ -3753,28 +3753,28 @@
         <v>824.2</v>
       </c>
       <c r="M30">
-        <v>225.7149132</v>
+        <v>233.7761601000001</v>
       </c>
       <c r="N30">
-        <v>598.4850868</v>
+        <v>590.4238399</v>
       </c>
       <c r="O30">
-        <v>179.54552604</v>
+        <v>177.12715197</v>
       </c>
       <c r="P30">
-        <v>418.9395607599999</v>
+        <v>413.29668793</v>
       </c>
       <c r="Q30">
-        <v>571.5395607599999</v>
+        <v>565.8966879299999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1019409927913448</v>
+        <v>0.1025452534308973</v>
       </c>
       <c r="T30">
-        <v>1.29655872497332</v>
+        <v>1.310513936048437</v>
       </c>
       <c r="U30">
         <v>0.05530000000000001</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.651508836147207</v>
+        <v>3.525594738349027</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08403302993593711</v>
+        <v>0.08382974506210598</v>
       </c>
       <c r="C31">
-        <v>11406.37062525246</v>
+        <v>11337.78485670094</v>
       </c>
       <c r="D31">
-        <v>14439.88762525246</v>
+        <v>14517.07485670093</v>
       </c>
       <c r="E31">
-        <v>1969.916999999999</v>
+        <v>2115.69</v>
       </c>
       <c r="F31">
-        <v>4227.416999999999</v>
+        <v>4373.19</v>
       </c>
       <c r="G31">
         <v>1193.9</v>
@@ -3835,28 +3835,28 @@
         <v>824.2</v>
       </c>
       <c r="M31">
-        <v>233.7761601</v>
+        <v>241.837407</v>
       </c>
       <c r="N31">
-        <v>590.4238399000001</v>
+        <v>582.3625930000001</v>
       </c>
       <c r="O31">
-        <v>177.12715197</v>
+        <v>174.7087779</v>
       </c>
       <c r="P31">
-        <v>413.2966879300001</v>
+        <v>407.6538151000001</v>
       </c>
       <c r="Q31">
-        <v>565.89668793</v>
+        <v>560.2538151</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1025452534308973</v>
+        <v>0.1031667786601514</v>
       </c>
       <c r="T31">
-        <v>1.310513936048437</v>
+        <v>1.324867867439987</v>
       </c>
       <c r="U31">
         <v>0.05530000000000001</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.525594738349028</v>
+        <v>3.408074913737394</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08382974506210598</v>
+        <v>0.08362646018827487</v>
       </c>
       <c r="C32">
-        <v>11337.78485670094</v>
+        <v>11270.02871886442</v>
       </c>
       <c r="D32">
-        <v>14517.07485670093</v>
+        <v>14595.09171886442</v>
       </c>
       <c r="E32">
-        <v>2115.69</v>
+        <v>2261.463</v>
       </c>
       <c r="F32">
-        <v>4373.19</v>
+        <v>4518.963</v>
       </c>
       <c r="G32">
         <v>1193.9</v>
@@ -3917,28 +3917,28 @@
         <v>824.2</v>
       </c>
       <c r="M32">
-        <v>241.837407</v>
+        <v>249.8986539</v>
       </c>
       <c r="N32">
-        <v>582.3625930000001</v>
+        <v>574.3013461</v>
       </c>
       <c r="O32">
-        <v>174.7087779</v>
+        <v>172.29040383</v>
       </c>
       <c r="P32">
-        <v>407.6538151000001</v>
+        <v>402.01094227</v>
       </c>
       <c r="Q32">
-        <v>560.2538151</v>
+        <v>554.6109422699999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1031667786601514</v>
+        <v>0.1038063191134418</v>
       </c>
       <c r="T32">
-        <v>1.324867867439987</v>
+        <v>1.339637854813899</v>
       </c>
       <c r="U32">
         <v>0.05530000000000001</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.408074913737394</v>
+        <v>3.298137013294252</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08362646018827487</v>
+        <v>0.08342317531444375</v>
       </c>
       <c r="C33">
-        <v>11270.02871886442</v>
+        <v>11203.11565968084</v>
       </c>
       <c r="D33">
-        <v>14595.09171886442</v>
+        <v>14673.95165968084</v>
       </c>
       <c r="E33">
-        <v>2261.463</v>
+        <v>2407.236</v>
       </c>
       <c r="F33">
-        <v>4518.963</v>
+        <v>4664.736</v>
       </c>
       <c r="G33">
         <v>1193.9</v>
@@ -3999,28 +3999,28 @@
         <v>824.2</v>
       </c>
       <c r="M33">
-        <v>249.8986539</v>
+        <v>257.9599008</v>
       </c>
       <c r="N33">
-        <v>574.3013461</v>
+        <v>566.2400992</v>
       </c>
       <c r="O33">
-        <v>172.29040383</v>
+        <v>169.87202976</v>
       </c>
       <c r="P33">
-        <v>402.01094227</v>
+        <v>396.36806944</v>
       </c>
       <c r="Q33">
-        <v>554.6109422699999</v>
+        <v>548.9680694399999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1038063191134418</v>
+        <v>0.1044646695800643</v>
       </c>
       <c r="T33">
-        <v>1.339637854813899</v>
+        <v>1.354842253581162</v>
       </c>
       <c r="U33">
         <v>0.05530000000000001</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.298137013294252</v>
+        <v>3.195070231628807</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08342317531444375</v>
+        <v>0.08321989044061263</v>
       </c>
       <c r="C34">
-        <v>11203.11565968084</v>
+        <v>11137.0594193137</v>
       </c>
       <c r="D34">
-        <v>14673.95165968084</v>
+        <v>14753.6684193137</v>
       </c>
       <c r="E34">
-        <v>2407.236</v>
+        <v>2553.009</v>
       </c>
       <c r="F34">
-        <v>4664.736</v>
+        <v>4810.509</v>
       </c>
       <c r="G34">
         <v>1193.9</v>
@@ -4081,28 +4081,28 @@
         <v>824.2</v>
       </c>
       <c r="M34">
-        <v>257.9599008</v>
+        <v>266.0211477</v>
       </c>
       <c r="N34">
-        <v>566.2400992</v>
+        <v>558.1788523</v>
       </c>
       <c r="O34">
-        <v>169.87202976</v>
+        <v>167.45365569</v>
       </c>
       <c r="P34">
-        <v>396.36806944</v>
+        <v>390.72519661</v>
       </c>
       <c r="Q34">
-        <v>548.9680694399999</v>
+        <v>543.3251966099999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1044646695800643</v>
+        <v>0.1051426722994219</v>
       </c>
       <c r="T34">
-        <v>1.354842253581162</v>
+        <v>1.370500514998195</v>
       </c>
       <c r="U34">
         <v>0.05530000000000001</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.195070231628807</v>
+        <v>3.098249921579449</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08321989044061263</v>
+        <v>0.0830166055667815</v>
       </c>
       <c r="C35">
-        <v>11137.0594193137</v>
+        <v>11071.87403813307</v>
       </c>
       <c r="D35">
-        <v>14753.6684193137</v>
+        <v>14834.25603813307</v>
       </c>
       <c r="E35">
-        <v>2553.009</v>
+        <v>2698.782</v>
       </c>
       <c r="F35">
-        <v>4810.509</v>
+        <v>4956.282</v>
       </c>
       <c r="G35">
         <v>1193.9</v>
@@ -4163,28 +4163,28 @@
         <v>824.2</v>
       </c>
       <c r="M35">
-        <v>266.0211477</v>
+        <v>274.0823946</v>
       </c>
       <c r="N35">
-        <v>558.1788523</v>
+        <v>550.1176054</v>
       </c>
       <c r="O35">
-        <v>167.45365569</v>
+        <v>165.03528162</v>
       </c>
       <c r="P35">
-        <v>390.72519661</v>
+        <v>385.08232378</v>
       </c>
       <c r="Q35">
-        <v>543.3251966099999</v>
+        <v>537.6823237799999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1051426722994219</v>
+        <v>0.1058412205557296</v>
       </c>
       <c r="T35">
-        <v>1.370500514998195</v>
+        <v>1.38663326918544</v>
       </c>
       <c r="U35">
         <v>0.05530000000000001</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.098249921579449</v>
+        <v>3.007124923885935</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0830166055667815</v>
+        <v>0.0834258206929504</v>
       </c>
       <c r="C36">
-        <v>11071.87403813307</v>
+        <v>10764.76497038841</v>
       </c>
       <c r="D36">
-        <v>14834.25603813307</v>
+        <v>14672.91997038841</v>
       </c>
       <c r="E36">
-        <v>2698.782</v>
+        <v>2844.555</v>
       </c>
       <c r="F36">
-        <v>4956.282</v>
+        <v>5102.055</v>
       </c>
       <c r="G36">
         <v>1193.9</v>
@@ -4245,45 +4245,45 @@
         <v>824.2</v>
       </c>
       <c r="M36">
-        <v>274.0823946</v>
+        <v>294.898779</v>
       </c>
       <c r="N36">
-        <v>550.1176054</v>
+        <v>529.3012209999999</v>
       </c>
       <c r="O36">
-        <v>165.03528162</v>
+        <v>158.7903663</v>
       </c>
       <c r="P36">
-        <v>385.08232378</v>
+        <v>370.5108547</v>
       </c>
       <c r="Q36">
-        <v>537.6823237799999</v>
+        <v>523.1108546999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1058412205557296</v>
+        <v>0.1065612626045391</v>
       </c>
       <c r="T36">
-        <v>1.38663326918544</v>
+        <v>1.403262415809216</v>
       </c>
       <c r="U36">
-        <v>0.05530000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V36">
         <v>0.3</v>
       </c>
       <c r="W36">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.007124923885935</v>
+        <v>2.794857282199869</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0834258206929504</v>
+        <v>0.08324003581911926</v>
       </c>
       <c r="C37">
-        <v>10764.76497038841</v>
+        <v>10691.80190568342</v>
       </c>
       <c r="D37">
-        <v>14672.91997038841</v>
+        <v>14745.72990568342</v>
       </c>
       <c r="E37">
-        <v>2844.555</v>
+        <v>2990.328</v>
       </c>
       <c r="F37">
-        <v>5102.055</v>
+        <v>5247.828</v>
       </c>
       <c r="G37">
         <v>1193.9</v>
@@ -4327,28 +4327,28 @@
         <v>824.2</v>
       </c>
       <c r="M37">
-        <v>294.898779</v>
+        <v>303.3244584</v>
       </c>
       <c r="N37">
-        <v>529.3012209999999</v>
+        <v>520.8755416</v>
       </c>
       <c r="O37">
-        <v>158.7903663</v>
+        <v>156.26266248</v>
       </c>
       <c r="P37">
-        <v>370.5108547</v>
+        <v>364.61287912</v>
       </c>
       <c r="Q37">
-        <v>523.1108546999999</v>
+        <v>517.2128791199999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1065612626045391</v>
+        <v>0.1073038059673739</v>
       </c>
       <c r="T37">
-        <v>1.403262415809216</v>
+        <v>1.420411223264985</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.794857282199869</v>
+        <v>2.717222357694318</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08324003581911928</v>
+        <v>0.08305425094528816</v>
       </c>
       <c r="C38">
-        <v>10691.80190568341</v>
+        <v>10619.56503915979</v>
       </c>
       <c r="D38">
-        <v>14745.72990568341</v>
+        <v>14819.26603915979</v>
       </c>
       <c r="E38">
-        <v>2990.328</v>
+        <v>3136.101</v>
       </c>
       <c r="F38">
-        <v>5247.828</v>
+        <v>5393.601</v>
       </c>
       <c r="G38">
         <v>1193.9</v>
@@ -4409,28 +4409,28 @@
         <v>824.2</v>
       </c>
       <c r="M38">
-        <v>303.3244584</v>
+        <v>311.7501378</v>
       </c>
       <c r="N38">
-        <v>520.8755416000001</v>
+        <v>512.4498622000001</v>
       </c>
       <c r="O38">
-        <v>156.26266248</v>
+        <v>153.73495866</v>
       </c>
       <c r="P38">
-        <v>364.6128791200001</v>
+        <v>358.7149035400001</v>
       </c>
       <c r="Q38">
-        <v>517.21287912</v>
+        <v>511.31490354</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1073038059673739</v>
+        <v>0.108069922135378</v>
       </c>
       <c r="T38">
-        <v>1.420411223264985</v>
+        <v>1.438104437306652</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.717222357694318</v>
+        <v>2.643783915594471</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08305425094528816</v>
+        <v>0.08286846607145704</v>
       </c>
       <c r="C39">
-        <v>10619.56503915979</v>
+        <v>10548.0652897995</v>
       </c>
       <c r="D39">
-        <v>14819.26603915979</v>
+        <v>14893.5392897995</v>
       </c>
       <c r="E39">
-        <v>3136.101</v>
+        <v>3281.874</v>
       </c>
       <c r="F39">
-        <v>5393.601</v>
+        <v>5539.374</v>
       </c>
       <c r="G39">
         <v>1193.9</v>
@@ -4491,28 +4491,28 @@
         <v>824.2</v>
       </c>
       <c r="M39">
-        <v>311.7501378</v>
+        <v>320.1758172</v>
       </c>
       <c r="N39">
-        <v>512.4498622000001</v>
+        <v>504.0241828000001</v>
       </c>
       <c r="O39">
-        <v>153.73495866</v>
+        <v>151.20725484</v>
       </c>
       <c r="P39">
-        <v>358.7149035400001</v>
+        <v>352.81692796</v>
       </c>
       <c r="Q39">
-        <v>511.31490354</v>
+        <v>505.41692796</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.108069922135378</v>
+        <v>0.1088607517281565</v>
       </c>
       <c r="T39">
-        <v>1.438104437306652</v>
+        <v>1.456368400188372</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.643783915594471</v>
+        <v>2.574210654657775</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08286846607145704</v>
+        <v>0.08268268119762592</v>
       </c>
       <c r="C40">
-        <v>10548.0652897995</v>
+        <v>10477.31379658823</v>
       </c>
       <c r="D40">
-        <v>14893.5392897995</v>
+        <v>14968.56079658823</v>
       </c>
       <c r="E40">
-        <v>3281.874</v>
+        <v>3427.647</v>
       </c>
       <c r="F40">
-        <v>5539.374</v>
+        <v>5685.147</v>
       </c>
       <c r="G40">
         <v>1193.9</v>
@@ -4573,28 +4573,28 @@
         <v>824.2</v>
       </c>
       <c r="M40">
-        <v>320.1758172</v>
+        <v>328.6014966</v>
       </c>
       <c r="N40">
-        <v>504.0241828000001</v>
+        <v>495.5985034</v>
       </c>
       <c r="O40">
-        <v>151.20725484</v>
+        <v>148.67955102</v>
       </c>
       <c r="P40">
-        <v>352.81692796</v>
+        <v>346.9189523800001</v>
       </c>
       <c r="Q40">
-        <v>505.41692796</v>
+        <v>499.51895238</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1088607517281565</v>
+        <v>0.1096775101600425</v>
       </c>
       <c r="T40">
-        <v>1.456368400188372</v>
+        <v>1.475231181525231</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.574210654657775</v>
+        <v>2.508205253256294</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08268268119762592</v>
+        <v>0.08347689632379481</v>
       </c>
       <c r="C41">
-        <v>10477.31379658823</v>
+        <v>10016.00903676753</v>
       </c>
       <c r="D41">
-        <v>14968.56079658823</v>
+        <v>14653.02903676754</v>
       </c>
       <c r="E41">
-        <v>3427.647</v>
+        <v>3573.42</v>
       </c>
       <c r="F41">
-        <v>5685.147</v>
+        <v>5830.92</v>
       </c>
       <c r="G41">
         <v>1193.9</v>
@@ -4655,45 +4655,45 @@
         <v>824.2</v>
       </c>
       <c r="M41">
-        <v>328.6014966</v>
+        <v>357.435396</v>
       </c>
       <c r="N41">
-        <v>495.5985034</v>
+        <v>466.764604</v>
       </c>
       <c r="O41">
-        <v>148.67955102</v>
+        <v>140.0293812</v>
       </c>
       <c r="P41">
-        <v>346.9189523800001</v>
+        <v>326.7352228</v>
       </c>
       <c r="Q41">
-        <v>499.51895238</v>
+        <v>479.3352227999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1096775101600425</v>
+        <v>0.1105214938729913</v>
       </c>
       <c r="T41">
-        <v>1.475231181525231</v>
+        <v>1.494722722239985</v>
       </c>
       <c r="U41">
-        <v>0.0578</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V41">
         <v>0.3</v>
       </c>
       <c r="W41">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.508205253256294</v>
+        <v>2.305871240575178</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08347689632379481</v>
+        <v>0.08411921144996368</v>
       </c>
       <c r="C42">
-        <v>10016.00903676753</v>
+        <v>9624.618712235759</v>
       </c>
       <c r="D42">
-        <v>14653.02903676754</v>
+        <v>14407.41171223576</v>
       </c>
       <c r="E42">
-        <v>3573.42</v>
+        <v>3719.193</v>
       </c>
       <c r="F42">
-        <v>5830.92</v>
+        <v>5976.693</v>
       </c>
       <c r="G42">
         <v>1193.9</v>
@@ -4737,45 +4737,45 @@
         <v>824.2</v>
       </c>
       <c r="M42">
-        <v>357.435396</v>
+        <v>383.1060213000001</v>
       </c>
       <c r="N42">
-        <v>466.764604</v>
+        <v>441.0939787</v>
       </c>
       <c r="O42">
-        <v>140.0293812</v>
+        <v>132.32819361</v>
       </c>
       <c r="P42">
-        <v>326.7352228</v>
+        <v>308.76578509</v>
       </c>
       <c r="Q42">
-        <v>479.3352227999999</v>
+        <v>461.3657850899999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1105214938729913</v>
+        <v>0.1113940872033283</v>
       </c>
       <c r="T42">
-        <v>1.494722722239985</v>
+        <v>1.514874993148459</v>
       </c>
       <c r="U42">
-        <v>0.06130000000000001</v>
+        <v>0.0641</v>
       </c>
       <c r="V42">
         <v>0.3</v>
       </c>
       <c r="W42">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.305871240575178</v>
+        <v>2.151362688592647</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08411921144996368</v>
+        <v>0.08397752657613256</v>
       </c>
       <c r="C43">
-        <v>9624.618712235759</v>
+        <v>9532.314663573148</v>
       </c>
       <c r="D43">
-        <v>14407.41171223576</v>
+        <v>14460.88066357315</v>
       </c>
       <c r="E43">
-        <v>3719.193</v>
+        <v>3864.966</v>
       </c>
       <c r="F43">
-        <v>5976.693</v>
+        <v>6122.466</v>
       </c>
       <c r="G43">
         <v>1193.9</v>
@@ -4819,28 +4819,28 @@
         <v>824.2</v>
       </c>
       <c r="M43">
-        <v>383.1060213000001</v>
+        <v>392.4500706000001</v>
       </c>
       <c r="N43">
-        <v>441.0939787</v>
+        <v>431.7499294</v>
       </c>
       <c r="O43">
-        <v>132.32819361</v>
+        <v>129.52497882</v>
       </c>
       <c r="P43">
-        <v>308.76578509</v>
+        <v>302.22495058</v>
       </c>
       <c r="Q43">
-        <v>461.3657850899999</v>
+        <v>454.8249505799999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1113940872033283</v>
+        <v>0.1122967699588492</v>
       </c>
       <c r="T43">
-        <v>1.514874993148459</v>
+        <v>1.535722169950329</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.151362688592647</v>
+        <v>2.100139767435679</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08397752657613257</v>
+        <v>0.08383584170230145</v>
       </c>
       <c r="C44">
-        <v>9532.314663573143</v>
+        <v>9440.408962431455</v>
       </c>
       <c r="D44">
-        <v>14460.88066357314</v>
+        <v>14514.74796243145</v>
       </c>
       <c r="E44">
-        <v>3864.965999999999</v>
+        <v>4010.739</v>
       </c>
       <c r="F44">
-        <v>6122.465999999999</v>
+        <v>6268.239</v>
       </c>
       <c r="G44">
         <v>1193.9</v>
@@ -4901,28 +4901,28 @@
         <v>824.2</v>
       </c>
       <c r="M44">
-        <v>392.4500706</v>
+        <v>401.7941199</v>
       </c>
       <c r="N44">
-        <v>431.7499294</v>
+        <v>422.4058801</v>
       </c>
       <c r="O44">
-        <v>129.52497882</v>
+        <v>126.72176403</v>
       </c>
       <c r="P44">
-        <v>302.22495058</v>
+        <v>295.6841160700001</v>
       </c>
       <c r="Q44">
-        <v>454.8249505799999</v>
+        <v>448.28411607</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1122967699588492</v>
+        <v>0.1132311257935113</v>
       </c>
       <c r="T44">
-        <v>1.535722169950329</v>
+        <v>1.557300826639984</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.10013976743568</v>
+        <v>2.051299307727873</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08383584170230145</v>
+        <v>0.08369415682847034</v>
       </c>
       <c r="C45">
-        <v>9440.408962431455</v>
+        <v>9348.906077031352</v>
       </c>
       <c r="D45">
-        <v>14514.74796243145</v>
+        <v>14569.01807703135</v>
       </c>
       <c r="E45">
-        <v>4010.739</v>
+        <v>4156.512</v>
       </c>
       <c r="F45">
-        <v>6268.239</v>
+        <v>6414.012</v>
       </c>
       <c r="G45">
         <v>1193.9</v>
@@ -4983,28 +4983,28 @@
         <v>824.2</v>
       </c>
       <c r="M45">
-        <v>401.7941199</v>
+        <v>411.1381692</v>
       </c>
       <c r="N45">
-        <v>422.4058801</v>
+        <v>413.0618308000001</v>
       </c>
       <c r="O45">
-        <v>126.72176403</v>
+        <v>123.91854924</v>
       </c>
       <c r="P45">
-        <v>295.6841160700001</v>
+        <v>289.14328156</v>
       </c>
       <c r="Q45">
-        <v>448.28411607</v>
+        <v>441.74328156</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1132311257935113</v>
+        <v>0.1141988514794113</v>
       </c>
       <c r="T45">
-        <v>1.557300826639984</v>
+        <v>1.579650149639984</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.051299307727873</v>
+        <v>2.004678868915876</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08369415682847034</v>
+        <v>0.08723797195463923</v>
       </c>
       <c r="C46">
-        <v>9348.906077031352</v>
+        <v>7957.176670397133</v>
       </c>
       <c r="D46">
-        <v>14569.01807703135</v>
+        <v>13323.06167039713</v>
       </c>
       <c r="E46">
-        <v>4156.512</v>
+        <v>4302.285</v>
       </c>
       <c r="F46">
-        <v>6414.012</v>
+        <v>6559.785</v>
       </c>
       <c r="G46">
         <v>1193.9</v>
@@ -5065,45 +5065,45 @@
         <v>824.2</v>
       </c>
       <c r="M46">
-        <v>411.1381692</v>
+        <v>497.231703</v>
       </c>
       <c r="N46">
-        <v>413.0618308000001</v>
+        <v>326.968297</v>
       </c>
       <c r="O46">
-        <v>123.91854924</v>
+        <v>98.0904891</v>
       </c>
       <c r="P46">
-        <v>289.14328156</v>
+        <v>228.8778079</v>
       </c>
       <c r="Q46">
-        <v>441.74328156</v>
+        <v>381.4778078999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1141988514794113</v>
+        <v>0.1152017671902531</v>
       </c>
       <c r="T46">
-        <v>1.579650149639984</v>
+        <v>1.602812175294529</v>
       </c>
       <c r="U46">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V46">
         <v>0.3</v>
       </c>
       <c r="W46">
-        <v>0.04487</v>
+        <v>0.05306</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.004678868915876</v>
+        <v>1.657577332714845</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08723797195463923</v>
+        <v>0.08717818708080809</v>
       </c>
       <c r="C47">
-        <v>7957.176670397133</v>
+        <v>7830.653367331744</v>
       </c>
       <c r="D47">
-        <v>13323.06167039713</v>
+        <v>13342.31136733174</v>
       </c>
       <c r="E47">
-        <v>4302.285</v>
+        <v>4448.058</v>
       </c>
       <c r="F47">
-        <v>6559.785</v>
+        <v>6705.558</v>
       </c>
       <c r="G47">
         <v>1193.9</v>
@@ -5147,28 +5147,28 @@
         <v>824.2</v>
       </c>
       <c r="M47">
-        <v>497.231703</v>
+        <v>508.2812964</v>
       </c>
       <c r="N47">
-        <v>326.968297</v>
+        <v>315.9187036</v>
       </c>
       <c r="O47">
-        <v>98.0904891</v>
+        <v>94.77561108</v>
       </c>
       <c r="P47">
-        <v>228.8778079</v>
+        <v>221.14309252</v>
       </c>
       <c r="Q47">
-        <v>381.4778078999999</v>
+        <v>373.7430925199999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1152017671902531</v>
+        <v>0.1162418279274224</v>
       </c>
       <c r="T47">
-        <v>1.602812175294529</v>
+        <v>1.626832053751094</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.657577332714845</v>
+        <v>1.621543042873218</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08717818708080809</v>
+        <v>0.08711840220697699</v>
       </c>
       <c r="C48">
-        <v>7830.653367331744</v>
+        <v>7704.185770229837</v>
       </c>
       <c r="D48">
-        <v>13342.31136733174</v>
+        <v>13361.61677022984</v>
       </c>
       <c r="E48">
-        <v>4448.058</v>
+        <v>4593.831</v>
       </c>
       <c r="F48">
-        <v>6705.558</v>
+        <v>6851.331</v>
       </c>
       <c r="G48">
         <v>1193.9</v>
@@ -5229,28 +5229,28 @@
         <v>824.2</v>
       </c>
       <c r="M48">
-        <v>508.2812964</v>
+        <v>519.3308898</v>
       </c>
       <c r="N48">
-        <v>315.9187036</v>
+        <v>304.8691102</v>
       </c>
       <c r="O48">
-        <v>94.77561108</v>
+        <v>91.46073306000001</v>
       </c>
       <c r="P48">
-        <v>221.14309252</v>
+        <v>213.40837714</v>
       </c>
       <c r="Q48">
-        <v>373.7430925199999</v>
+        <v>366.0083771399999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1162418279274224</v>
+        <v>0.1173211362395792</v>
       </c>
       <c r="T48">
-        <v>1.626832053751094</v>
+        <v>1.651758342715455</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.621543042873218</v>
+        <v>1.587042127067405</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08711840220697699</v>
+        <v>0.08705861733314586</v>
       </c>
       <c r="C49">
-        <v>7704.185770229837</v>
+        <v>7577.774121249867</v>
       </c>
       <c r="D49">
-        <v>13361.61677022984</v>
+        <v>13380.97812124987</v>
       </c>
       <c r="E49">
-        <v>4593.831</v>
+        <v>4739.604</v>
       </c>
       <c r="F49">
-        <v>6851.331</v>
+        <v>6997.104</v>
       </c>
       <c r="G49">
         <v>1193.9</v>
@@ -5311,28 +5311,28 @@
         <v>824.2</v>
       </c>
       <c r="M49">
-        <v>519.3308898</v>
+        <v>530.3804832000001</v>
       </c>
       <c r="N49">
-        <v>304.8691102</v>
+        <v>293.8195168</v>
       </c>
       <c r="O49">
-        <v>91.46073306000001</v>
+        <v>88.14585503999999</v>
       </c>
       <c r="P49">
-        <v>213.40837714</v>
+        <v>205.67366176</v>
       </c>
       <c r="Q49">
-        <v>366.0083771399999</v>
+        <v>358.2736617599999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1173211362395792</v>
+        <v>0.1184419564098959</v>
       </c>
       <c r="T49">
-        <v>1.651758342715455</v>
+        <v>1.677643335101521</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.587042127067405</v>
+        <v>1.553978749420167</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08705861733314586</v>
+        <v>0.08699883245931474</v>
       </c>
       <c r="C50">
-        <v>7577.774121249868</v>
+        <v>7451.418663955864</v>
       </c>
       <c r="D50">
-        <v>13380.97812124987</v>
+        <v>13400.39566395586</v>
       </c>
       <c r="E50">
-        <v>4739.603999999999</v>
+        <v>4885.376999999999</v>
       </c>
       <c r="F50">
-        <v>6997.103999999999</v>
+        <v>7142.876999999999</v>
       </c>
       <c r="G50">
         <v>1193.9</v>
@@ -5393,28 +5393,28 @@
         <v>824.2</v>
       </c>
       <c r="M50">
-        <v>530.3804832</v>
+        <v>541.4300766</v>
       </c>
       <c r="N50">
-        <v>293.8195168000001</v>
+        <v>282.7699234</v>
       </c>
       <c r="O50">
-        <v>88.14585504000003</v>
+        <v>84.83097702000001</v>
       </c>
       <c r="P50">
-        <v>205.6736617600001</v>
+        <v>197.93894638</v>
       </c>
       <c r="Q50">
-        <v>358.27366176</v>
+        <v>350.53894638</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1184419564098959</v>
+        <v>0.1196067303123818</v>
       </c>
       <c r="T50">
-        <v>1.677643335101521</v>
+        <v>1.704543425228218</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.553978749420168</v>
+        <v>1.522264897391184</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08699883245931474</v>
+        <v>0.09190904758548361</v>
       </c>
       <c r="C51">
-        <v>7451.418663955864</v>
+        <v>5878.619322459295</v>
       </c>
       <c r="D51">
-        <v>13400.39566395586</v>
+        <v>11973.3693224593</v>
       </c>
       <c r="E51">
-        <v>4885.376999999999</v>
+        <v>5031.15</v>
       </c>
       <c r="F51">
-        <v>7142.876999999999</v>
+        <v>7288.65</v>
       </c>
       <c r="G51">
         <v>1193.9</v>
@@ -5475,45 +5475,45 @@
         <v>824.2</v>
       </c>
       <c r="M51">
-        <v>541.4300766</v>
+        <v>655.9785000000001</v>
       </c>
       <c r="N51">
-        <v>282.7699234</v>
+        <v>168.2215</v>
       </c>
       <c r="O51">
-        <v>84.83097702000001</v>
+        <v>50.46644999999999</v>
       </c>
       <c r="P51">
-        <v>197.93894638</v>
+        <v>117.75505</v>
       </c>
       <c r="Q51">
-        <v>350.53894638</v>
+        <v>270.3550499999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1196067303123818</v>
+        <v>0.1208180951709672</v>
       </c>
       <c r="T51">
-        <v>1.704543425228218</v>
+        <v>1.732519518959982</v>
       </c>
       <c r="U51">
-        <v>0.07580000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V51">
         <v>0.3</v>
       </c>
       <c r="W51">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.522264897391184</v>
+        <v>1.256443618197852</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09190904758548361</v>
+        <v>0.1037831423603764</v>
       </c>
       <c r="C52">
-        <v>5878.619322459295</v>
+        <v>3280.876382195563</v>
       </c>
       <c r="D52">
-        <v>11973.3693224593</v>
+        <v>9521.399382195563</v>
       </c>
       <c r="E52">
-        <v>5031.15</v>
+        <v>5176.923</v>
       </c>
       <c r="F52">
-        <v>7288.65</v>
+        <v>7434.423</v>
       </c>
       <c r="G52">
         <v>1193.9</v>
@@ -5557,45 +5557,45 @@
         <v>824.2</v>
       </c>
       <c r="M52">
-        <v>655.9785000000001</v>
+        <v>881.7225678000001</v>
       </c>
       <c r="N52">
-        <v>168.2215</v>
+        <v>-57.52256780000005</v>
       </c>
       <c r="O52">
-        <v>50.46644999999999</v>
+        <v>-17.25677034000001</v>
       </c>
       <c r="P52">
-        <v>117.75505</v>
+        <v>-40.26579746000003</v>
       </c>
       <c r="Q52">
-        <v>270.3550499999999</v>
+        <v>112.3342025399999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1208180951709672</v>
+        <v>0.1229778187878519</v>
       </c>
       <c r="T52">
-        <v>1.732519518959982</v>
+        <v>1.782397662536995</v>
       </c>
       <c r="U52">
-        <v>0.09000000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V52">
-        <v>0.3</v>
+        <v>0.2804283445040341</v>
       </c>
       <c r="W52">
-        <v>0.063</v>
+        <v>0.08534119834182156</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y52">
-        <v>1.256443618197852</v>
+        <v>0.9347611483467804</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1037831423603764</v>
+        <v>0.1045111423603764</v>
       </c>
       <c r="C53">
-        <v>3280.876382195563</v>
+        <v>3017.040975783988</v>
       </c>
       <c r="D53">
-        <v>9521.399382195563</v>
+        <v>9403.336975783988</v>
       </c>
       <c r="E53">
-        <v>5176.923</v>
+        <v>5322.696</v>
       </c>
       <c r="F53">
-        <v>7434.423</v>
+        <v>7580.196</v>
       </c>
       <c r="G53">
         <v>1193.9</v>
@@ -5639,37 +5639,37 @@
         <v>824.2</v>
       </c>
       <c r="M53">
-        <v>881.7225678000001</v>
+        <v>899.0112456000001</v>
       </c>
       <c r="N53">
-        <v>-57.52256780000005</v>
+        <v>-74.81124560000001</v>
       </c>
       <c r="O53">
-        <v>-17.25677034000001</v>
+        <v>-22.44337368</v>
       </c>
       <c r="P53">
-        <v>-40.26579746000003</v>
+        <v>-52.36787192000001</v>
       </c>
       <c r="Q53">
-        <v>112.3342025399999</v>
+        <v>100.2321280799999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1229778187878519</v>
+        <v>0.1245856900125988</v>
       </c>
       <c r="T53">
-        <v>1.782397662536995</v>
+        <v>1.819530947173182</v>
       </c>
       <c r="U53">
         <v>0.1186</v>
       </c>
       <c r="V53">
-        <v>0.2804283445040341</v>
+        <v>0.2750354917251104</v>
       </c>
       <c r="W53">
-        <v>0.08534119834182156</v>
+        <v>0.08598079068140192</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.9347611483467804</v>
+        <v>0.9167849724170347</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1045111423603764</v>
+        <v>0.1052391423603764</v>
       </c>
       <c r="C54">
-        <v>3017.040975783988</v>
+        <v>2756.097583908781</v>
       </c>
       <c r="D54">
-        <v>9403.336975783988</v>
+        <v>9288.166583908782</v>
       </c>
       <c r="E54">
-        <v>5322.696</v>
+        <v>5468.469</v>
       </c>
       <c r="F54">
-        <v>7580.196</v>
+        <v>7725.969</v>
       </c>
       <c r="G54">
         <v>1193.9</v>
@@ -5721,37 +5721,37 @@
         <v>824.2</v>
       </c>
       <c r="M54">
-        <v>899.0112456000001</v>
+        <v>916.2999234000001</v>
       </c>
       <c r="N54">
-        <v>-74.81124560000001</v>
+        <v>-92.09992340000008</v>
       </c>
       <c r="O54">
-        <v>-22.44337368</v>
+        <v>-27.62997702000002</v>
       </c>
       <c r="P54">
-        <v>-52.36787192000001</v>
+        <v>-64.46994638000005</v>
       </c>
       <c r="Q54">
-        <v>100.2321280799999</v>
+        <v>88.13005361999986</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1245856900125988</v>
+        <v>0.1262619812894626</v>
       </c>
       <c r="T54">
-        <v>1.819530947173182</v>
+        <v>1.858244371581123</v>
       </c>
       <c r="U54">
         <v>0.1186</v>
       </c>
       <c r="V54">
-        <v>0.2750354917251104</v>
+        <v>0.2698461428246366</v>
       </c>
       <c r="W54">
-        <v>0.08598079068140192</v>
+        <v>0.0865962474609981</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.9167849724170347</v>
+        <v>0.8994871427487887</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1052391423603764</v>
+        <v>0.1059671423603764</v>
       </c>
       <c r="C55">
-        <v>2756.097583908781</v>
+        <v>2497.941229675582</v>
       </c>
       <c r="D55">
-        <v>9288.166583908782</v>
+        <v>9175.783229675582</v>
       </c>
       <c r="E55">
-        <v>5468.469</v>
+        <v>5614.242</v>
       </c>
       <c r="F55">
-        <v>7725.969</v>
+        <v>7871.742</v>
       </c>
       <c r="G55">
         <v>1193.9</v>
@@ -5803,37 +5803,37 @@
         <v>824.2</v>
       </c>
       <c r="M55">
-        <v>916.2999234000001</v>
+        <v>933.5886012000001</v>
       </c>
       <c r="N55">
-        <v>-92.09992340000008</v>
+        <v>-109.3886012</v>
       </c>
       <c r="O55">
-        <v>-27.62997702000002</v>
+        <v>-32.81658036000001</v>
       </c>
       <c r="P55">
-        <v>-64.46994638000005</v>
+        <v>-76.57202084000002</v>
       </c>
       <c r="Q55">
-        <v>88.13005361999986</v>
+        <v>76.02797915999989</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1262619812894626</v>
+        <v>0.1280111547957553</v>
       </c>
       <c r="T55">
-        <v>1.858244371581123</v>
+        <v>1.898640988354625</v>
       </c>
       <c r="U55">
         <v>0.1186</v>
       </c>
       <c r="V55">
-        <v>0.2698461428246366</v>
+        <v>0.2648489920315878</v>
       </c>
       <c r="W55">
-        <v>0.0865962474609981</v>
+        <v>0.08718890954505371</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8994871427487887</v>
+        <v>0.882829973438626</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1059671423603764</v>
+        <v>0.1066951423603764</v>
       </c>
       <c r="C56">
-        <v>2497.941229675582</v>
+        <v>2242.471956175278</v>
       </c>
       <c r="D56">
-        <v>9175.783229675582</v>
+        <v>9066.086956175279</v>
       </c>
       <c r="E56">
-        <v>5614.242</v>
+        <v>5760.015</v>
       </c>
       <c r="F56">
-        <v>7871.742</v>
+        <v>8017.515</v>
       </c>
       <c r="G56">
         <v>1193.9</v>
@@ -5885,37 +5885,37 @@
         <v>824.2</v>
       </c>
       <c r="M56">
-        <v>933.5886012000001</v>
+        <v>950.8772790000002</v>
       </c>
       <c r="N56">
-        <v>-109.3886012</v>
+        <v>-126.6772790000001</v>
       </c>
       <c r="O56">
-        <v>-32.81658036000001</v>
+        <v>-38.00318370000003</v>
       </c>
       <c r="P56">
-        <v>-76.57202084000002</v>
+        <v>-88.67409530000009</v>
       </c>
       <c r="Q56">
-        <v>76.02797915999989</v>
+        <v>63.92590469999982</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1280111547957553</v>
+        <v>0.1298380693467721</v>
       </c>
       <c r="T56">
-        <v>1.898640988354625</v>
+        <v>1.940833010318061</v>
       </c>
       <c r="U56">
         <v>0.1186</v>
       </c>
       <c r="V56">
-        <v>0.2648489920315878</v>
+        <v>0.2600335558128316</v>
       </c>
       <c r="W56">
-        <v>0.08718890954505371</v>
+        <v>0.08776002028059818</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.882829973438626</v>
+        <v>0.8667785193761054</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1066951423603764</v>
+        <v>0.1074231423603764</v>
       </c>
       <c r="C57">
-        <v>2242.471956175278</v>
+        <v>1989.594529959915</v>
       </c>
       <c r="D57">
-        <v>9066.086956175279</v>
+        <v>8958.982529959916</v>
       </c>
       <c r="E57">
-        <v>5760.015</v>
+        <v>5905.788</v>
       </c>
       <c r="F57">
-        <v>8017.515</v>
+        <v>8163.288</v>
       </c>
       <c r="G57">
         <v>1193.9</v>
@@ -5967,37 +5967,37 @@
         <v>824.2</v>
       </c>
       <c r="M57">
-        <v>950.8772790000002</v>
+        <v>968.1659568000001</v>
       </c>
       <c r="N57">
-        <v>-126.6772790000001</v>
+        <v>-143.9659568000001</v>
       </c>
       <c r="O57">
-        <v>-38.00318370000003</v>
+        <v>-43.18978704000002</v>
       </c>
       <c r="P57">
-        <v>-88.67409530000009</v>
+        <v>-100.77616976</v>
       </c>
       <c r="Q57">
-        <v>63.92590469999982</v>
+        <v>51.82383023999986</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1298380693467721</v>
+        <v>0.1317480254682896</v>
       </c>
       <c r="T57">
-        <v>1.940833010318061</v>
+        <v>1.984942851461654</v>
       </c>
       <c r="U57">
         <v>0.1186</v>
       </c>
       <c r="V57">
-        <v>0.2600335558128316</v>
+        <v>0.2553900994590311</v>
       </c>
       <c r="W57">
-        <v>0.08776002028059818</v>
+        <v>0.08831073420415893</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8667785193761054</v>
+        <v>0.8513003315301035</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1074231423603764</v>
+        <v>0.1081511423603764</v>
       </c>
       <c r="C58">
-        <v>1989.594529959915</v>
+        <v>1739.218165291564</v>
       </c>
       <c r="D58">
-        <v>8958.982529959916</v>
+        <v>8854.379165291564</v>
       </c>
       <c r="E58">
-        <v>5905.788</v>
+        <v>6051.561</v>
       </c>
       <c r="F58">
-        <v>8163.288</v>
+        <v>8309.061</v>
       </c>
       <c r="G58">
         <v>1193.9</v>
@@ -6049,37 +6049,37 @@
         <v>824.2</v>
       </c>
       <c r="M58">
-        <v>968.1659568000001</v>
+        <v>985.4546346000001</v>
       </c>
       <c r="N58">
-        <v>-143.9659568000001</v>
+        <v>-161.2546346</v>
       </c>
       <c r="O58">
-        <v>-43.18978704000002</v>
+        <v>-48.37639038000001</v>
       </c>
       <c r="P58">
-        <v>-100.77616976</v>
+        <v>-112.87824422</v>
       </c>
       <c r="Q58">
-        <v>51.82383023999986</v>
+        <v>39.72175577999988</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1317480254682896</v>
+        <v>0.1337468167582498</v>
       </c>
       <c r="T58">
-        <v>1.984942851461654</v>
+        <v>2.031104313123552</v>
       </c>
       <c r="U58">
         <v>0.1186</v>
       </c>
       <c r="V58">
-        <v>0.2553900994590311</v>
+        <v>0.2509095713983464</v>
       </c>
       <c r="W58">
-        <v>0.08831073420415893</v>
+        <v>0.08884212483215613</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8513003315301035</v>
+        <v>0.8363652379944878</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1081511423603764</v>
+        <v>0.1088791423603764</v>
       </c>
       <c r="C59">
-        <v>1739.218165291564</v>
+        <v>1491.256267485916</v>
       </c>
       <c r="D59">
-        <v>8854.379165291564</v>
+        <v>8752.190267485918</v>
       </c>
       <c r="E59">
-        <v>6051.561</v>
+        <v>6197.334000000001</v>
       </c>
       <c r="F59">
-        <v>8309.061</v>
+        <v>8454.834000000001</v>
       </c>
       <c r="G59">
         <v>1193.9</v>
@@ -6131,37 +6131,37 @@
         <v>824.2</v>
       </c>
       <c r="M59">
-        <v>985.4546346000001</v>
+        <v>1002.7433124</v>
       </c>
       <c r="N59">
-        <v>-161.2546346</v>
+        <v>-178.5433124000001</v>
       </c>
       <c r="O59">
-        <v>-48.37639038000001</v>
+        <v>-53.56299372000003</v>
       </c>
       <c r="P59">
-        <v>-112.87824422</v>
+        <v>-124.9803186800001</v>
       </c>
       <c r="Q59">
-        <v>39.72175577999988</v>
+        <v>27.61968131999984</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1337468167582498</v>
+        <v>0.1358407885858272</v>
       </c>
       <c r="T59">
-        <v>2.031104313123552</v>
+        <v>2.079463939626494</v>
       </c>
       <c r="U59">
         <v>0.1186</v>
       </c>
       <c r="V59">
-        <v>0.2509095713983464</v>
+        <v>0.2465835443052714</v>
       </c>
       <c r="W59">
-        <v>0.08884212483215613</v>
+        <v>0.08935519164539484</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8363652379944878</v>
+        <v>0.8219451476842379</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1088791423603764</v>
+        <v>0.1096071423603764</v>
       </c>
       <c r="C60">
-        <v>1491.256267485918</v>
+        <v>1245.626193825676</v>
       </c>
       <c r="D60">
-        <v>8752.190267485918</v>
+        <v>8652.333193825676</v>
       </c>
       <c r="E60">
-        <v>6197.333999999999</v>
+        <v>6343.107</v>
       </c>
       <c r="F60">
-        <v>8454.833999999999</v>
+        <v>8600.607</v>
       </c>
       <c r="G60">
         <v>1193.9</v>
@@ -6213,37 +6213,37 @@
         <v>824.2</v>
       </c>
       <c r="M60">
-        <v>1002.7433124</v>
+        <v>1020.0319902</v>
       </c>
       <c r="N60">
-        <v>-178.5433123999999</v>
+        <v>-195.8319902000001</v>
       </c>
       <c r="O60">
-        <v>-53.56299371999996</v>
+        <v>-58.74959706000001</v>
       </c>
       <c r="P60">
-        <v>-124.9803186799999</v>
+        <v>-137.0823931400001</v>
       </c>
       <c r="Q60">
-        <v>27.61968131999998</v>
+        <v>15.51760685999986</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1358407885858272</v>
+        <v>0.1380369053806035</v>
       </c>
       <c r="T60">
-        <v>2.079463939626494</v>
+        <v>2.130182572300311</v>
       </c>
       <c r="U60">
         <v>0.1186</v>
       </c>
       <c r="V60">
-        <v>0.2465835443052714</v>
+        <v>0.2424041621984024</v>
       </c>
       <c r="W60">
-        <v>0.08935519164539482</v>
+        <v>0.08985086636326949</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8219451476842381</v>
+        <v>0.8080138739946746</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1096071423603764</v>
+        <v>0.1622386949392388</v>
       </c>
       <c r="C61">
-        <v>1245.626193825676</v>
+        <v>-2811.095221203417</v>
       </c>
       <c r="D61">
-        <v>8652.333193825676</v>
+        <v>4741.384778796582</v>
       </c>
       <c r="E61">
-        <v>6343.107</v>
+        <v>6488.879999999999</v>
       </c>
       <c r="F61">
-        <v>8600.607</v>
+        <v>8746.379999999999</v>
       </c>
       <c r="G61">
         <v>1193.9</v>
@@ -6295,45 +6295,45 @@
         <v>824.2</v>
       </c>
       <c r="M61">
-        <v>1020.0319902</v>
+        <v>1756.273104</v>
       </c>
       <c r="N61">
-        <v>-195.8319902000001</v>
+        <v>-932.0731039999998</v>
       </c>
       <c r="O61">
-        <v>-58.74959706000001</v>
+        <v>-279.6219311999999</v>
       </c>
       <c r="P61">
-        <v>-137.0823931400001</v>
+        <v>-652.4511727999999</v>
       </c>
       <c r="Q61">
-        <v>15.51760685999986</v>
+        <v>-499.8511728</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1380369053806035</v>
+        <v>0.1468017094622744</v>
       </c>
       <c r="T61">
-        <v>2.130182572300311</v>
+        <v>2.332602989890862</v>
       </c>
       <c r="U61">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.2424041621984024</v>
+        <v>0.1407867600072295</v>
       </c>
       <c r="W61">
-        <v>0.08985086636326949</v>
+        <v>0.1725300185905483</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.8080138739946746</v>
+        <v>0.4692892000240984</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1622386949392388</v>
+        <v>0.1637886949392387</v>
       </c>
       <c r="C62">
-        <v>-2811.095221203417</v>
+        <v>-3019.15509038965</v>
       </c>
       <c r="D62">
-        <v>4741.384778796582</v>
+        <v>4679.09790961035</v>
       </c>
       <c r="E62">
-        <v>6488.879999999999</v>
+        <v>6634.653</v>
       </c>
       <c r="F62">
-        <v>8746.379999999999</v>
+        <v>8892.153</v>
       </c>
       <c r="G62">
         <v>1193.9</v>
@@ -6377,37 +6377,37 @@
         <v>824.2</v>
       </c>
       <c r="M62">
-        <v>1756.273104</v>
+        <v>1785.5443224</v>
       </c>
       <c r="N62">
-        <v>-932.0731039999998</v>
+        <v>-961.3443224</v>
       </c>
       <c r="O62">
-        <v>-279.6219311999999</v>
+        <v>-288.40329672</v>
       </c>
       <c r="P62">
-        <v>-652.4511727999999</v>
+        <v>-672.9410256799999</v>
       </c>
       <c r="Q62">
-        <v>-499.8511728</v>
+        <v>-520.34102568</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1468017094622744</v>
+        <v>0.149391496884384</v>
       </c>
       <c r="T62">
-        <v>2.332602989890862</v>
+        <v>2.392413322964987</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1407867600072295</v>
+        <v>0.1384787803349798</v>
       </c>
       <c r="W62">
-        <v>0.1725300185905483</v>
+        <v>0.172993460908736</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4692892000240984</v>
+        <v>0.4615959344499327</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1637886949392387</v>
+        <v>0.1653386949392387</v>
       </c>
       <c r="C63">
-        <v>-3019.15509038965</v>
+        <v>-3225.599672621516</v>
       </c>
       <c r="D63">
-        <v>4679.09790961035</v>
+        <v>4618.426327378484</v>
       </c>
       <c r="E63">
-        <v>6634.653</v>
+        <v>6780.425999999999</v>
       </c>
       <c r="F63">
-        <v>8892.153</v>
+        <v>9037.925999999999</v>
       </c>
       <c r="G63">
         <v>1193.9</v>
@@ -6459,37 +6459,37 @@
         <v>824.2</v>
       </c>
       <c r="M63">
-        <v>1785.5443224</v>
+        <v>1814.8155408</v>
       </c>
       <c r="N63">
-        <v>-961.3443224</v>
+        <v>-990.6155408</v>
       </c>
       <c r="O63">
-        <v>-288.40329672</v>
+        <v>-297.18466224</v>
       </c>
       <c r="P63">
-        <v>-672.9410256799999</v>
+        <v>-693.43087856</v>
       </c>
       <c r="Q63">
-        <v>-520.34102568</v>
+        <v>-540.8308785600001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.149391496884384</v>
+        <v>0.1521175889076572</v>
       </c>
       <c r="T63">
-        <v>2.392413322964987</v>
+        <v>2.455371568306171</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1384787803349798</v>
+        <v>0.1362452516198995</v>
       </c>
       <c r="W63">
-        <v>0.172993460908736</v>
+        <v>0.1734419534747242</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4615959344499327</v>
+        <v>0.4541508387329983</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1653386949392387</v>
+        <v>0.1668886949392387</v>
       </c>
       <c r="C64">
-        <v>-3225.599672621516</v>
+        <v>-3430.49099750749</v>
       </c>
       <c r="D64">
-        <v>4618.426327378484</v>
+        <v>4559.308002492509</v>
       </c>
       <c r="E64">
-        <v>6780.425999999999</v>
+        <v>6926.198999999999</v>
       </c>
       <c r="F64">
-        <v>9037.925999999999</v>
+        <v>9183.698999999999</v>
       </c>
       <c r="G64">
         <v>1193.9</v>
@@ -6541,37 +6541,37 @@
         <v>824.2</v>
       </c>
       <c r="M64">
-        <v>1814.8155408</v>
+        <v>1844.0867592</v>
       </c>
       <c r="N64">
-        <v>-990.6155408</v>
+        <v>-1019.8867592</v>
       </c>
       <c r="O64">
-        <v>-297.18466224</v>
+        <v>-305.9660277599999</v>
       </c>
       <c r="P64">
-        <v>-693.43087856</v>
+        <v>-713.9207314399998</v>
       </c>
       <c r="Q64">
-        <v>-540.8308785600001</v>
+        <v>-561.3207314399999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1521175889076572</v>
+        <v>0.1549910372565128</v>
       </c>
       <c r="T64">
-        <v>2.455371568306171</v>
+        <v>2.521732962044176</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1362452516198995</v>
+        <v>0.1340826285783138</v>
       </c>
       <c r="W64">
-        <v>0.1734419534747242</v>
+        <v>0.1738762081814746</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4541508387329983</v>
+        <v>0.4469420952610461</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1668886949392387</v>
+        <v>0.1684386949392387</v>
       </c>
       <c r="C65">
-        <v>-3430.49099750749</v>
+        <v>-3633.887958748801</v>
       </c>
       <c r="D65">
-        <v>4559.308002492509</v>
+        <v>4501.684041251199</v>
       </c>
       <c r="E65">
-        <v>6926.198999999999</v>
+        <v>7071.972</v>
       </c>
       <c r="F65">
-        <v>9183.698999999999</v>
+        <v>9329.472</v>
       </c>
       <c r="G65">
         <v>1193.9</v>
@@ -6623,37 +6623,37 @@
         <v>824.2</v>
       </c>
       <c r="M65">
-        <v>1844.0867592</v>
+        <v>1873.3579776</v>
       </c>
       <c r="N65">
-        <v>-1019.8867592</v>
+        <v>-1049.1579776</v>
       </c>
       <c r="O65">
-        <v>-305.9660277599999</v>
+        <v>-314.7473932799999</v>
       </c>
       <c r="P65">
-        <v>-713.9207314399998</v>
+        <v>-734.41058432</v>
       </c>
       <c r="Q65">
-        <v>-561.3207314399999</v>
+        <v>-581.8105843200001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1549910372565128</v>
+        <v>0.1580241216247493</v>
       </c>
       <c r="T65">
-        <v>2.521732962044176</v>
+        <v>2.591781099878736</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1340826285783138</v>
+        <v>0.1319875875067777</v>
       </c>
       <c r="W65">
-        <v>0.1738762081814746</v>
+        <v>0.174296892428639</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4469420952610461</v>
+        <v>0.4399586250225922</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1684386949392387</v>
+        <v>0.1699886949392387</v>
       </c>
       <c r="C66">
-        <v>-3633.887958748801</v>
+        <v>-3835.846509835823</v>
       </c>
       <c r="D66">
-        <v>4501.684041251199</v>
+        <v>4445.498490164176</v>
       </c>
       <c r="E66">
-        <v>7071.972</v>
+        <v>7217.744999999999</v>
       </c>
       <c r="F66">
-        <v>9329.472</v>
+        <v>9475.244999999999</v>
       </c>
       <c r="G66">
         <v>1193.9</v>
@@ -6705,37 +6705,37 @@
         <v>824.2</v>
       </c>
       <c r="M66">
-        <v>1873.3579776</v>
+        <v>1902.629196</v>
       </c>
       <c r="N66">
-        <v>-1049.1579776</v>
+        <v>-1078.429196</v>
       </c>
       <c r="O66">
-        <v>-314.7473932799999</v>
+        <v>-323.5287587999999</v>
       </c>
       <c r="P66">
-        <v>-734.41058432</v>
+        <v>-754.9004371999999</v>
       </c>
       <c r="Q66">
-        <v>-581.8105843200001</v>
+        <v>-602.3004372</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1580241216247493</v>
+        <v>0.1612305250997421</v>
       </c>
       <c r="T66">
-        <v>2.591781099878736</v>
+        <v>2.6658319884467</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1319875875067777</v>
+        <v>0.1299570092374426</v>
       </c>
       <c r="W66">
-        <v>0.174296892428639</v>
+        <v>0.1747046325451215</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4399586250225922</v>
+        <v>0.4331900307914754</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1699886949392387</v>
+        <v>0.1715386949392387</v>
       </c>
       <c r="C67">
-        <v>-3835.846509835823</v>
+        <v>-4036.419845270228</v>
       </c>
       <c r="D67">
-        <v>4445.498490164176</v>
+        <v>4390.698154729773</v>
       </c>
       <c r="E67">
-        <v>7217.744999999999</v>
+        <v>7363.518</v>
       </c>
       <c r="F67">
-        <v>9475.244999999999</v>
+        <v>9621.018</v>
       </c>
       <c r="G67">
         <v>1193.9</v>
@@ -6787,37 +6787,37 @@
         <v>824.2</v>
       </c>
       <c r="M67">
-        <v>1902.629196</v>
+        <v>1931.9004144</v>
       </c>
       <c r="N67">
-        <v>-1078.429196</v>
+        <v>-1107.7004144</v>
       </c>
       <c r="O67">
-        <v>-323.5287587999999</v>
+        <v>-332.31012432</v>
       </c>
       <c r="P67">
-        <v>-754.9004371999999</v>
+        <v>-775.39029008</v>
       </c>
       <c r="Q67">
-        <v>-602.3004372</v>
+        <v>-622.7902900800001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1612305250997421</v>
+        <v>0.1646255405438522</v>
       </c>
       <c r="T67">
-        <v>2.6658319884467</v>
+        <v>2.744238811636309</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1299570092374426</v>
+        <v>0.1279879636429359</v>
       </c>
       <c r="W67">
-        <v>0.1747046325451215</v>
+        <v>0.1751000169004985</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4331900307914754</v>
+        <v>0.4266265454764531</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1715386949392387</v>
+        <v>0.1730886949392387</v>
       </c>
       <c r="C68">
-        <v>-4036.419845270228</v>
+        <v>-4235.658568546594</v>
       </c>
       <c r="D68">
-        <v>4390.698154729773</v>
+        <v>4337.232431453405</v>
       </c>
       <c r="E68">
-        <v>7363.518</v>
+        <v>7509.290999999999</v>
       </c>
       <c r="F68">
-        <v>9621.018</v>
+        <v>9766.790999999999</v>
       </c>
       <c r="G68">
         <v>1193.9</v>
@@ -6869,37 +6869,37 @@
         <v>824.2</v>
       </c>
       <c r="M68">
-        <v>1931.9004144</v>
+        <v>1961.1716328</v>
       </c>
       <c r="N68">
-        <v>-1107.7004144</v>
+        <v>-1136.9716328</v>
       </c>
       <c r="O68">
-        <v>-332.31012432</v>
+        <v>-341.09148984</v>
       </c>
       <c r="P68">
-        <v>-775.39029008</v>
+        <v>-795.8801429600001</v>
       </c>
       <c r="Q68">
-        <v>-622.7902900800001</v>
+        <v>-643.2801429600001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1646255405438522</v>
+        <v>0.1682263144997265</v>
       </c>
       <c r="T68">
-        <v>2.744238811636309</v>
+        <v>2.827397563504076</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1279879636429359</v>
+        <v>0.1260776955288622</v>
       </c>
       <c r="W68">
-        <v>0.1751000169004985</v>
+        <v>0.1754835987378044</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4266265454764531</v>
+        <v>0.4202589850962074</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1730886949392387</v>
+        <v>0.1746386949392388</v>
       </c>
       <c r="C69">
-        <v>-4235.658568546594</v>
+        <v>-4433.610848008586</v>
       </c>
       <c r="D69">
-        <v>4337.232431453405</v>
+        <v>4285.053151991414</v>
       </c>
       <c r="E69">
-        <v>7509.290999999999</v>
+        <v>7655.064</v>
       </c>
       <c r="F69">
-        <v>9766.790999999999</v>
+        <v>9912.564</v>
       </c>
       <c r="G69">
         <v>1193.9</v>
@@ -6951,37 +6951,37 @@
         <v>824.2</v>
       </c>
       <c r="M69">
-        <v>1961.1716328</v>
+        <v>1990.4428512</v>
       </c>
       <c r="N69">
-        <v>-1136.9716328</v>
+        <v>-1166.2428512</v>
       </c>
       <c r="O69">
-        <v>-341.09148984</v>
+        <v>-349.87285536</v>
       </c>
       <c r="P69">
-        <v>-795.8801429600001</v>
+        <v>-816.3699958400001</v>
       </c>
       <c r="Q69">
-        <v>-643.2801429600001</v>
+        <v>-663.7699958400002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1682263144997265</v>
+        <v>0.172052136827843</v>
       </c>
       <c r="T69">
-        <v>2.827397563504076</v>
+        <v>2.915753737363578</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1260776955288622</v>
+        <v>0.1242236117710848</v>
       </c>
       <c r="W69">
-        <v>0.1754835987378044</v>
+        <v>0.1758558987563662</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4202589850962074</v>
+        <v>0.4140787059036162</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1746386949392388</v>
+        <v>0.1761886949392387</v>
       </c>
       <c r="C70">
-        <v>-4433.610848008586</v>
+        <v>-4630.322561588637</v>
       </c>
       <c r="D70">
-        <v>4285.053151991414</v>
+        <v>4234.114438411362</v>
       </c>
       <c r="E70">
-        <v>7655.064</v>
+        <v>7800.837</v>
       </c>
       <c r="F70">
-        <v>9912.564</v>
+        <v>10058.337</v>
       </c>
       <c r="G70">
         <v>1193.9</v>
@@ -7033,37 +7033,37 @@
         <v>824.2</v>
       </c>
       <c r="M70">
-        <v>1990.4428512</v>
+        <v>2019.7140696</v>
       </c>
       <c r="N70">
-        <v>-1166.2428512</v>
+        <v>-1195.5140696</v>
       </c>
       <c r="O70">
-        <v>-349.87285536</v>
+        <v>-358.65422088</v>
       </c>
       <c r="P70">
-        <v>-816.3699958400001</v>
+        <v>-836.8598487199999</v>
       </c>
       <c r="Q70">
-        <v>-663.7699958400002</v>
+        <v>-684.25984872</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.172052136827843</v>
+        <v>0.1761247864029347</v>
       </c>
       <c r="T70">
-        <v>2.915753737363578</v>
+        <v>3.009810309536597</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1242236117710848</v>
+        <v>0.1224232695715039</v>
       </c>
       <c r="W70">
-        <v>0.1758558987563662</v>
+        <v>0.176217407470042</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4140787059036162</v>
+        <v>0.4080775652383464</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1761886949392387</v>
+        <v>0.1777386949392387</v>
       </c>
       <c r="C71">
-        <v>-4630.322561588637</v>
+        <v>-4825.837431345348</v>
       </c>
       <c r="D71">
-        <v>4234.114438411362</v>
+        <v>4184.372568654653</v>
       </c>
       <c r="E71">
-        <v>7800.837</v>
+        <v>7946.610000000001</v>
       </c>
       <c r="F71">
-        <v>10058.337</v>
+        <v>10204.11</v>
       </c>
       <c r="G71">
         <v>1193.9</v>
@@ -7115,37 +7115,37 @@
         <v>824.2</v>
       </c>
       <c r="M71">
-        <v>2019.7140696</v>
+        <v>2048.985288</v>
       </c>
       <c r="N71">
-        <v>-1195.5140696</v>
+        <v>-1224.785288</v>
       </c>
       <c r="O71">
-        <v>-358.65422088</v>
+        <v>-367.4355864000001</v>
       </c>
       <c r="P71">
-        <v>-836.8598487199999</v>
+        <v>-857.3497016000001</v>
       </c>
       <c r="Q71">
-        <v>-684.25984872</v>
+        <v>-704.7497016000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1761247864029347</v>
+        <v>0.1804689459496992</v>
       </c>
       <c r="T71">
-        <v>3.009810309536597</v>
+        <v>3.110137319854484</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1224232695715039</v>
+        <v>0.1206743657204824</v>
       </c>
       <c r="W71">
-        <v>0.176217407470042</v>
+        <v>0.1765685873633271</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4080775652383464</v>
+        <v>0.4022478857349414</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1777386949392387</v>
+        <v>0.1792886949392388</v>
       </c>
       <c r="C72">
-        <v>-4825.837431345348</v>
+        <v>-5020.197148627787</v>
       </c>
       <c r="D72">
-        <v>4184.372568654653</v>
+        <v>4135.785851372213</v>
       </c>
       <c r="E72">
-        <v>7946.610000000001</v>
+        <v>8092.383</v>
       </c>
       <c r="F72">
-        <v>10204.11</v>
+        <v>10349.883</v>
       </c>
       <c r="G72">
         <v>1193.9</v>
@@ -7197,37 +7197,37 @@
         <v>824.2</v>
       </c>
       <c r="M72">
-        <v>2048.985288</v>
+        <v>2078.2565064</v>
       </c>
       <c r="N72">
-        <v>-1224.785288</v>
+        <v>-1254.0565064</v>
       </c>
       <c r="O72">
-        <v>-367.4355864000001</v>
+        <v>-376.21695192</v>
       </c>
       <c r="P72">
-        <v>-857.3497016000001</v>
+        <v>-877.8395544800001</v>
       </c>
       <c r="Q72">
-        <v>-704.7497016000002</v>
+        <v>-725.2395544800002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1804689459496992</v>
+        <v>0.1851127027065854</v>
       </c>
       <c r="T72">
-        <v>3.110137319854484</v>
+        <v>3.217383434332225</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1206743657204824</v>
+        <v>0.1189747267666728</v>
       </c>
       <c r="W72">
-        <v>0.1765685873633271</v>
+        <v>0.1769098748652521</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4022478857349414</v>
+        <v>0.3965824225555761</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1792886949392387</v>
+        <v>0.1808386949392387</v>
       </c>
       <c r="C73">
-        <v>-5020.197148627785</v>
+        <v>-5213.441490619881</v>
       </c>
       <c r="D73">
-        <v>4135.785851372214</v>
+        <v>4088.314509380118</v>
       </c>
       <c r="E73">
-        <v>8092.383</v>
+        <v>8238.155999999999</v>
       </c>
       <c r="F73">
-        <v>10349.883</v>
+        <v>10495.656</v>
       </c>
       <c r="G73">
         <v>1193.9</v>
@@ -7279,37 +7279,37 @@
         <v>824.2</v>
       </c>
       <c r="M73">
-        <v>2078.2565064</v>
+        <v>2107.5277248</v>
       </c>
       <c r="N73">
-        <v>-1254.0565064</v>
+        <v>-1283.3277248</v>
       </c>
       <c r="O73">
-        <v>-376.21695192</v>
+        <v>-384.9983174399999</v>
       </c>
       <c r="P73">
-        <v>-877.8395544800001</v>
+        <v>-898.3294073599998</v>
       </c>
       <c r="Q73">
-        <v>-725.2395544800002</v>
+        <v>-745.7294073599999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1851127027065853</v>
+        <v>0.1900881563746776</v>
       </c>
       <c r="T73">
-        <v>3.217383434332224</v>
+        <v>3.332289985558374</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1189747267666728</v>
+        <v>0.1173223000060246</v>
       </c>
       <c r="W73">
-        <v>0.1769098748652521</v>
+        <v>0.1772416821587903</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3965824225555761</v>
+        <v>0.3910743333534153</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1808386949392387</v>
+        <v>0.1823886949392387</v>
       </c>
       <c r="C74">
-        <v>-5213.441490619881</v>
+        <v>-5405.608428949537</v>
       </c>
       <c r="D74">
-        <v>4088.314509380118</v>
+        <v>4041.920571050463</v>
       </c>
       <c r="E74">
-        <v>8238.155999999999</v>
+        <v>8383.929</v>
       </c>
       <c r="F74">
-        <v>10495.656</v>
+        <v>10641.429</v>
       </c>
       <c r="G74">
         <v>1193.9</v>
@@ -7361,37 +7361,37 @@
         <v>824.2</v>
       </c>
       <c r="M74">
-        <v>2107.5277248</v>
+        <v>2136.7989432</v>
       </c>
       <c r="N74">
-        <v>-1283.3277248</v>
+        <v>-1312.5989432</v>
       </c>
       <c r="O74">
-        <v>-384.9983174399999</v>
+        <v>-393.7796829599999</v>
       </c>
       <c r="P74">
-        <v>-898.3294073599998</v>
+        <v>-918.8192602399999</v>
       </c>
       <c r="Q74">
-        <v>-745.7294073599999</v>
+        <v>-766.21926024</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1900881563746776</v>
+        <v>0.1954321621663323</v>
       </c>
       <c r="T74">
-        <v>3.332289985558374</v>
+        <v>3.455708133171647</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1173223000060246</v>
+        <v>0.1157151452114215</v>
       </c>
       <c r="W74">
-        <v>0.1772416821587903</v>
+        <v>0.1775643988415466</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3910743333534153</v>
+        <v>0.3857171507047383</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1823886949392387</v>
+        <v>0.1839386949392388</v>
       </c>
       <c r="C75">
-        <v>-5405.608428949537</v>
+        <v>-5596.734230985809</v>
       </c>
       <c r="D75">
-        <v>4041.920571050463</v>
+        <v>3996.567769014191</v>
       </c>
       <c r="E75">
-        <v>8383.929</v>
+        <v>8529.701999999999</v>
       </c>
       <c r="F75">
-        <v>10641.429</v>
+        <v>10787.202</v>
       </c>
       <c r="G75">
         <v>1193.9</v>
@@ -7443,37 +7443,37 @@
         <v>824.2</v>
       </c>
       <c r="M75">
-        <v>2136.7989432</v>
+        <v>2166.0701616</v>
       </c>
       <c r="N75">
-        <v>-1312.5989432</v>
+        <v>-1341.8701616</v>
       </c>
       <c r="O75">
-        <v>-393.7796829599999</v>
+        <v>-402.56104848</v>
       </c>
       <c r="P75">
-        <v>-918.8192602399999</v>
+        <v>-939.3091131200001</v>
       </c>
       <c r="Q75">
-        <v>-766.21926024</v>
+        <v>-786.7091131200002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1954321621663323</v>
+        <v>0.2011872453265759</v>
       </c>
       <c r="T75">
-        <v>3.455708133171647</v>
+        <v>3.58861998444748</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1157151452114215</v>
+        <v>0.1141514270328888</v>
       </c>
       <c r="W75">
-        <v>0.1775643988415466</v>
+        <v>0.177878393451796</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3857171507047383</v>
+        <v>0.3805047567762959</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1839386949392388</v>
+        <v>0.1854886949392388</v>
       </c>
       <c r="C76">
-        <v>-5596.734230985809</v>
+        <v>-5786.853554392055</v>
       </c>
       <c r="D76">
-        <v>3996.567769014191</v>
+        <v>3952.221445607943</v>
       </c>
       <c r="E76">
-        <v>8529.701999999999</v>
+        <v>8675.474999999999</v>
       </c>
       <c r="F76">
-        <v>10787.202</v>
+        <v>10932.975</v>
       </c>
       <c r="G76">
         <v>1193.9</v>
@@ -7525,37 +7525,37 @@
         <v>824.2</v>
       </c>
       <c r="M76">
-        <v>2166.0701616</v>
+        <v>2195.34138</v>
       </c>
       <c r="N76">
-        <v>-1341.8701616</v>
+        <v>-1371.14138</v>
       </c>
       <c r="O76">
-        <v>-402.56104848</v>
+        <v>-411.3424139999999</v>
       </c>
       <c r="P76">
-        <v>-939.3091131200001</v>
+        <v>-959.7989659999998</v>
       </c>
       <c r="Q76">
-        <v>-786.7091131200002</v>
+        <v>-807.1989659999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2011872453265759</v>
+        <v>0.207402735139639</v>
       </c>
       <c r="T76">
-        <v>3.58861998444748</v>
+        <v>3.73216478382538</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1141514270328888</v>
+        <v>0.1126294080057836</v>
       </c>
       <c r="W76">
-        <v>0.177878393451796</v>
+        <v>0.1781840148724387</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3805047567762959</v>
+        <v>0.3754313600192787</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1854886949392388</v>
+        <v>0.1870386949392387</v>
       </c>
       <c r="C77">
-        <v>-5786.853554392055</v>
+        <v>-5975.999535453144</v>
       </c>
       <c r="D77">
-        <v>3952.221445607943</v>
+        <v>3908.848464546856</v>
       </c>
       <c r="E77">
-        <v>8675.474999999999</v>
+        <v>8821.248</v>
       </c>
       <c r="F77">
-        <v>10932.975</v>
+        <v>11078.748</v>
       </c>
       <c r="G77">
         <v>1193.9</v>
@@ -7607,37 +7607,37 @@
         <v>824.2</v>
       </c>
       <c r="M77">
-        <v>2195.34138</v>
+        <v>2224.6125984</v>
       </c>
       <c r="N77">
-        <v>-1371.14138</v>
+        <v>-1400.4125984</v>
       </c>
       <c r="O77">
-        <v>-411.3424139999999</v>
+        <v>-420.12377952</v>
       </c>
       <c r="P77">
-        <v>-959.7989659999998</v>
+        <v>-980.28881888</v>
       </c>
       <c r="Q77">
-        <v>-807.1989659999999</v>
+        <v>-827.6888188800001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.207402735139639</v>
+        <v>0.214136182437124</v>
       </c>
       <c r="T77">
-        <v>3.73216478382538</v>
+        <v>3.887671649818104</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1126294080057836</v>
+        <v>0.1111474421109707</v>
       </c>
       <c r="W77">
-        <v>0.1781840148724387</v>
+        <v>0.1784815936241171</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3754313600192787</v>
+        <v>0.3704914737032355</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1870386949392387</v>
+        <v>0.1885886949392387</v>
       </c>
       <c r="C78">
-        <v>-5975.999535453144</v>
+        <v>-6164.20387164979</v>
       </c>
       <c r="D78">
-        <v>3908.848464546856</v>
+        <v>3866.417128350208</v>
       </c>
       <c r="E78">
-        <v>8821.248</v>
+        <v>8967.020999999999</v>
       </c>
       <c r="F78">
-        <v>11078.748</v>
+        <v>11224.521</v>
       </c>
       <c r="G78">
         <v>1193.9</v>
@@ -7689,37 +7689,37 @@
         <v>824.2</v>
       </c>
       <c r="M78">
-        <v>2224.6125984</v>
+        <v>2253.8838168</v>
       </c>
       <c r="N78">
-        <v>-1400.4125984</v>
+        <v>-1429.6838168</v>
       </c>
       <c r="O78">
-        <v>-420.12377952</v>
+        <v>-428.9051450399999</v>
       </c>
       <c r="P78">
-        <v>-980.28881888</v>
+        <v>-1000.77867176</v>
       </c>
       <c r="Q78">
-        <v>-827.6888188800001</v>
+        <v>-848.1786717599998</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.214136182437124</v>
+        <v>0.2214551468909119</v>
       </c>
       <c r="T78">
-        <v>3.887671649818104</v>
+        <v>4.056700851984108</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1111474421109707</v>
+        <v>0.1097039688368022</v>
       </c>
       <c r="W78">
-        <v>0.1784815936241171</v>
+        <v>0.1787714430575701</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3704914737032355</v>
+        <v>0.365679896122674</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1885886949392387</v>
+        <v>0.1901386949392387</v>
       </c>
       <c r="C79">
-        <v>-6164.20387164979</v>
+        <v>-6351.496898912515</v>
       </c>
       <c r="D79">
-        <v>3866.417128350208</v>
+        <v>3824.897101087485</v>
       </c>
       <c r="E79">
-        <v>8967.020999999999</v>
+        <v>9112.794</v>
       </c>
       <c r="F79">
-        <v>11224.521</v>
+        <v>11370.294</v>
       </c>
       <c r="G79">
         <v>1193.9</v>
@@ -7771,37 +7771,37 @@
         <v>824.2</v>
       </c>
       <c r="M79">
-        <v>2253.8838168</v>
+        <v>2283.1550352</v>
       </c>
       <c r="N79">
-        <v>-1429.6838168</v>
+        <v>-1458.9550352</v>
       </c>
       <c r="O79">
-        <v>-428.9051450399999</v>
+        <v>-437.6865105599999</v>
       </c>
       <c r="P79">
-        <v>-1000.77867176</v>
+        <v>-1021.26852464</v>
       </c>
       <c r="Q79">
-        <v>-848.1786717599998</v>
+        <v>-868.66852464</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2214551468909119</v>
+        <v>0.2294394717495898</v>
       </c>
       <c r="T79">
-        <v>4.056700851984108</v>
+        <v>4.241096345256114</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1097039688368022</v>
+        <v>0.1082975076978688</v>
       </c>
       <c r="W79">
-        <v>0.1787714430575701</v>
+        <v>0.1790538604542679</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.365679896122674</v>
+        <v>0.3609916923262295</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1901386949392387</v>
+        <v>0.1916886949392387</v>
       </c>
       <c r="C80">
-        <v>-6351.496898912515</v>
+        <v>-6537.907663950818</v>
       </c>
       <c r="D80">
-        <v>3824.897101087485</v>
+        <v>3784.259336049181</v>
       </c>
       <c r="E80">
-        <v>9112.794</v>
+        <v>9258.566999999999</v>
       </c>
       <c r="F80">
-        <v>11370.294</v>
+        <v>11516.067</v>
       </c>
       <c r="G80">
         <v>1193.9</v>
@@ -7853,37 +7853,37 @@
         <v>824.2</v>
       </c>
       <c r="M80">
-        <v>2283.1550352</v>
+        <v>2312.4262536</v>
       </c>
       <c r="N80">
-        <v>-1458.9550352</v>
+        <v>-1488.2262536</v>
       </c>
       <c r="O80">
-        <v>-437.6865105599999</v>
+        <v>-446.46787608</v>
       </c>
       <c r="P80">
-        <v>-1021.26852464</v>
+        <v>-1041.75837752</v>
       </c>
       <c r="Q80">
-        <v>-868.66852464</v>
+        <v>-889.1583775200002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2294394717495898</v>
+        <v>0.2381842084995702</v>
       </c>
       <c r="T80">
-        <v>4.241096345256114</v>
+        <v>4.443053314077834</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1082975076978688</v>
+        <v>0.1069266531700477</v>
       </c>
       <c r="W80">
-        <v>0.1790538604542679</v>
+        <v>0.1793291280434544</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3609916923262295</v>
+        <v>0.3564221772334923</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1916886949392387</v>
+        <v>0.1932386949392388</v>
       </c>
       <c r="C81">
-        <v>-6537.907663950818</v>
+        <v>-6723.463992020112</v>
       </c>
       <c r="D81">
-        <v>3784.259336049181</v>
+        <v>3744.476007979888</v>
       </c>
       <c r="E81">
-        <v>9258.566999999999</v>
+        <v>9404.34</v>
       </c>
       <c r="F81">
-        <v>11516.067</v>
+        <v>11661.84</v>
       </c>
       <c r="G81">
         <v>1193.9</v>
@@ -7935,37 +7935,37 @@
         <v>824.2</v>
       </c>
       <c r="M81">
-        <v>2312.4262536</v>
+        <v>2341.697472</v>
       </c>
       <c r="N81">
-        <v>-1488.2262536</v>
+        <v>-1517.497472</v>
       </c>
       <c r="O81">
-        <v>-446.46787608</v>
+        <v>-455.2492416000001</v>
       </c>
       <c r="P81">
-        <v>-1041.75837752</v>
+        <v>-1062.2482304</v>
       </c>
       <c r="Q81">
-        <v>-889.1583775200002</v>
+        <v>-909.6482304000003</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2381842084995702</v>
+        <v>0.2478034189245488</v>
       </c>
       <c r="T81">
-        <v>4.443053314077834</v>
+        <v>4.665205979781726</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1069266531700477</v>
+        <v>0.1055900700054221</v>
       </c>
       <c r="W81">
-        <v>0.1793291280434544</v>
+        <v>0.1795975139429113</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3564221772334923</v>
+        <v>0.3519669000180737</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1932386949392388</v>
+        <v>0.1947886949392387</v>
       </c>
       <c r="C82">
-        <v>-6723.463992020112</v>
+        <v>-6908.192550458526</v>
       </c>
       <c r="D82">
-        <v>3744.476007979888</v>
+        <v>3705.520449541473</v>
       </c>
       <c r="E82">
-        <v>9404.34</v>
+        <v>9550.112999999999</v>
       </c>
       <c r="F82">
-        <v>11661.84</v>
+        <v>11807.613</v>
       </c>
       <c r="G82">
         <v>1193.9</v>
@@ -8017,37 +8017,37 @@
         <v>824.2</v>
       </c>
       <c r="M82">
-        <v>2341.697472</v>
+        <v>2370.9686904</v>
       </c>
       <c r="N82">
-        <v>-1517.497472</v>
+        <v>-1546.7686904</v>
       </c>
       <c r="O82">
-        <v>-455.2492416000001</v>
+        <v>-464.03060712</v>
       </c>
       <c r="P82">
-        <v>-1062.2482304</v>
+        <v>-1082.73808328</v>
       </c>
       <c r="Q82">
-        <v>-909.6482304000003</v>
+        <v>-930.13808328</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2478034189245488</v>
+        <v>0.2584351778153144</v>
       </c>
       <c r="T82">
-        <v>4.665205979781726</v>
+        <v>4.910743136612343</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1055900700054221</v>
+        <v>0.1042864888942441</v>
       </c>
       <c r="W82">
-        <v>0.1795975139429113</v>
+        <v>0.1798592730300358</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3519669000180737</v>
+        <v>0.3476216296474802</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1947886949392387</v>
+        <v>0.1963386949392387</v>
       </c>
       <c r="C83">
-        <v>-6908.192550458526</v>
+        <v>-7092.118908298566</v>
       </c>
       <c r="D83">
-        <v>3705.520449541473</v>
+        <v>3667.367091701434</v>
       </c>
       <c r="E83">
-        <v>9550.112999999999</v>
+        <v>9695.886</v>
       </c>
       <c r="F83">
-        <v>11807.613</v>
+        <v>11953.386</v>
       </c>
       <c r="G83">
         <v>1193.9</v>
@@ -8099,37 +8099,37 @@
         <v>824.2</v>
       </c>
       <c r="M83">
-        <v>2370.9686904</v>
+        <v>2400.2399088</v>
       </c>
       <c r="N83">
-        <v>-1546.7686904</v>
+        <v>-1576.0399088</v>
       </c>
       <c r="O83">
-        <v>-464.03060712</v>
+        <v>-472.81197264</v>
       </c>
       <c r="P83">
-        <v>-1082.73808328</v>
+        <v>-1103.22793616</v>
       </c>
       <c r="Q83">
-        <v>-930.13808328</v>
+        <v>-950.6279361600002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2584351778153144</v>
+        <v>0.2702482432494986</v>
       </c>
       <c r="T83">
-        <v>4.910743136612343</v>
+        <v>5.183562199757473</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1042864888942441</v>
+        <v>0.1030147024443143</v>
       </c>
       <c r="W83">
-        <v>0.1798592730300358</v>
+        <v>0.1801146477491817</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3476216296474802</v>
+        <v>0.3433823414810475</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1963386949392387</v>
+        <v>0.1978886949392387</v>
       </c>
       <c r="C84">
-        <v>-7092.118908298566</v>
+        <v>-7275.267592233577</v>
       </c>
       <c r="D84">
-        <v>3667.367091701434</v>
+        <v>3629.991407766423</v>
       </c>
       <c r="E84">
-        <v>9695.886</v>
+        <v>9841.659</v>
       </c>
       <c r="F84">
-        <v>11953.386</v>
+        <v>12099.159</v>
       </c>
       <c r="G84">
         <v>1193.9</v>
@@ -8181,37 +8181,37 @@
         <v>824.2</v>
       </c>
       <c r="M84">
-        <v>2400.2399088</v>
+        <v>2429.5111272</v>
       </c>
       <c r="N84">
-        <v>-1576.0399088</v>
+        <v>-1605.3111272</v>
       </c>
       <c r="O84">
-        <v>-472.81197264</v>
+        <v>-481.5933381599999</v>
       </c>
       <c r="P84">
-        <v>-1103.22793616</v>
+        <v>-1123.71778904</v>
       </c>
       <c r="Q84">
-        <v>-950.6279361600002</v>
+        <v>-971.1177890399999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2702482432494986</v>
+        <v>0.2834510810877044</v>
       </c>
       <c r="T84">
-        <v>5.183562199757473</v>
+        <v>5.488477623272619</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1030147024443143</v>
+        <v>0.1017735614510093</v>
       </c>
       <c r="W84">
-        <v>0.1801146477491817</v>
+        <v>0.1803638688606373</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3433823414810475</v>
+        <v>0.3392452048366976</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1978886949392387</v>
+        <v>0.1994386949392387</v>
       </c>
       <c r="C85">
-        <v>-7275.267592233577</v>
+        <v>-7457.662139196491</v>
       </c>
       <c r="D85">
-        <v>3629.991407766423</v>
+        <v>3593.369860803509</v>
       </c>
       <c r="E85">
-        <v>9841.659</v>
+        <v>9987.432000000001</v>
       </c>
       <c r="F85">
-        <v>12099.159</v>
+        <v>12244.932</v>
       </c>
       <c r="G85">
         <v>1193.9</v>
@@ -8263,37 +8263,37 @@
         <v>824.2</v>
       </c>
       <c r="M85">
-        <v>2429.5111272</v>
+        <v>2458.7823456</v>
       </c>
       <c r="N85">
-        <v>-1605.3111272</v>
+        <v>-1634.5823456</v>
       </c>
       <c r="O85">
-        <v>-481.5933381599999</v>
+        <v>-490.37470368</v>
       </c>
       <c r="P85">
-        <v>-1123.71778904</v>
+        <v>-1144.20764192</v>
       </c>
       <c r="Q85">
-        <v>-971.1177890399999</v>
+        <v>-991.6076419200001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2834510810877044</v>
+        <v>0.298304273655686</v>
       </c>
       <c r="T85">
-        <v>5.488477623272619</v>
+        <v>5.831507474727159</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1017735614510093</v>
+        <v>0.1005619714337354</v>
       </c>
       <c r="W85">
-        <v>0.1803638688606373</v>
+        <v>0.180607156136106</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3392452048366976</v>
+        <v>0.3352065714457845</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1994386949392387</v>
+        <v>0.2009886949392388</v>
       </c>
       <c r="C86">
-        <v>-7457.662139196489</v>
+        <v>-7639.325145787668</v>
       </c>
       <c r="D86">
-        <v>3593.369860803509</v>
+        <v>3557.479854212332</v>
       </c>
       <c r="E86">
-        <v>9987.431999999999</v>
+        <v>10133.205</v>
       </c>
       <c r="F86">
-        <v>12244.932</v>
+        <v>12390.705</v>
       </c>
       <c r="G86">
         <v>1193.9</v>
@@ -8345,37 +8345,37 @@
         <v>824.2</v>
       </c>
       <c r="M86">
-        <v>2458.7823456</v>
+        <v>2488.053564</v>
       </c>
       <c r="N86">
-        <v>-1634.5823456</v>
+        <v>-1663.853564</v>
       </c>
       <c r="O86">
-        <v>-490.3747036799999</v>
+        <v>-499.1560692</v>
       </c>
       <c r="P86">
-        <v>-1144.20764192</v>
+        <v>-1164.6974948</v>
       </c>
       <c r="Q86">
-        <v>-991.6076419199999</v>
+        <v>-1012.0974948</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2983042736556858</v>
+        <v>0.3151378918993982</v>
       </c>
       <c r="T86">
-        <v>5.831507474727156</v>
+        <v>6.220274639708966</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1005619714337354</v>
+        <v>0.09937888941686787</v>
       </c>
       <c r="W86">
-        <v>0.180607156136106</v>
+        <v>0.1808447190050929</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3352065714457846</v>
+        <v>0.3312629647228928</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2009886949392388</v>
+        <v>0.2025386949392387</v>
       </c>
       <c r="C87">
-        <v>-7639.325145787668</v>
+        <v>-7820.278314769976</v>
       </c>
       <c r="D87">
-        <v>3557.479854212332</v>
+        <v>3522.299685230024</v>
       </c>
       <c r="E87">
-        <v>10133.205</v>
+        <v>10278.978</v>
       </c>
       <c r="F87">
-        <v>12390.705</v>
+        <v>12536.478</v>
       </c>
       <c r="G87">
         <v>1193.9</v>
@@ -8427,37 +8427,37 @@
         <v>824.2</v>
       </c>
       <c r="M87">
-        <v>2488.053564</v>
+        <v>2517.3247824</v>
       </c>
       <c r="N87">
-        <v>-1663.853564</v>
+        <v>-1693.1247824</v>
       </c>
       <c r="O87">
-        <v>-499.1560692</v>
+        <v>-507.9374347199999</v>
       </c>
       <c r="P87">
-        <v>-1164.6974948</v>
+        <v>-1185.18734768</v>
       </c>
       <c r="Q87">
-        <v>-1012.0974948</v>
+        <v>-1032.58734768</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3151378918993982</v>
+        <v>0.3343763127493553</v>
       </c>
       <c r="T87">
-        <v>6.220274639708966</v>
+        <v>6.664579971116749</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.09937888941686787</v>
+        <v>0.0982233209352764</v>
       </c>
       <c r="W87">
-        <v>0.1808447190050929</v>
+        <v>0.1810767571561965</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3312629647228928</v>
+        <v>0.3274110697842546</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2025386949392387</v>
+        <v>0.2040886949392388</v>
       </c>
       <c r="C88">
-        <v>-7820.278314769976</v>
+        <v>-8000.542498832126</v>
       </c>
       <c r="D88">
-        <v>3522.299685230024</v>
+        <v>3487.808501167875</v>
       </c>
       <c r="E88">
-        <v>10278.978</v>
+        <v>10424.751</v>
       </c>
       <c r="F88">
-        <v>12536.478</v>
+        <v>12682.251</v>
       </c>
       <c r="G88">
         <v>1193.9</v>
@@ -8509,37 +8509,37 @@
         <v>824.2</v>
       </c>
       <c r="M88">
-        <v>2517.3247824</v>
+        <v>2546.5960008</v>
       </c>
       <c r="N88">
-        <v>-1693.1247824</v>
+        <v>-1722.3960008</v>
       </c>
       <c r="O88">
-        <v>-507.9374347199999</v>
+        <v>-516.7188002400001</v>
       </c>
       <c r="P88">
-        <v>-1185.18734768</v>
+        <v>-1205.67720056</v>
       </c>
       <c r="Q88">
-        <v>-1032.58734768</v>
+        <v>-1053.07720056</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3343763127493553</v>
+        <v>0.3565744906531518</v>
       </c>
       <c r="T88">
-        <v>6.664579971116749</v>
+        <v>7.177239968894961</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.0982233209352764</v>
+        <v>0.09709431724636516</v>
       </c>
       <c r="W88">
-        <v>0.1810767571561965</v>
+        <v>0.1813034610969299</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3274110697842546</v>
+        <v>0.3236477241545506</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2040886949392388</v>
+        <v>0.2056386949392387</v>
       </c>
       <c r="C89">
-        <v>-8000.542498832126</v>
+        <v>-8180.137741805675</v>
       </c>
       <c r="D89">
-        <v>3487.808501167875</v>
+        <v>3453.986258194324</v>
       </c>
       <c r="E89">
-        <v>10424.751</v>
+        <v>10570.524</v>
       </c>
       <c r="F89">
-        <v>12682.251</v>
+        <v>12828.024</v>
       </c>
       <c r="G89">
         <v>1193.9</v>
@@ -8591,37 +8591,37 @@
         <v>824.2</v>
       </c>
       <c r="M89">
-        <v>2546.5960008</v>
+        <v>2575.8672192</v>
       </c>
       <c r="N89">
-        <v>-1722.3960008</v>
+        <v>-1751.6672192</v>
       </c>
       <c r="O89">
-        <v>-516.7188002400001</v>
+        <v>-525.50016576</v>
       </c>
       <c r="P89">
-        <v>-1205.67720056</v>
+        <v>-1226.16705344</v>
       </c>
       <c r="Q89">
-        <v>-1053.07720056</v>
+        <v>-1073.56705344</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3565744906531518</v>
+        <v>0.3824723648742478</v>
       </c>
       <c r="T89">
-        <v>7.177239968894961</v>
+        <v>7.775343299636208</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.09709431724636516</v>
+        <v>0.09599097273220193</v>
       </c>
       <c r="W89">
-        <v>0.1813034610969299</v>
+        <v>0.1815250126753739</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3236477241545506</v>
+        <v>0.3199699091073398</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2056386949392387</v>
+        <v>0.2071886949392387</v>
       </c>
       <c r="C90">
-        <v>-8180.137741805675</v>
+        <v>-8359.083317506946</v>
       </c>
       <c r="D90">
-        <v>3453.986258194324</v>
+        <v>3420.813682493053</v>
       </c>
       <c r="E90">
-        <v>10570.524</v>
+        <v>10716.297</v>
       </c>
       <c r="F90">
-        <v>12828.024</v>
+        <v>12973.797</v>
       </c>
       <c r="G90">
         <v>1193.9</v>
@@ -8673,37 +8673,37 @@
         <v>824.2</v>
       </c>
       <c r="M90">
-        <v>2575.8672192</v>
+        <v>2605.1384376</v>
       </c>
       <c r="N90">
-        <v>-1751.6672192</v>
+        <v>-1780.9384376</v>
       </c>
       <c r="O90">
-        <v>-525.50016576</v>
+        <v>-534.2815312799999</v>
       </c>
       <c r="P90">
-        <v>-1226.16705344</v>
+        <v>-1246.65690632</v>
       </c>
       <c r="Q90">
-        <v>-1073.56705344</v>
+        <v>-1094.05690632</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3824723648742478</v>
+        <v>0.4130789434991795</v>
       </c>
       <c r="T90">
-        <v>7.775343299636208</v>
+        <v>8.482192690512228</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.09599097273220193</v>
+        <v>0.09491242247678394</v>
       </c>
       <c r="W90">
-        <v>0.1815250126753739</v>
+        <v>0.1817415855666618</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3199699091073398</v>
+        <v>0.3163747415892798</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2071886949392387</v>
+        <v>0.2087386949392387</v>
       </c>
       <c r="C91">
-        <v>-8359.083317506946</v>
+        <v>-8537.397766361937</v>
       </c>
       <c r="D91">
-        <v>3420.813682493053</v>
+        <v>3388.272233638062</v>
       </c>
       <c r="E91">
-        <v>10716.297</v>
+        <v>10862.07</v>
       </c>
       <c r="F91">
-        <v>12973.797</v>
+        <v>13119.57</v>
       </c>
       <c r="G91">
         <v>1193.9</v>
@@ -8755,37 +8755,37 @@
         <v>824.2</v>
       </c>
       <c r="M91">
-        <v>2605.1384376</v>
+        <v>2634.409656</v>
       </c>
       <c r="N91">
-        <v>-1780.9384376</v>
+        <v>-1810.209656</v>
       </c>
       <c r="O91">
-        <v>-534.2815312799999</v>
+        <v>-543.0628967999999</v>
       </c>
       <c r="P91">
-        <v>-1246.65690632</v>
+        <v>-1267.1467592</v>
       </c>
       <c r="Q91">
-        <v>-1094.05690632</v>
+        <v>-1114.5467592</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4130789434991795</v>
+        <v>0.4498068378490975</v>
       </c>
       <c r="T91">
-        <v>8.482192690512228</v>
+        <v>9.330411959563451</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.09491242247678394</v>
+        <v>0.09385784000481967</v>
       </c>
       <c r="W91">
-        <v>0.1817415855666618</v>
+        <v>0.1819533457270322</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3163747415892798</v>
+        <v>0.3128594666827322</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2087386949392387</v>
+        <v>0.2102886949392387</v>
       </c>
       <c r="C92">
-        <v>-8537.397766361937</v>
+        <v>-8715.098929960528</v>
       </c>
       <c r="D92">
-        <v>3388.272233638062</v>
+        <v>3356.34407003947</v>
       </c>
       <c r="E92">
-        <v>10862.07</v>
+        <v>11007.843</v>
       </c>
       <c r="F92">
-        <v>13119.57</v>
+        <v>13265.343</v>
       </c>
       <c r="G92">
         <v>1193.9</v>
@@ -8837,37 +8837,37 @@
         <v>824.2</v>
       </c>
       <c r="M92">
-        <v>2634.409656</v>
+        <v>2663.6808744</v>
       </c>
       <c r="N92">
-        <v>-1810.209656</v>
+        <v>-1839.4808744</v>
       </c>
       <c r="O92">
-        <v>-543.0628967999999</v>
+        <v>-551.84426232</v>
       </c>
       <c r="P92">
-        <v>-1267.1467592</v>
+        <v>-1287.63661208</v>
       </c>
       <c r="Q92">
-        <v>-1114.5467592</v>
+        <v>-1135.03661208</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4498068378490975</v>
+        <v>0.4946964864989972</v>
       </c>
       <c r="T92">
-        <v>9.330411959563451</v>
+        <v>10.36712439951495</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.09385784000481967</v>
+        <v>0.09282643516960186</v>
       </c>
       <c r="W92">
-        <v>0.1819533457270322</v>
+        <v>0.1821604518179439</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3128594666827322</v>
+        <v>0.3094214505653395</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2102886949392387</v>
+        <v>0.2118386949392387</v>
       </c>
       <c r="C93">
-        <v>-8715.098929960528</v>
+        <v>-8892.203983675268</v>
       </c>
       <c r="D93">
-        <v>3356.34407003947</v>
+        <v>3325.012016324732</v>
       </c>
       <c r="E93">
-        <v>11007.843</v>
+        <v>11153.616</v>
       </c>
       <c r="F93">
-        <v>13265.343</v>
+        <v>13411.116</v>
       </c>
       <c r="G93">
         <v>1193.9</v>
@@ -8919,37 +8919,37 @@
         <v>824.2</v>
       </c>
       <c r="M93">
-        <v>2663.6808744</v>
+        <v>2692.9520928</v>
       </c>
       <c r="N93">
-        <v>-1839.4808744</v>
+        <v>-1868.7520928</v>
       </c>
       <c r="O93">
-        <v>-551.84426232</v>
+        <v>-560.62562784</v>
       </c>
       <c r="P93">
-        <v>-1287.63661208</v>
+        <v>-1308.12646496</v>
       </c>
       <c r="Q93">
-        <v>-1135.03661208</v>
+        <v>-1155.52646496</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4946964864989972</v>
+        <v>0.550808547311372</v>
       </c>
       <c r="T93">
-        <v>10.36712439951495</v>
+        <v>11.66301494945432</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.09282643516960186</v>
+        <v>0.09181745217862793</v>
       </c>
       <c r="W93">
-        <v>0.1821604518179439</v>
+        <v>0.1823630556025315</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3094214505653395</v>
+        <v>0.3060581739287598</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2118386949392387</v>
+        <v>0.2133886949392387</v>
       </c>
       <c r="C94">
-        <v>-8892.203983675268</v>
+        <v>-9068.729467470024</v>
       </c>
       <c r="D94">
-        <v>3325.012016324732</v>
+        <v>3294.259532529974</v>
       </c>
       <c r="E94">
-        <v>11153.616</v>
+        <v>11299.389</v>
       </c>
       <c r="F94">
-        <v>13411.116</v>
+        <v>13556.889</v>
       </c>
       <c r="G94">
         <v>1193.9</v>
@@ -9001,37 +9001,37 @@
         <v>824.2</v>
       </c>
       <c r="M94">
-        <v>2692.9520928</v>
+        <v>2722.2233112</v>
       </c>
       <c r="N94">
-        <v>-1868.7520928</v>
+        <v>-1898.0233112</v>
       </c>
       <c r="O94">
-        <v>-560.62562784</v>
+        <v>-569.4069933599999</v>
       </c>
       <c r="P94">
-        <v>-1308.12646496</v>
+        <v>-1328.61631784</v>
       </c>
       <c r="Q94">
-        <v>-1155.52646496</v>
+        <v>-1176.01631784</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.550808547311372</v>
+        <v>0.6229526254987109</v>
       </c>
       <c r="T94">
-        <v>11.66301494945432</v>
+        <v>13.32915994223351</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.09181745217862793</v>
+        <v>0.09083016774659967</v>
       </c>
       <c r="W94">
-        <v>0.1823630556025315</v>
+        <v>0.1825613023164828</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3060581739287598</v>
+        <v>0.3027672258219989</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2133886949392387</v>
+        <v>0.2149386949392387</v>
       </c>
       <c r="C95">
-        <v>-9068.729467470024</v>
+        <v>-9244.691315014676</v>
       </c>
       <c r="D95">
-        <v>3294.259532529974</v>
+        <v>3264.070684985325</v>
       </c>
       <c r="E95">
-        <v>11299.389</v>
+        <v>11445.162</v>
       </c>
       <c r="F95">
-        <v>13556.889</v>
+        <v>13702.662</v>
       </c>
       <c r="G95">
         <v>1193.9</v>
@@ -9083,37 +9083,37 @@
         <v>824.2</v>
       </c>
       <c r="M95">
-        <v>2722.2233112</v>
+        <v>2751.4945296</v>
       </c>
       <c r="N95">
-        <v>-1898.0233112</v>
+        <v>-1927.2945296</v>
       </c>
       <c r="O95">
-        <v>-569.4069933599999</v>
+        <v>-578.18835888</v>
       </c>
       <c r="P95">
-        <v>-1328.61631784</v>
+        <v>-1349.10617072</v>
       </c>
       <c r="Q95">
-        <v>-1176.01631784</v>
+        <v>-1196.50617072</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6229526254987109</v>
+        <v>0.7191447297484962</v>
       </c>
       <c r="T95">
-        <v>13.32915994223351</v>
+        <v>15.55068659927243</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.09083016774659967</v>
+        <v>0.08986388936631669</v>
       </c>
       <c r="W95">
-        <v>0.1825613023164828</v>
+        <v>0.1827553310152436</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3027672258219989</v>
+        <v>0.2995462978877224</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2149386949392387</v>
+        <v>0.2164886949392388</v>
       </c>
       <c r="C96">
-        <v>-9244.691315014676</v>
+        <v>-9420.10488121344</v>
       </c>
       <c r="D96">
-        <v>3264.070684985325</v>
+        <v>3234.43011878656</v>
       </c>
       <c r="E96">
-        <v>11445.162</v>
+        <v>11590.935</v>
       </c>
       <c r="F96">
-        <v>13702.662</v>
+        <v>13848.435</v>
       </c>
       <c r="G96">
         <v>1193.9</v>
@@ -9165,37 +9165,37 @@
         <v>824.2</v>
       </c>
       <c r="M96">
-        <v>2751.4945296</v>
+        <v>2780.765748</v>
       </c>
       <c r="N96">
-        <v>-1927.2945296</v>
+        <v>-1956.565748</v>
       </c>
       <c r="O96">
-        <v>-578.18835888</v>
+        <v>-586.9697243999999</v>
       </c>
       <c r="P96">
-        <v>-1349.10617072</v>
+        <v>-1369.5960236</v>
       </c>
       <c r="Q96">
-        <v>-1196.50617072</v>
+        <v>-1216.9960236</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7191447297484962</v>
+        <v>0.853813675698196</v>
       </c>
       <c r="T96">
-        <v>15.55068659927243</v>
+        <v>18.66082391912693</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.08986388936631669</v>
+        <v>0.08891795368877653</v>
       </c>
       <c r="W96">
-        <v>0.1827553310152436</v>
+        <v>0.1829452748992937</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2995462978877224</v>
+        <v>0.2963931789625884</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2164886949392388</v>
+        <v>0.2180386949392387</v>
       </c>
       <c r="C97">
-        <v>-9420.10488121344</v>
+        <v>-9594.984968246858</v>
       </c>
       <c r="D97">
-        <v>3234.43011878656</v>
+        <v>3205.323031753142</v>
       </c>
       <c r="E97">
-        <v>11590.935</v>
+        <v>11736.708</v>
       </c>
       <c r="F97">
-        <v>13848.435</v>
+        <v>13994.208</v>
       </c>
       <c r="G97">
         <v>1193.9</v>
@@ -9247,37 +9247,37 @@
         <v>824.2</v>
       </c>
       <c r="M97">
-        <v>2780.765748</v>
+        <v>2810.0369664</v>
       </c>
       <c r="N97">
-        <v>-1956.565748</v>
+        <v>-1985.8369664</v>
       </c>
       <c r="O97">
-        <v>-586.9697243999999</v>
+        <v>-595.7510899199999</v>
       </c>
       <c r="P97">
-        <v>-1369.5960236</v>
+        <v>-1390.08587648</v>
       </c>
       <c r="Q97">
-        <v>-1216.9960236</v>
+        <v>-1237.48587648</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.853813675698196</v>
+        <v>1.055817094622745</v>
       </c>
       <c r="T97">
-        <v>18.66082391912693</v>
+        <v>23.32602989890866</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.08891795368877653</v>
+        <v>0.08799172500451845</v>
       </c>
       <c r="W97">
-        <v>0.1829452748992937</v>
+        <v>0.1831312616190927</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2963931789625884</v>
+        <v>0.2933057500150614</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2180386949392387</v>
+        <v>0.2195886949392387</v>
       </c>
       <c r="C98">
-        <v>-9594.984968246856</v>
+        <v>-9769.345850220161</v>
       </c>
       <c r="D98">
-        <v>3205.323031753142</v>
+        <v>3176.735149779839</v>
       </c>
       <c r="E98">
-        <v>11736.708</v>
+        <v>11882.481</v>
       </c>
       <c r="F98">
-        <v>13994.208</v>
+        <v>14139.981</v>
       </c>
       <c r="G98">
         <v>1193.9</v>
@@ -9329,37 +9329,37 @@
         <v>824.2</v>
       </c>
       <c r="M98">
-        <v>2810.0369664</v>
+        <v>2839.3081848</v>
       </c>
       <c r="N98">
-        <v>-1985.8369664</v>
+        <v>-2015.1081848</v>
       </c>
       <c r="O98">
-        <v>-595.7510899199999</v>
+        <v>-604.53245544</v>
       </c>
       <c r="P98">
-        <v>-1390.08587648</v>
+        <v>-1410.57572936</v>
       </c>
       <c r="Q98">
-        <v>-1237.48587648</v>
+        <v>-1257.97572936</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.055817094622743</v>
+        <v>1.39248945949699</v>
       </c>
       <c r="T98">
-        <v>23.3260298989086</v>
+        <v>31.10137319854481</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.08799172500451845</v>
+        <v>0.08708459381890483</v>
       </c>
       <c r="W98">
-        <v>0.1831312616190927</v>
+        <v>0.1833134135611639</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2933057500150614</v>
+        <v>0.2902819793963495</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2195886949392387</v>
+        <v>0.2211386949392387</v>
       </c>
       <c r="C99">
-        <v>-9769.345850220161</v>
+        <v>-9943.201296504278</v>
       </c>
       <c r="D99">
-        <v>3176.735149779839</v>
+        <v>3148.65270349572</v>
       </c>
       <c r="E99">
-        <v>11882.481</v>
+        <v>12028.254</v>
       </c>
       <c r="F99">
-        <v>14139.981</v>
+        <v>14285.754</v>
       </c>
       <c r="G99">
         <v>1193.9</v>
@@ -9411,37 +9411,37 @@
         <v>824.2</v>
       </c>
       <c r="M99">
-        <v>2839.3081848</v>
+        <v>2868.5794032</v>
       </c>
       <c r="N99">
-        <v>-2015.1081848</v>
+        <v>-2044.3794032</v>
       </c>
       <c r="O99">
-        <v>-604.53245544</v>
+        <v>-613.3138209599999</v>
       </c>
       <c r="P99">
-        <v>-1410.57572936</v>
+        <v>-1431.06558224</v>
       </c>
       <c r="Q99">
-        <v>-1257.97572936</v>
+        <v>-1278.46558224</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.39248945949699</v>
+        <v>2.065834189245485</v>
       </c>
       <c r="T99">
-        <v>31.10137319854481</v>
+        <v>46.65205979781721</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.08708459381890483</v>
+        <v>0.0861959755146303</v>
       </c>
       <c r="W99">
-        <v>0.1833134135611639</v>
+        <v>0.1834918481166622</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2902819793963495</v>
+        <v>0.287319918382101</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2211386949392387</v>
+        <v>0.2226886949392388</v>
       </c>
       <c r="C100">
-        <v>-9943.201296504278</v>
+        <v>-10116.56459384971</v>
       </c>
       <c r="D100">
-        <v>3148.65270349572</v>
+        <v>3121.062406150289</v>
       </c>
       <c r="E100">
-        <v>12028.254</v>
+        <v>12174.027</v>
       </c>
       <c r="F100">
-        <v>14285.754</v>
+        <v>14431.527</v>
       </c>
       <c r="G100">
         <v>1193.9</v>
@@ -9493,37 +9493,37 @@
         <v>824.2</v>
       </c>
       <c r="M100">
-        <v>2868.5794032</v>
+        <v>2897.8506216</v>
       </c>
       <c r="N100">
-        <v>-2044.3794032</v>
+        <v>-2073.6506216</v>
       </c>
       <c r="O100">
-        <v>-613.3138209599999</v>
+        <v>-622.0951864799999</v>
       </c>
       <c r="P100">
-        <v>-1431.06558224</v>
+        <v>-1451.55543512</v>
       </c>
       <c r="Q100">
-        <v>-1278.46558224</v>
+        <v>-1298.95543512</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.065834189245485</v>
+        <v>4.085868378490971</v>
       </c>
       <c r="T100">
-        <v>46.65205979781721</v>
+        <v>93.30411959563442</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.0861959755146303</v>
+        <v>0.08532530909529061</v>
       </c>
       <c r="W100">
-        <v>0.1834918481166622</v>
+        <v>0.1836666779336657</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.287319918382101</v>
+        <v>0.2844176969843021</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2226886949392388</v>
-      </c>
-      <c r="C101">
-        <v>-10116.56459384971</v>
-      </c>
-      <c r="D101">
-        <v>3121.062406150289</v>
-      </c>
-      <c r="E101">
-        <v>12174.027</v>
-      </c>
-      <c r="F101">
-        <v>14431.527</v>
-      </c>
-      <c r="G101">
-        <v>1193.9</v>
-      </c>
-      <c r="H101">
-        <v>12319.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>976.8</v>
-      </c>
-      <c r="K101">
-        <v>152.5999999999999</v>
-      </c>
-      <c r="L101">
-        <v>824.2</v>
-      </c>
-      <c r="M101">
-        <v>2897.8506216</v>
-      </c>
-      <c r="N101">
-        <v>-2073.6506216</v>
-      </c>
-      <c r="O101">
-        <v>-622.0951864799999</v>
-      </c>
-      <c r="P101">
-        <v>-1451.55543512</v>
-      </c>
-      <c r="Q101">
-        <v>-1298.95543512</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.085868378490971</v>
-      </c>
-      <c r="T101">
-        <v>93.30411959563442</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.08532530909529061</v>
-      </c>
-      <c r="W101">
-        <v>0.1836666779336657</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2844176969843021</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
